--- a/listings-sale.xlsx
+++ b/listings-sale.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4790" uniqueCount="1013">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4790" uniqueCount="1016">
   <si>
     <t>Source</t>
   </si>
@@ -167,12 +167,12 @@
     <t>https://www.barnes-international.com/en/for-sale/france/boulogne-billancourt/ref-APM-85141225.html</t>
   </si>
   <si>
+    <t>https://www.barnes-international.com/en/for-sale/france/boulogne-billancourt/ref-APM-87142043.html</t>
+  </si>
+  <si>
     <t>https://www.barnes-international.com/en/for-sale/france/boulogne-billancourt/ref-APM-87180111.html</t>
   </si>
   <si>
-    <t>https://www.barnes-international.com/en/for-sale/france/boulogne-billancourt/ref-APM-87142043.html</t>
-  </si>
-  <si>
     <t>https://www.barnes-international.com/en/for-sale/france/boulogne-billancourt/ref-APM-87044516.html</t>
   </si>
   <si>
@@ -227,12 +227,12 @@
     <t>https://www.barnes-international.com/en/for-sale/france/boulogne-billancourt/ref-APM-86668965.html</t>
   </si>
   <si>
+    <t>https://www.barnes-international.com/en/for-sale/france/boulogne-billancourt/ref-APM-87090755.html</t>
+  </si>
+  <si>
     <t>https://www.barnes-international.com/en/for-sale/france/boulogne-billancourt/ref-APM-86688062.html</t>
   </si>
   <si>
-    <t>https://www.barnes-international.com/en/for-sale/france/boulogne-billancourt/ref-APM-87090755.html</t>
-  </si>
-  <si>
     <t>https://www.barnes-international.com/en/for-sale/france/boulogne-billancourt/ref-APM-85341482.html</t>
   </si>
   <si>
@@ -242,12 +242,12 @@
     <t>https://www.barnes-international.com/en/for-sale/france/boulogne-billancourt/ref-APM-87014108.html</t>
   </si>
   <si>
+    <t>https://www.barnes-international.com/en/for-sale/france/boulogne-billancourt/ref-APM-86687783.html</t>
+  </si>
+  <si>
     <t>https://www.barnes-international.com/en/for-sale/france/boulogne-billancourt/ref-APM-86869751.html</t>
   </si>
   <si>
-    <t>https://www.barnes-international.com/en/for-sale/france/boulogne-billancourt/ref-APM-86687783.html</t>
-  </si>
-  <si>
     <t>https://www.barnes-international.com/en/for-sale/france/boulogne-billancourt/ref-APM-86940243.html</t>
   </si>
   <si>
@@ -2342,351 +2342,345 @@
     <t>https://www.junot.fr/fr/biens/86680981-rueil-malmaison-buzenval</t>
   </si>
   <si>
+    <t>Issy-les-Moulineaux</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86869353-issy-les-moulineaux-ile-saint-germain</t>
+  </si>
+  <si>
+    <t>La-Garenne-Colombes</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86822565-la-garenne-colombes-centre-joffre</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/87100502-levallois-perret-rue-louise-michel</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86701550-levallois-perret-rue-louise-michel</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86853140-levallois-perret-ile-de-la-jatte</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86708606-levallois-perret-centre</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86485296-neuilly-sur-seine-victor-hugo</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/85763759-neuilly-sur-seine-bineau-inkermann</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86796860-neuilly-sur-seine-chezy-borghese</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/85956594-neuilly-sur-seine-victor-hugo</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86054527-neuilly-sur-seine-victor-hugo</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86051120-neuilly-sur-seine-victor-hugo</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86050603-neuilly-sur-seine-victor-hugo</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86050567-neuilly-sur-seine-victor-hugo</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86050621-neuilly-sur-seine-victor-hugo</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86832826-neuilly-sur-seine-chateau</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86929257-paris-17e-berthier-pereire</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86786953-paris-17e-pereire</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86626370-paris-17e-pereire</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86333838-paris-17e-rue-faraday</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86209540-neuilly-sur-seine-victor-hugo</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/85955977-neuilly-sur-seine-victor-hugo</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/87090480-paris-17e-pereire</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/87013921-neuilly-sur-seine-sablons</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/87102677-neuilly-sur-seine-sablons-roule</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86209563-neuilly-sur-seine-victor-hugo</t>
+  </si>
+  <si>
+    <t>Meudon</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86726109-meudon-bellevue</t>
+  </si>
+  <si>
+    <t>Nanterre</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86955023-nanterre-mont-valerien</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86600894-nanterre-centre-rer</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86711850-rueil-malmaison-coteaux</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/87145908-suresnes-liberte</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86279836-rueil-malmaison-coeur-de-ville</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/83448958-rueil-malmaison-les-coteaux</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86502288-rueil-malmaison-mont-valerien</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86656447-rueil-malmaison-coteaux</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86737189-rueil-malmaison-coteaux</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86732987-suresnes-fecheray</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86961848-rueil-malmaison-centre-ville</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86754230-rueil-malmaison-rueil-sur-seine</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/87013564-suresnes-carnot-gambetta</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/85342115-rueil-malmaison-plateau</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86855201-suresnes-carnot-gambetta</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86818496-rueil-malmaison-mont-valerien</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86665428-rueil-malmaison-mont-valerien</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86406200-rueil-malmaison-triangle-dor-les-martinets</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86872057-rueil-malmaison-buzenval</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86803064-rueil-malmaison-mont-valerien</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/87151941-rueil-malmaison-mont-valerien</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/82823472-rueil-malmaison-centre-ville</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/87176871-neuilly-sur-seine-saint-james</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/87169484-neuilly-sur-seine</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/87095615-neuilly-sur-seine-victor-hugo</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86884592-neuilly-sur-seine-sablons</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86108932-neuilly-sur-seine-pont-de-neuilly</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86911620-neuilly-sur-seine-madrid-saint-james</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86806678-neuilly-sur-seine-pont-de-neuilly</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/85460591-rueil-malmaison-saint-cucufa</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/82573732-rueil-malmaison-centre-ville</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86872335-rueil-malmaison-bords-de-seine</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/87089492-rueil-malmaison-saint-cucufa</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86883296-rueil-malmaison-richelieu</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86790803-rueil-malmaison-centre-ville-chateau-de-la-malmaison</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/87090496-rueil-malmaison-buzenval</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/87043503-rueil-malmaison-saint-cucufa</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/85269373-rueil-malmaison-hameau-de-la-jonchere</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/84234005-rueil-malmaison-centre-ville</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/87003936-rueil-malmaison-chataigneraie-empereur</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/85308431-rueil-malmaison-parc-de-la-malmaison</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/85972482-rueil-malmaison-buzenval</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/85639422-rueil-malmaison-parc-de-la-malmaison</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86778792-rueil-malmaison-saint-cucufa</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/85842451-rueil-malmaison-saint-cucufa</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/85624615-rueil-malmaison-coeur-de-ville</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86992006-saint-cloud-montretout</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/87119982-saint-cloud-pasteur</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/87069117-saint-cloud-parc-de-montretout</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86364093-saint-cloud-montretout</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86377932-saint-cloud-montretout</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/87072517-saint-cloud-montretout</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/84682885-saint-cloud-les-coteaux</t>
+  </si>
+  <si>
+    <t>Sceaux</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86935086-sceaux-parc-de-sceaux</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86358591-verrieres-le-buisson-entre-le-centre-et-la-foret</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86369553-vanves-michelet</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86044992-paris-15e-convention</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86342372-paris-15e-convention</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86095295-paris-15e-vaugirard</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/87149452-paris-14e-rue-roli</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/87220895-paris-15e-saint-lambert</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86741268-suresnes-parc-du-chateau-republique</t>
+  </si>
+  <si>
+    <t>Vanves</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86800284-paris-15e-villa-violet</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86694620-paris-15e-quartier-commerce</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86962420-paris-15e-entrepreneurs-commerce</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86689945-paris-16e-garigliano</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86694718-paris-15e-quartier-commerce</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86694703-paris-15e-quartier-commerce</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/85962720-paris-15e-volontaires</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/87252349-paris-15e-commerce-fondary</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/87067584-paris-15e-suffren-breteuil</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/87067560-paris-15e</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/87067590-paris-15e-suffren-breteuil</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86492856-vaucresson-division-thery</t>
+  </si>
+  <si>
+    <t>Ville-D-Avray</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86927403-ville-d-avray-centre</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/87157964-ville-d-avray-cote-dargent</t>
+  </si>
+  <si>
     <t>https://www.junot.fr/fr/biens/86973126-ville-d-avray-centre</t>
   </si>
   <si>
-    <t>https://www.junot.fr/fr/biens/86992006-saint-cloud-montretout</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86364093-saint-cloud-montretout</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/87119982-saint-cloud-pasteur</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/87043503-rueil-malmaison-saint-cucufa</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/87072517-saint-cloud-montretout</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86377932-saint-cloud-montretout</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86191512-rueil-malmaison-richelieu-chataigneraie</t>
+    <t>https://www.junot.fr/fr/biens/85599270-ville-d-avray-les-etangs-de-corot</t>
   </si>
   <si>
     <t>https://www.junot.fr/fr/biens/85905505-ville-d-avray-cote-dargent</t>
   </si>
   <si>
-    <t>https://www.junot.fr/fr/biens/86235728-saint-cloud-milons</t>
-  </si>
-  <si>
-    <t>Issy-les-Moulineaux</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86869353-issy-les-moulineaux-ile-saint-germain</t>
-  </si>
-  <si>
-    <t>La-Garenne-Colombes</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86822565-la-garenne-colombes-centre-joffre</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/87100502-levallois-perret-rue-louise-michel</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86701550-levallois-perret-rue-louise-michel</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86853140-levallois-perret-ile-de-la-jatte</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86708606-levallois-perret-centre</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86485296-neuilly-sur-seine-victor-hugo</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/85763759-neuilly-sur-seine-bineau-inkermann</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86796860-neuilly-sur-seine-chezy-borghese</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/85956594-neuilly-sur-seine-victor-hugo</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86054527-neuilly-sur-seine-victor-hugo</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86051120-neuilly-sur-seine-victor-hugo</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86050603-neuilly-sur-seine-victor-hugo</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86050567-neuilly-sur-seine-victor-hugo</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86050621-neuilly-sur-seine-victor-hugo</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86832826-neuilly-sur-seine-chateau</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86929257-paris-17e-berthier-pereire</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86786953-paris-17e-pereire</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86626370-paris-17e-pereire</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86333838-paris-17e-rue-faraday</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86209540-neuilly-sur-seine-victor-hugo</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/85955977-neuilly-sur-seine-victor-hugo</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/87090480-paris-17e-pereire</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/87013921-neuilly-sur-seine-sablons</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/87102677-neuilly-sur-seine-sablons-roule</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86209563-neuilly-sur-seine-victor-hugo</t>
-  </si>
-  <si>
-    <t>Meudon</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86726109-meudon-bellevue</t>
-  </si>
-  <si>
-    <t>Nanterre</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86955023-nanterre-mont-valerien</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86600894-nanterre-centre-rer</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86711850-rueil-malmaison-coteaux</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/87145908-suresnes-liberte</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86279836-rueil-malmaison-coeur-de-ville</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/83448958-rueil-malmaison-les-coteaux</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86502288-rueil-malmaison-mont-valerien</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86656447-rueil-malmaison-coteaux</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86737189-rueil-malmaison-coteaux</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86732987-suresnes-fecheray</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86961848-rueil-malmaison-centre-ville</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86754230-rueil-malmaison-rueil-sur-seine</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/87013564-suresnes-carnot-gambetta</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/85342115-rueil-malmaison-plateau</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86855201-suresnes-carnot-gambetta</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86818496-rueil-malmaison-mont-valerien</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86665428-rueil-malmaison-mont-valerien</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86406200-rueil-malmaison-triangle-dor-les-martinets</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86872057-rueil-malmaison-buzenval</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86803064-rueil-malmaison-mont-valerien</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/87151941-rueil-malmaison-mont-valerien</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/82823472-rueil-malmaison-centre-ville</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/87176871-neuilly-sur-seine-saint-james</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/87169484-neuilly-sur-seine</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/87095615-neuilly-sur-seine-victor-hugo</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86884592-neuilly-sur-seine-sablons</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86108932-neuilly-sur-seine-pont-de-neuilly</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86911620-neuilly-sur-seine-madrid-saint-james</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86806678-neuilly-sur-seine-pont-de-neuilly</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/85460591-rueil-malmaison-saint-cucufa</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/82573732-rueil-malmaison-centre-ville</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86872335-rueil-malmaison-bords-de-seine</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/87089492-rueil-malmaison-saint-cucufa</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86883296-rueil-malmaison-richelieu</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86790803-rueil-malmaison-centre-ville-chateau-de-la-malmaison</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/87090496-rueil-malmaison-buzenval</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/85269373-rueil-malmaison-hameau-de-la-jonchere</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/84234005-rueil-malmaison-centre-ville</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/87003936-rueil-malmaison-chataigneraie-empereur</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/85308431-rueil-malmaison-parc-de-la-malmaison</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/85972482-rueil-malmaison-buzenval</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/85639422-rueil-malmaison-parc-de-la-malmaison</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86778792-rueil-malmaison-saint-cucufa</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/85842451-rueil-malmaison-saint-cucufa</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/85624615-rueil-malmaison-coeur-de-ville</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/87069117-saint-cloud-parc-de-montretout</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/84682885-saint-cloud-les-coteaux</t>
-  </si>
-  <si>
-    <t>Sceaux</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86935086-sceaux-parc-de-sceaux</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86358591-verrieres-le-buisson-entre-le-centre-et-la-foret</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86369553-vanves-michelet</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86044992-paris-15e-convention</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86342372-paris-15e-convention</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86095295-paris-15e-vaugirard</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/87149452-paris-14e-rue-roli</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/87220895-paris-15e-saint-lambert</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86741268-suresnes-parc-du-chateau-republique</t>
-  </si>
-  <si>
-    <t>Vanves</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86800284-paris-15e-villa-violet</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86694620-paris-15e-quartier-commerce</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86962420-paris-15e-entrepreneurs-commerce</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86689945-paris-16e-garigliano</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86694718-paris-15e-quartier-commerce</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86694703-paris-15e-quartier-commerce</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/85962720-paris-15e-volontaires</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/87252349-paris-15e-commerce-fondary</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/87067584-paris-15e-suffren-breteuil</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/87067560-paris-15e</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/87067590-paris-15e-suffren-breteuil</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86492856-vaucresson-division-thery</t>
-  </si>
-  <si>
-    <t>Ville-D-Avray</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86927403-ville-d-avray-centre</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/87157964-ville-d-avray-cote-dargent</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/85599270-ville-d-avray-les-etangs-de-corot</t>
-  </si>
-  <si>
     <t>Bougival</t>
   </si>
   <si>
@@ -2744,12 +2738,33 @@
     <t>https://www.junot.fr/fr/biens/87170292-le-vesinet-centre-ville</t>
   </si>
   <si>
+    <t>https://www.junot.fr/fr/biens/86197868-le-vesinet-centre</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86491268-le-vesinet-charmettes</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/85675677-le-vesinet</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/87049238-croissy-sur-seine-coeur-de-ville</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86872237-le-vesinet-centre</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86355108-le-vesinet-charmettes</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/87116726-le-vesinet-centre</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86353933-rueil-malmaison-bords-de-seine</t>
+  </si>
+  <si>
     <t>Croissy-sur-Seine</t>
   </si>
   <si>
-    <t>https://www.junot.fr/fr/biens/87049238-croissy-sur-seine-coeur-de-ville</t>
-  </si>
-  <si>
     <t>https://www.junot.fr/fr/biens/86744535-croissy-sur-seine-quartier-de-lecluse</t>
   </si>
   <si>
@@ -2777,133 +2792,127 @@
     <t>https://www.junot.fr/fr/biens/86333080-la-celle-saint-cloud-chataigneraie</t>
   </si>
   <si>
+    <t>Le-Chesnay-Rocquencourt</t>
+  </si>
+  <si>
     <t>https://www.junot.fr/fr/biens/86796631-le-chesnay-rocquencourt-aubert</t>
   </si>
   <si>
+    <t>Le-Mesnil-le-Roi</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86383927-le-mesnil-le-roi-saint-germain-en-laye</t>
+  </si>
+  <si>
+    <t>Le-Pecq</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86820063-le-pecq-limite-le-vesinet</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86341196-le-vesinet-pelouses</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/85932180-le-vesinet-ibis</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/85969840-le-vesinet-lac-inferieur</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86495403-le-vesinet-lac-inferieur</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/87097485-marly-le-roi-montval</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86346204-le-vesinet-lac-inferieur</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86837357-le-vesinet-centre-ville</t>
+  </si>
+  <si>
+    <t>Louveciennes</t>
+  </si>
+  <si>
     <t>https://www.junot.fr/fr/biens/85998514-louveciennes-louveciennes</t>
   </si>
   <si>
-    <t>Le-Chesnay-Rocquencourt</t>
+    <t>Maisons-Laffitte</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/87093747-maisons-laffitte-parc-de-maisons-laffitte</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/85936999-maisons-laffitte-entre-centre-et-parc</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/87042274-maisons-laffitte-parc</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86373985-maisons-laffitte-foch</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86800783-maisons-laffitte-petit-parc</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86933530-maisons-laffitte-charlemagne</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86344051-maisons-laffitte-petit-parc</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86344394-maisons-laffitte-petit-parc</t>
+  </si>
+  <si>
+    <t>Marly-le-Roi</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86082156-marly-le-roi-village</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86802694-marly-le-roi-village</t>
+  </si>
+  <si>
+    <t>Neauphle-le-Chateau</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86281033-neauphle-le-chateau-ile-de-france</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86962497-thoiry-yvelines</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86749833-versailles-saint-louis</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86875411-versailles-saint-louis</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/87024618-rambouillet-eure-et-loir</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86096224-rambouillet-yvelines</t>
+  </si>
+  <si>
+    <t>Rambouillet</t>
   </si>
   <si>
     <t>https://www.junot.fr/fr/biens/86760248-versailles-notre-dame</t>
   </si>
   <si>
-    <t>https://www.junot.fr/fr/biens/86749833-versailles-saint-louis</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86875411-versailles-saint-louis</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86802694-marly-le-roi-village</t>
-  </si>
-  <si>
     <t>https://www.junot.fr/fr/biens/86822950-versailles-centre-ville</t>
   </si>
   <si>
-    <t>https://www.junot.fr/fr/biens/86082156-marly-le-roi-village</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/87097485-marly-le-roi-montval</t>
-  </si>
-  <si>
-    <t>Le-Mesnil-le-Roi</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86383927-le-mesnil-le-roi-saint-germain-en-laye</t>
-  </si>
-  <si>
-    <t>Le-Pecq</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86820063-le-pecq-limite-le-vesinet</t>
-  </si>
-  <si>
-    <t>Le-Vesinet</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86355108-le-vesinet-charmettes</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/87116726-le-vesinet-centre</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86346204-le-vesinet-lac-inferieur</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86495403-le-vesinet-lac-inferieur</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86491268-le-vesinet-charmettes</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86872237-le-vesinet-centre</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86837357-le-vesinet-centre-ville</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/85675677-le-vesinet</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/85932180-le-vesinet-ibis</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86341196-le-vesinet-pelouses</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/85969840-le-vesinet-lac-inferieur</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86197868-le-vesinet-centre</t>
-  </si>
-  <si>
-    <t>Maisons-Laffitte</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/87093747-maisons-laffitte-parc-de-maisons-laffitte</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/85936999-maisons-laffitte-entre-centre-et-parc</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/87042274-maisons-laffitte-parc</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86373985-maisons-laffitte-foch</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86800783-maisons-laffitte-petit-parc</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86933530-maisons-laffitte-charlemagne</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86344051-maisons-laffitte-petit-parc</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86344394-maisons-laffitte-petit-parc</t>
-  </si>
-  <si>
-    <t>Neauphle-le-Chateau</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86281033-neauphle-le-chateau-ile-de-france</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86962497-thoiry-yvelines</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/87024618-rambouillet-eure-et-loir</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86096224-rambouillet-yvelines</t>
+    <t>Thoiry</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86910338-bray-et-lu-vexin</t>
   </si>
   <si>
     <t>Prospector — Paris Listings</t>
   </si>
   <si>
-    <t>Generated: 15/08/2026, 07:56:57</t>
+    <t>Generated: 16/08/2026, 08:03:02</t>
   </si>
   <si>
     <t>Barnes: FAILED — Timed out after 300000ms: Barnes scrape</t>
@@ -4729,13 +4738,13 @@
         <v>1790000</v>
       </c>
       <c r="C37" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D37" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E37" s="2">
-        <v>162</v>
+        <v>137</v>
       </c>
       <c r="F37" s="4">
         <f>B37/E37</f>
@@ -4764,13 +4773,13 @@
         <v>1790000</v>
       </c>
       <c r="C38" s="2">
+        <v>5</v>
+      </c>
+      <c r="D38" s="2">
         <v>3</v>
       </c>
-      <c r="D38" s="2">
-        <v>2</v>
-      </c>
       <c r="E38" s="2">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="F38" s="4">
         <f>B38/E38</f>
@@ -5430,10 +5439,10 @@
         <v>3</v>
       </c>
       <c r="D57" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E57" s="2">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="F57" s="4">
         <f>B57/E57</f>
@@ -5465,10 +5474,10 @@
         <v>3</v>
       </c>
       <c r="D58" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E58" s="2">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="F58" s="4">
         <f>B58/E58</f>
@@ -5602,13 +5611,13 @@
         <v>750000</v>
       </c>
       <c r="C62" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D62" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E62" s="2">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F62" s="4">
         <f>B62/E62</f>
@@ -5637,13 +5646,13 @@
         <v>750000</v>
       </c>
       <c r="C63" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D63" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E63" s="2">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F63" s="4">
         <f>B63/E63</f>
@@ -24697,22 +24706,22 @@
         <v>731</v>
       </c>
       <c r="B612" s="3">
-        <v>2700000</v>
+        <v>2900000</v>
       </c>
       <c r="C612" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D612" s="2">
         <v>1</v>
       </c>
       <c r="E612" s="2">
-        <v>328.59</v>
+        <v>206.01</v>
       </c>
       <c r="F612" s="4">
         <f>B612/E612</f>
       </c>
       <c r="G612" s="2" t="s">
-        <v>200</v>
+        <v>776</v>
       </c>
       <c r="H612" s="2" t="s">
         <v>13</v>
@@ -24724,7 +24733,7 @@
         <v>14</v>
       </c>
       <c r="K612" s="2" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
     </row>
     <row r="613" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24732,22 +24741,22 @@
         <v>731</v>
       </c>
       <c r="B613" s="3">
-        <v>390000</v>
+        <v>1295000</v>
       </c>
       <c r="C613" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D613" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E613" s="2">
-        <v>48.26</v>
+        <v>174.35</v>
       </c>
       <c r="F613" s="4">
         <f>B613/E613</f>
       </c>
       <c r="G613" s="2" t="s">
-        <v>200</v>
+        <v>778</v>
       </c>
       <c r="H613" s="2" t="s">
         <v>13</v>
@@ -24759,7 +24768,7 @@
         <v>14</v>
       </c>
       <c r="K613" s="2" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
     </row>
     <row r="614" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24767,25 +24776,25 @@
         <v>731</v>
       </c>
       <c r="B614" s="3">
-        <v>2780000</v>
+        <v>735000</v>
       </c>
       <c r="C614" s="2">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D614" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E614" s="2">
-        <v>425.73</v>
+        <v>66</v>
       </c>
       <c r="F614" s="4">
         <f>B614/E614</f>
       </c>
       <c r="G614" s="2" t="s">
-        <v>200</v>
+        <v>109</v>
       </c>
       <c r="H614" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="I614" s="2" t="s">
         <v>13</v>
@@ -24794,7 +24803,7 @@
         <v>14</v>
       </c>
       <c r="K614" s="2" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
     </row>
     <row r="615" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24802,21 +24811,25 @@
         <v>731</v>
       </c>
       <c r="B615" s="3">
-        <v>1570000</v>
-      </c>
-      <c r="C615" s="2"/>
-      <c r="D615" s="2"/>
+        <v>735000</v>
+      </c>
+      <c r="C615" s="2">
+        <v>2</v>
+      </c>
+      <c r="D615" s="2">
+        <v>1</v>
+      </c>
       <c r="E615" s="2">
-        <v>280.1</v>
+        <v>66</v>
       </c>
       <c r="F615" s="4">
         <f>B615/E615</f>
       </c>
       <c r="G615" s="2" t="s">
-        <v>200</v>
+        <v>109</v>
       </c>
       <c r="H615" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="I615" s="2" t="s">
         <v>13</v>
@@ -24825,7 +24838,7 @@
         <v>14</v>
       </c>
       <c r="K615" s="2" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
     </row>
     <row r="616" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24833,25 +24846,25 @@
         <v>731</v>
       </c>
       <c r="B616" s="3">
-        <v>1750000</v>
+        <v>1290000</v>
       </c>
       <c r="C616" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D616" s="2">
         <v>1</v>
       </c>
       <c r="E616" s="2">
-        <v>233</v>
+        <v>105.32</v>
       </c>
       <c r="F616" s="4">
         <f>B616/E616</f>
       </c>
       <c r="G616" s="2" t="s">
-        <v>200</v>
+        <v>109</v>
       </c>
       <c r="H616" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="I616" s="2" t="s">
         <v>13</v>
@@ -24860,7 +24873,7 @@
         <v>14</v>
       </c>
       <c r="K616" s="2" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
     </row>
     <row r="617" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24868,25 +24881,25 @@
         <v>731</v>
       </c>
       <c r="B617" s="3">
-        <v>2690000</v>
+        <v>2150000</v>
       </c>
       <c r="C617" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D617" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E617" s="2">
-        <v>262.48</v>
+        <v>160.24</v>
       </c>
       <c r="F617" s="4">
         <f>B617/E617</f>
       </c>
       <c r="G617" s="2" t="s">
-        <v>200</v>
+        <v>109</v>
       </c>
       <c r="H617" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="I617" s="2" t="s">
         <v>13</v>
@@ -24895,7 +24908,7 @@
         <v>14</v>
       </c>
       <c r="K617" s="2" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
     </row>
     <row r="618" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24903,25 +24916,23 @@
         <v>731</v>
       </c>
       <c r="B618" s="3">
-        <v>2490000</v>
-      </c>
-      <c r="C618" s="2">
-        <v>10</v>
-      </c>
+        <v>350000</v>
+      </c>
+      <c r="C618" s="2"/>
       <c r="D618" s="2">
         <v>1</v>
       </c>
       <c r="E618" s="2">
-        <v>295</v>
+        <v>32.99</v>
       </c>
       <c r="F618" s="4">
         <f>B618/E618</f>
       </c>
       <c r="G618" s="2" t="s">
-        <v>200</v>
+        <v>109</v>
       </c>
       <c r="H618" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="I618" s="2" t="s">
         <v>214</v>
@@ -24930,7 +24941,7 @@
         <v>14</v>
       </c>
       <c r="K618" s="2" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
     </row>
     <row r="619" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24938,25 +24949,25 @@
         <v>731</v>
       </c>
       <c r="B619" s="3">
-        <v>875000</v>
+        <v>2290000</v>
       </c>
       <c r="C619" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D619" s="2">
         <v>1</v>
       </c>
       <c r="E619" s="2">
-        <v>123.72</v>
+        <v>134</v>
       </c>
       <c r="F619" s="4">
         <f>B619/E619</f>
       </c>
       <c r="G619" s="2" t="s">
-        <v>200</v>
+        <v>109</v>
       </c>
       <c r="H619" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="I619" s="2" t="s">
         <v>13</v>
@@ -24965,7 +24976,7 @@
         <v>14</v>
       </c>
       <c r="K619" s="2" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
     </row>
     <row r="620" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24973,25 +24984,25 @@
         <v>731</v>
       </c>
       <c r="B620" s="3">
-        <v>3290000</v>
+        <v>2295000</v>
       </c>
       <c r="C620" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D620" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E620" s="2">
-        <v>430.3</v>
+        <v>172.78</v>
       </c>
       <c r="F620" s="4">
         <f>B620/E620</f>
       </c>
       <c r="G620" s="2" t="s">
-        <v>200</v>
+        <v>109</v>
       </c>
       <c r="H620" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="I620" s="2" t="s">
         <v>13</v>
@@ -25000,7 +25011,7 @@
         <v>14</v>
       </c>
       <c r="K620" s="2" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
     </row>
     <row r="621" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25008,25 +25019,23 @@
         <v>731</v>
       </c>
       <c r="B621" s="3">
-        <v>450000</v>
-      </c>
-      <c r="C621" s="2">
-        <v>1</v>
-      </c>
+        <v>2575000</v>
+      </c>
+      <c r="C621" s="2"/>
       <c r="D621" s="2">
         <v>1</v>
       </c>
       <c r="E621" s="2">
-        <v>71</v>
+        <v>170.9</v>
       </c>
       <c r="F621" s="4">
         <f>B621/E621</f>
       </c>
       <c r="G621" s="2" t="s">
-        <v>200</v>
+        <v>109</v>
       </c>
       <c r="H621" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="I621" s="2" t="s">
         <v>13</v>
@@ -25035,7 +25044,7 @@
         <v>14</v>
       </c>
       <c r="K621" s="2" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
     </row>
     <row r="622" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25043,25 +25052,21 @@
         <v>731</v>
       </c>
       <c r="B622" s="3">
-        <v>2900000</v>
-      </c>
-      <c r="C622" s="2">
-        <v>3</v>
-      </c>
-      <c r="D622" s="2">
-        <v>1</v>
-      </c>
+        <v>306275</v>
+      </c>
+      <c r="C622" s="2"/>
+      <c r="D622" s="2"/>
       <c r="E622" s="2">
-        <v>206.01</v>
+        <v>20.4</v>
       </c>
       <c r="F622" s="4">
         <f>B622/E622</f>
       </c>
       <c r="G622" s="2" t="s">
-        <v>786</v>
+        <v>109</v>
       </c>
       <c r="H622" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="I622" s="2" t="s">
         <v>13</v>
@@ -25070,7 +25075,7 @@
         <v>14</v>
       </c>
       <c r="K622" s="2" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
     </row>
     <row r="623" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25078,25 +25083,23 @@
         <v>731</v>
       </c>
       <c r="B623" s="3">
-        <v>1295000</v>
-      </c>
-      <c r="C623" s="2">
-        <v>4</v>
-      </c>
+        <v>1883000</v>
+      </c>
+      <c r="C623" s="2"/>
       <c r="D623" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E623" s="2">
-        <v>174.35</v>
+        <v>126</v>
       </c>
       <c r="F623" s="4">
         <f>B623/E623</f>
       </c>
       <c r="G623" s="2" t="s">
-        <v>788</v>
+        <v>109</v>
       </c>
       <c r="H623" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="I623" s="2" t="s">
         <v>13</v>
@@ -25113,16 +25116,12 @@
         <v>731</v>
       </c>
       <c r="B624" s="3">
-        <v>735000</v>
-      </c>
-      <c r="C624" s="2">
-        <v>2</v>
-      </c>
-      <c r="D624" s="2">
-        <v>1</v>
-      </c>
+        <v>1919950</v>
+      </c>
+      <c r="C624" s="2"/>
+      <c r="D624" s="2"/>
       <c r="E624" s="2">
-        <v>66</v>
+        <v>135.1</v>
       </c>
       <c r="F624" s="4">
         <f>B624/E624</f>
@@ -25148,16 +25147,12 @@
         <v>731</v>
       </c>
       <c r="B625" s="3">
-        <v>735000</v>
-      </c>
-      <c r="C625" s="2">
-        <v>2</v>
-      </c>
-      <c r="D625" s="2">
-        <v>1</v>
-      </c>
+        <v>2269400</v>
+      </c>
+      <c r="C625" s="2"/>
+      <c r="D625" s="2"/>
       <c r="E625" s="2">
-        <v>66</v>
+        <v>160.6</v>
       </c>
       <c r="F625" s="4">
         <f>B625/E625</f>
@@ -25183,16 +25178,12 @@
         <v>731</v>
       </c>
       <c r="B626" s="3">
-        <v>1290000</v>
-      </c>
-      <c r="C626" s="2">
-        <v>2</v>
-      </c>
-      <c r="D626" s="2">
-        <v>1</v>
-      </c>
+        <v>2328550</v>
+      </c>
+      <c r="C626" s="2"/>
+      <c r="D626" s="2"/>
       <c r="E626" s="2">
-        <v>105.32</v>
+        <v>158</v>
       </c>
       <c r="F626" s="4">
         <f>B626/E626</f>
@@ -25218,16 +25209,16 @@
         <v>731</v>
       </c>
       <c r="B627" s="3">
-        <v>2150000</v>
+        <v>1275000</v>
       </c>
       <c r="C627" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D627" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E627" s="2">
-        <v>160.24</v>
+        <v>109.85</v>
       </c>
       <c r="F627" s="4">
         <f>B627/E627</f>
@@ -25239,7 +25230,7 @@
         <v>214</v>
       </c>
       <c r="I627" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="J627" s="2" t="s">
         <v>14</v>
@@ -25253,14 +25244,16 @@
         <v>731</v>
       </c>
       <c r="B628" s="3">
-        <v>350000</v>
-      </c>
-      <c r="C628" s="2"/>
+        <v>1750000</v>
+      </c>
+      <c r="C628" s="2">
+        <v>5</v>
+      </c>
       <c r="D628" s="2">
         <v>1</v>
       </c>
       <c r="E628" s="2">
-        <v>32.99</v>
+        <v>159.85</v>
       </c>
       <c r="F628" s="4">
         <f>B628/E628</f>
@@ -25286,16 +25279,16 @@
         <v>731</v>
       </c>
       <c r="B629" s="3">
-        <v>2290000</v>
+        <v>798000</v>
       </c>
       <c r="C629" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D629" s="2">
         <v>1</v>
       </c>
       <c r="E629" s="2">
-        <v>134</v>
+        <v>73.88</v>
       </c>
       <c r="F629" s="4">
         <f>B629/E629</f>
@@ -25321,16 +25314,16 @@
         <v>731</v>
       </c>
       <c r="B630" s="3">
-        <v>2295000</v>
+        <v>639000</v>
       </c>
       <c r="C630" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D630" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E630" s="2">
-        <v>172.78</v>
+        <v>70.51</v>
       </c>
       <c r="F630" s="4">
         <f>B630/E630</f>
@@ -25342,7 +25335,7 @@
         <v>214</v>
       </c>
       <c r="I630" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="J630" s="2" t="s">
         <v>14</v>
@@ -25356,14 +25349,16 @@
         <v>731</v>
       </c>
       <c r="B631" s="3">
-        <v>2575000</v>
-      </c>
-      <c r="C631" s="2"/>
+        <v>289000</v>
+      </c>
+      <c r="C631" s="2">
+        <v>1</v>
+      </c>
       <c r="D631" s="2">
         <v>1</v>
       </c>
       <c r="E631" s="2">
-        <v>170.9</v>
+        <v>31.86</v>
       </c>
       <c r="F631" s="4">
         <f>B631/E631</f>
@@ -25372,7 +25367,7 @@
         <v>109</v>
       </c>
       <c r="H631" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="I631" s="2" t="s">
         <v>13</v>
@@ -25389,12 +25384,12 @@
         <v>731</v>
       </c>
       <c r="B632" s="3">
-        <v>306275</v>
+        <v>2533950</v>
       </c>
       <c r="C632" s="2"/>
       <c r="D632" s="2"/>
       <c r="E632" s="2">
-        <v>20.4</v>
+        <v>171</v>
       </c>
       <c r="F632" s="4">
         <f>B632/E632</f>
@@ -25406,7 +25401,7 @@
         <v>214</v>
       </c>
       <c r="I632" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="J632" s="2" t="s">
         <v>14</v>
@@ -25420,14 +25415,14 @@
         <v>731</v>
       </c>
       <c r="B633" s="3">
-        <v>1883000</v>
+        <v>2404300</v>
       </c>
       <c r="C633" s="2"/>
       <c r="D633" s="2">
         <v>1</v>
       </c>
       <c r="E633" s="2">
-        <v>126</v>
+        <v>170.7</v>
       </c>
       <c r="F633" s="4">
         <f>B633/E633</f>
@@ -25453,12 +25448,14 @@
         <v>731</v>
       </c>
       <c r="B634" s="3">
-        <v>1919950</v>
+        <v>172000</v>
       </c>
       <c r="C634" s="2"/>
-      <c r="D634" s="2"/>
+      <c r="D634" s="2">
+        <v>1</v>
+      </c>
       <c r="E634" s="2">
-        <v>135.1</v>
+        <v>15.56</v>
       </c>
       <c r="F634" s="4">
         <f>B634/E634</f>
@@ -25484,12 +25481,16 @@
         <v>731</v>
       </c>
       <c r="B635" s="3">
-        <v>2269400</v>
-      </c>
-      <c r="C635" s="2"/>
-      <c r="D635" s="2"/>
+        <v>2790000</v>
+      </c>
+      <c r="C635" s="2">
+        <v>3</v>
+      </c>
+      <c r="D635" s="2">
+        <v>1</v>
+      </c>
       <c r="E635" s="2">
-        <v>160.6</v>
+        <v>160.32</v>
       </c>
       <c r="F635" s="4">
         <f>B635/E635</f>
@@ -25515,12 +25516,16 @@
         <v>731</v>
       </c>
       <c r="B636" s="3">
-        <v>2328550</v>
-      </c>
-      <c r="C636" s="2"/>
-      <c r="D636" s="2"/>
+        <v>470000</v>
+      </c>
+      <c r="C636" s="2">
+        <v>1</v>
+      </c>
+      <c r="D636" s="2">
+        <v>1</v>
+      </c>
       <c r="E636" s="2">
-        <v>158</v>
+        <v>40.48</v>
       </c>
       <c r="F636" s="4">
         <f>B636/E636</f>
@@ -25529,7 +25534,7 @@
         <v>109</v>
       </c>
       <c r="H636" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="I636" s="2" t="s">
         <v>13</v>
@@ -25546,16 +25551,12 @@
         <v>731</v>
       </c>
       <c r="B637" s="3">
-        <v>1275000</v>
-      </c>
-      <c r="C637" s="2">
-        <v>3</v>
-      </c>
-      <c r="D637" s="2">
-        <v>1</v>
-      </c>
+        <v>2526150</v>
+      </c>
+      <c r="C637" s="2"/>
+      <c r="D637" s="2"/>
       <c r="E637" s="2">
-        <v>109.85</v>
+        <v>169</v>
       </c>
       <c r="F637" s="4">
         <f>B637/E637</f>
@@ -25581,34 +25582,34 @@
         <v>731</v>
       </c>
       <c r="B638" s="3">
-        <v>1750000</v>
+        <v>2400000</v>
       </c>
       <c r="C638" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D638" s="2">
         <v>1</v>
       </c>
       <c r="E638" s="2">
-        <v>159.85</v>
+        <v>243.61</v>
       </c>
       <c r="F638" s="4">
         <f>B638/E638</f>
       </c>
       <c r="G638" s="2" t="s">
-        <v>109</v>
+        <v>804</v>
       </c>
       <c r="H638" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="I638" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="J638" s="2" t="s">
         <v>14</v>
       </c>
       <c r="K638" s="2" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="639" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25616,25 +25617,25 @@
         <v>731</v>
       </c>
       <c r="B639" s="3">
-        <v>798000</v>
+        <v>1350000</v>
       </c>
       <c r="C639" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D639" s="2">
         <v>1</v>
       </c>
       <c r="E639" s="2">
-        <v>73.88</v>
+        <v>170</v>
       </c>
       <c r="F639" s="4">
         <f>B639/E639</f>
       </c>
       <c r="G639" s="2" t="s">
-        <v>109</v>
+        <v>806</v>
       </c>
       <c r="H639" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="I639" s="2" t="s">
         <v>13</v>
@@ -25643,7 +25644,7 @@
         <v>14</v>
       </c>
       <c r="K639" s="2" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
     </row>
     <row r="640" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25651,34 +25652,34 @@
         <v>731</v>
       </c>
       <c r="B640" s="3">
-        <v>639000</v>
+        <v>1300000</v>
       </c>
       <c r="C640" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D640" s="2">
         <v>1</v>
       </c>
       <c r="E640" s="2">
-        <v>70.51</v>
+        <v>181.93</v>
       </c>
       <c r="F640" s="4">
         <f>B640/E640</f>
       </c>
       <c r="G640" s="2" t="s">
-        <v>109</v>
+        <v>806</v>
       </c>
       <c r="H640" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="I640" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="J640" s="2" t="s">
         <v>14</v>
       </c>
       <c r="K640" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="641" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25686,22 +25687,22 @@
         <v>731</v>
       </c>
       <c r="B641" s="3">
-        <v>289000</v>
+        <v>780000</v>
       </c>
       <c r="C641" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D641" s="2">
         <v>1</v>
       </c>
       <c r="E641" s="2">
-        <v>31.86</v>
+        <v>130.94</v>
       </c>
       <c r="F641" s="4">
         <f>B641/E641</f>
       </c>
       <c r="G641" s="2" t="s">
-        <v>109</v>
+        <v>806</v>
       </c>
       <c r="H641" s="2" t="s">
         <v>13</v>
@@ -25713,7 +25714,7 @@
         <v>14</v>
       </c>
       <c r="K641" s="2" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
     </row>
     <row r="642" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25721,30 +25722,34 @@
         <v>731</v>
       </c>
       <c r="B642" s="3">
-        <v>2533950</v>
-      </c>
-      <c r="C642" s="2"/>
-      <c r="D642" s="2"/>
+        <v>990000</v>
+      </c>
+      <c r="C642" s="2">
+        <v>4</v>
+      </c>
+      <c r="D642" s="2">
+        <v>1</v>
+      </c>
       <c r="E642" s="2">
-        <v>171</v>
+        <v>130.24</v>
       </c>
       <c r="F642" s="4">
         <f>B642/E642</f>
       </c>
       <c r="G642" s="2" t="s">
-        <v>109</v>
+        <v>806</v>
       </c>
       <c r="H642" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="I642" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="J642" s="2" t="s">
         <v>14</v>
       </c>
       <c r="K642" s="2" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
     </row>
     <row r="643" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25752,23 +25757,25 @@
         <v>731</v>
       </c>
       <c r="B643" s="3">
-        <v>2404300</v>
-      </c>
-      <c r="C643" s="2"/>
+        <v>985000</v>
+      </c>
+      <c r="C643" s="2">
+        <v>3</v>
+      </c>
       <c r="D643" s="2">
         <v>1</v>
       </c>
       <c r="E643" s="2">
-        <v>170.7</v>
+        <v>141.58</v>
       </c>
       <c r="F643" s="4">
         <f>B643/E643</f>
       </c>
       <c r="G643" s="2" t="s">
-        <v>109</v>
+        <v>806</v>
       </c>
       <c r="H643" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="I643" s="2" t="s">
         <v>13</v>
@@ -25777,7 +25784,7 @@
         <v>14</v>
       </c>
       <c r="K643" s="2" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
     </row>
     <row r="644" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25785,23 +25792,25 @@
         <v>731</v>
       </c>
       <c r="B644" s="3">
-        <v>172000</v>
-      </c>
-      <c r="C644" s="2"/>
+        <v>875000</v>
+      </c>
+      <c r="C644" s="2">
+        <v>4</v>
+      </c>
       <c r="D644" s="2">
         <v>1</v>
       </c>
       <c r="E644" s="2">
-        <v>15.56</v>
+        <v>109.85</v>
       </c>
       <c r="F644" s="4">
         <f>B644/E644</f>
       </c>
       <c r="G644" s="2" t="s">
-        <v>109</v>
+        <v>806</v>
       </c>
       <c r="H644" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="I644" s="2" t="s">
         <v>13</v>
@@ -25810,7 +25819,7 @@
         <v>14</v>
       </c>
       <c r="K644" s="2" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
     </row>
     <row r="645" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25818,25 +25827,25 @@
         <v>731</v>
       </c>
       <c r="B645" s="3">
-        <v>2790000</v>
+        <v>650000</v>
       </c>
       <c r="C645" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D645" s="2">
         <v>1</v>
       </c>
       <c r="E645" s="2">
-        <v>160.32</v>
+        <v>153.4</v>
       </c>
       <c r="F645" s="4">
         <f>B645/E645</f>
       </c>
       <c r="G645" s="2" t="s">
-        <v>109</v>
+        <v>806</v>
       </c>
       <c r="H645" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="I645" s="2" t="s">
         <v>13</v>
@@ -25845,7 +25854,7 @@
         <v>14</v>
       </c>
       <c r="K645" s="2" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
     </row>
     <row r="646" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25853,22 +25862,22 @@
         <v>731</v>
       </c>
       <c r="B646" s="3">
-        <v>470000</v>
+        <v>740000</v>
       </c>
       <c r="C646" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D646" s="2">
         <v>1</v>
       </c>
       <c r="E646" s="2">
-        <v>40.48</v>
+        <v>118.44</v>
       </c>
       <c r="F646" s="4">
         <f>B646/E646</f>
       </c>
       <c r="G646" s="2" t="s">
-        <v>109</v>
+        <v>806</v>
       </c>
       <c r="H646" s="2" t="s">
         <v>13</v>
@@ -25880,7 +25889,7 @@
         <v>14</v>
       </c>
       <c r="K646" s="2" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
     </row>
     <row r="647" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25888,30 +25897,34 @@
         <v>731</v>
       </c>
       <c r="B647" s="3">
-        <v>2526150</v>
-      </c>
-      <c r="C647" s="2"/>
-      <c r="D647" s="2"/>
+        <v>1350000</v>
+      </c>
+      <c r="C647" s="2">
+        <v>5</v>
+      </c>
+      <c r="D647" s="2">
+        <v>1</v>
+      </c>
       <c r="E647" s="2">
-        <v>169</v>
+        <v>258.62</v>
       </c>
       <c r="F647" s="4">
         <f>B647/E647</f>
       </c>
       <c r="G647" s="2" t="s">
-        <v>109</v>
+        <v>806</v>
       </c>
       <c r="H647" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="I647" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="J647" s="2" t="s">
         <v>14</v>
       </c>
       <c r="K647" s="2" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
     </row>
     <row r="648" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25919,22 +25932,22 @@
         <v>731</v>
       </c>
       <c r="B648" s="3">
-        <v>2400000</v>
+        <v>1195000</v>
       </c>
       <c r="C648" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D648" s="2">
         <v>1</v>
       </c>
       <c r="E648" s="2">
-        <v>243.61</v>
+        <v>193.27</v>
       </c>
       <c r="F648" s="4">
         <f>B648/E648</f>
       </c>
       <c r="G648" s="2" t="s">
-        <v>814</v>
+        <v>806</v>
       </c>
       <c r="H648" s="2" t="s">
         <v>13</v>
@@ -25946,7 +25959,7 @@
         <v>14</v>
       </c>
       <c r="K648" s="2" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="649" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25954,7 +25967,7 @@
         <v>731</v>
       </c>
       <c r="B649" s="3">
-        <v>1350000</v>
+        <v>1150000</v>
       </c>
       <c r="C649" s="2">
         <v>4</v>
@@ -25963,13 +25976,13 @@
         <v>1</v>
       </c>
       <c r="E649" s="2">
-        <v>170</v>
+        <v>117.15</v>
       </c>
       <c r="F649" s="4">
         <f>B649/E649</f>
       </c>
       <c r="G649" s="2" t="s">
-        <v>816</v>
+        <v>806</v>
       </c>
       <c r="H649" s="2" t="s">
         <v>13</v>
@@ -25989,25 +26002,25 @@
         <v>731</v>
       </c>
       <c r="B650" s="3">
-        <v>1300000</v>
+        <v>995000</v>
       </c>
       <c r="C650" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D650" s="2">
         <v>1</v>
       </c>
       <c r="E650" s="2">
-        <v>181.93</v>
+        <v>109.07</v>
       </c>
       <c r="F650" s="4">
         <f>B650/E650</f>
       </c>
       <c r="G650" s="2" t="s">
-        <v>816</v>
+        <v>806</v>
       </c>
       <c r="H650" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="I650" s="2" t="s">
         <v>13</v>
@@ -26024,7 +26037,7 @@
         <v>731</v>
       </c>
       <c r="B651" s="3">
-        <v>780000</v>
+        <v>1090000</v>
       </c>
       <c r="C651" s="2">
         <v>4</v>
@@ -26033,16 +26046,16 @@
         <v>1</v>
       </c>
       <c r="E651" s="2">
-        <v>130.94</v>
+        <v>138.13</v>
       </c>
       <c r="F651" s="4">
         <f>B651/E651</f>
       </c>
       <c r="G651" s="2" t="s">
-        <v>816</v>
+        <v>806</v>
       </c>
       <c r="H651" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="I651" s="2" t="s">
         <v>13</v>
@@ -26059,22 +26072,22 @@
         <v>731</v>
       </c>
       <c r="B652" s="3">
-        <v>990000</v>
+        <v>1100000</v>
       </c>
       <c r="C652" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D652" s="2">
         <v>1</v>
       </c>
       <c r="E652" s="2">
-        <v>130.24</v>
+        <v>183</v>
       </c>
       <c r="F652" s="4">
         <f>B652/E652</f>
       </c>
       <c r="G652" s="2" t="s">
-        <v>816</v>
+        <v>806</v>
       </c>
       <c r="H652" s="2" t="s">
         <v>13</v>
@@ -26094,28 +26107,28 @@
         <v>731</v>
       </c>
       <c r="B653" s="3">
-        <v>985000</v>
+        <v>650000</v>
       </c>
       <c r="C653" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D653" s="2">
         <v>1</v>
       </c>
       <c r="E653" s="2">
-        <v>141.58</v>
+        <v>86.77</v>
       </c>
       <c r="F653" s="4">
         <f>B653/E653</f>
       </c>
       <c r="G653" s="2" t="s">
-        <v>816</v>
+        <v>806</v>
       </c>
       <c r="H653" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="I653" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="J653" s="2" t="s">
         <v>14</v>
@@ -26129,25 +26142,25 @@
         <v>731</v>
       </c>
       <c r="B654" s="3">
-        <v>875000</v>
+        <v>375000</v>
       </c>
       <c r="C654" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D654" s="2">
         <v>1</v>
       </c>
       <c r="E654" s="2">
-        <v>109.85</v>
+        <v>53.33</v>
       </c>
       <c r="F654" s="4">
         <f>B654/E654</f>
       </c>
       <c r="G654" s="2" t="s">
-        <v>816</v>
+        <v>806</v>
       </c>
       <c r="H654" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="I654" s="2" t="s">
         <v>13</v>
@@ -26164,7 +26177,7 @@
         <v>731</v>
       </c>
       <c r="B655" s="3">
-        <v>650000</v>
+        <v>1190000</v>
       </c>
       <c r="C655" s="2">
         <v>5</v>
@@ -26173,13 +26186,13 @@
         <v>1</v>
       </c>
       <c r="E655" s="2">
-        <v>153.4</v>
+        <v>247</v>
       </c>
       <c r="F655" s="4">
         <f>B655/E655</f>
       </c>
       <c r="G655" s="2" t="s">
-        <v>816</v>
+        <v>806</v>
       </c>
       <c r="H655" s="2" t="s">
         <v>13</v>
@@ -26199,28 +26212,28 @@
         <v>731</v>
       </c>
       <c r="B656" s="3">
-        <v>740000</v>
+        <v>385000</v>
       </c>
       <c r="C656" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D656" s="2">
         <v>1</v>
       </c>
       <c r="E656" s="2">
-        <v>118.44</v>
+        <v>76.56</v>
       </c>
       <c r="F656" s="4">
         <f>B656/E656</f>
       </c>
       <c r="G656" s="2" t="s">
-        <v>816</v>
+        <v>806</v>
       </c>
       <c r="H656" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I656" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="J656" s="2" t="s">
         <v>14</v>
@@ -26234,22 +26247,22 @@
         <v>731</v>
       </c>
       <c r="B657" s="3">
-        <v>1350000</v>
+        <v>1260000</v>
       </c>
       <c r="C657" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D657" s="2">
         <v>1</v>
       </c>
       <c r="E657" s="2">
-        <v>258.62</v>
+        <v>168</v>
       </c>
       <c r="F657" s="4">
         <f>B657/E657</f>
       </c>
       <c r="G657" s="2" t="s">
-        <v>816</v>
+        <v>806</v>
       </c>
       <c r="H657" s="2" t="s">
         <v>13</v>
@@ -26269,22 +26282,22 @@
         <v>731</v>
       </c>
       <c r="B658" s="3">
-        <v>1195000</v>
+        <v>1180000</v>
       </c>
       <c r="C658" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D658" s="2">
         <v>1</v>
       </c>
       <c r="E658" s="2">
-        <v>193.27</v>
+        <v>228</v>
       </c>
       <c r="F658" s="4">
         <f>B658/E658</f>
       </c>
       <c r="G658" s="2" t="s">
-        <v>816</v>
+        <v>806</v>
       </c>
       <c r="H658" s="2" t="s">
         <v>13</v>
@@ -26304,28 +26317,28 @@
         <v>731</v>
       </c>
       <c r="B659" s="3">
-        <v>1150000</v>
+        <v>330000</v>
       </c>
       <c r="C659" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D659" s="2">
         <v>1</v>
       </c>
       <c r="E659" s="2">
-        <v>117.15</v>
+        <v>57.74</v>
       </c>
       <c r="F659" s="4">
         <f>B659/E659</f>
       </c>
       <c r="G659" s="2" t="s">
-        <v>816</v>
+        <v>806</v>
       </c>
       <c r="H659" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="I659" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="J659" s="2" t="s">
         <v>14</v>
@@ -26339,25 +26352,25 @@
         <v>731</v>
       </c>
       <c r="B660" s="3">
-        <v>995000</v>
+        <v>600000</v>
       </c>
       <c r="C660" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D660" s="2">
         <v>1</v>
       </c>
       <c r="E660" s="2">
-        <v>109.07</v>
+        <v>90.46</v>
       </c>
       <c r="F660" s="4">
         <f>B660/E660</f>
       </c>
       <c r="G660" s="2" t="s">
-        <v>816</v>
+        <v>806</v>
       </c>
       <c r="H660" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="I660" s="2" t="s">
         <v>13</v>
@@ -26374,28 +26387,28 @@
         <v>731</v>
       </c>
       <c r="B661" s="3">
-        <v>1090000</v>
+        <v>395000</v>
       </c>
       <c r="C661" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D661" s="2">
         <v>1</v>
       </c>
       <c r="E661" s="2">
-        <v>138.13</v>
+        <v>42.95</v>
       </c>
       <c r="F661" s="4">
         <f>B661/E661</f>
       </c>
       <c r="G661" s="2" t="s">
-        <v>816</v>
+        <v>12</v>
       </c>
       <c r="H661" s="2" t="s">
         <v>214</v>
       </c>
       <c r="I661" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="J661" s="2" t="s">
         <v>14</v>
@@ -26409,22 +26422,22 @@
         <v>731</v>
       </c>
       <c r="B662" s="3">
-        <v>1100000</v>
+        <v>2700000</v>
       </c>
       <c r="C662" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D662" s="2">
         <v>1</v>
       </c>
       <c r="E662" s="2">
-        <v>183</v>
+        <v>250</v>
       </c>
       <c r="F662" s="4">
         <f>B662/E662</f>
       </c>
       <c r="G662" s="2" t="s">
-        <v>816</v>
+        <v>12</v>
       </c>
       <c r="H662" s="2" t="s">
         <v>13</v>
@@ -26444,28 +26457,26 @@
         <v>731</v>
       </c>
       <c r="B663" s="3">
-        <v>650000</v>
+        <v>120000</v>
       </c>
       <c r="C663" s="2">
-        <v>2</v>
-      </c>
-      <c r="D663" s="2">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D663" s="2"/>
       <c r="E663" s="2">
-        <v>86.77</v>
+        <v>9.56</v>
       </c>
       <c r="F663" s="4">
         <f>B663/E663</f>
       </c>
       <c r="G663" s="2" t="s">
-        <v>816</v>
+        <v>12</v>
       </c>
       <c r="H663" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="I663" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="J663" s="2" t="s">
         <v>14</v>
@@ -26479,7 +26490,7 @@
         <v>731</v>
       </c>
       <c r="B664" s="3">
-        <v>375000</v>
+        <v>455000</v>
       </c>
       <c r="C664" s="2">
         <v>1</v>
@@ -26488,13 +26499,13 @@
         <v>1</v>
       </c>
       <c r="E664" s="2">
-        <v>53.33</v>
+        <v>41.51</v>
       </c>
       <c r="F664" s="4">
         <f>B664/E664</f>
       </c>
       <c r="G664" s="2" t="s">
-        <v>816</v>
+        <v>12</v>
       </c>
       <c r="H664" s="2" t="s">
         <v>214</v>
@@ -26514,25 +26525,25 @@
         <v>731</v>
       </c>
       <c r="B665" s="3">
-        <v>1190000</v>
+        <v>569000</v>
       </c>
       <c r="C665" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D665" s="2">
         <v>1</v>
       </c>
       <c r="E665" s="2">
-        <v>247</v>
+        <v>53.14</v>
       </c>
       <c r="F665" s="4">
         <f>B665/E665</f>
       </c>
       <c r="G665" s="2" t="s">
-        <v>816</v>
+        <v>12</v>
       </c>
       <c r="H665" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="I665" s="2" t="s">
         <v>13</v>
@@ -26549,7 +26560,7 @@
         <v>731</v>
       </c>
       <c r="B666" s="3">
-        <v>385000</v>
+        <v>2950000</v>
       </c>
       <c r="C666" s="2">
         <v>3</v>
@@ -26558,19 +26569,19 @@
         <v>1</v>
       </c>
       <c r="E666" s="2">
-        <v>76.56</v>
+        <v>191.04</v>
       </c>
       <c r="F666" s="4">
         <f>B666/E666</f>
       </c>
       <c r="G666" s="2" t="s">
-        <v>816</v>
+        <v>12</v>
       </c>
       <c r="H666" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I666" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="J666" s="2" t="s">
         <v>14</v>
@@ -26584,25 +26595,25 @@
         <v>731</v>
       </c>
       <c r="B667" s="3">
-        <v>1260000</v>
+        <v>1790000</v>
       </c>
       <c r="C667" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D667" s="2">
         <v>1</v>
       </c>
       <c r="E667" s="2">
-        <v>168</v>
+        <v>91.08</v>
       </c>
       <c r="F667" s="4">
         <f>B667/E667</f>
       </c>
       <c r="G667" s="2" t="s">
-        <v>816</v>
+        <v>12</v>
       </c>
       <c r="H667" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="I667" s="2" t="s">
         <v>13</v>
@@ -26619,22 +26630,22 @@
         <v>731</v>
       </c>
       <c r="B668" s="3">
-        <v>1180000</v>
+        <v>950000</v>
       </c>
       <c r="C668" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D668" s="2">
         <v>1</v>
       </c>
       <c r="E668" s="2">
-        <v>228</v>
+        <v>114.21</v>
       </c>
       <c r="F668" s="4">
         <f>B668/E668</f>
       </c>
       <c r="G668" s="2" t="s">
-        <v>816</v>
+        <v>115</v>
       </c>
       <c r="H668" s="2" t="s">
         <v>13</v>
@@ -26654,28 +26665,28 @@
         <v>731</v>
       </c>
       <c r="B669" s="3">
-        <v>330000</v>
+        <v>550000</v>
       </c>
       <c r="C669" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D669" s="2">
         <v>1</v>
       </c>
       <c r="E669" s="2">
-        <v>57.74</v>
+        <v>83.1</v>
       </c>
       <c r="F669" s="4">
         <f>B669/E669</f>
       </c>
       <c r="G669" s="2" t="s">
-        <v>816</v>
+        <v>115</v>
       </c>
       <c r="H669" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="I669" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="J669" s="2" t="s">
         <v>14</v>
@@ -26689,7 +26700,7 @@
         <v>731</v>
       </c>
       <c r="B670" s="3">
-        <v>600000</v>
+        <v>630000</v>
       </c>
       <c r="C670" s="2">
         <v>3</v>
@@ -26698,19 +26709,19 @@
         <v>1</v>
       </c>
       <c r="E670" s="2">
-        <v>90.46</v>
+        <v>89.66</v>
       </c>
       <c r="F670" s="4">
         <f>B670/E670</f>
       </c>
       <c r="G670" s="2" t="s">
-        <v>816</v>
+        <v>115</v>
       </c>
       <c r="H670" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="I670" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="J670" s="2" t="s">
         <v>14</v>
@@ -26724,28 +26735,28 @@
         <v>731</v>
       </c>
       <c r="B671" s="3">
-        <v>395000</v>
+        <v>675000</v>
       </c>
       <c r="C671" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D671" s="2">
         <v>1</v>
       </c>
       <c r="E671" s="2">
-        <v>42.95</v>
+        <v>75</v>
       </c>
       <c r="F671" s="4">
         <f>B671/E671</f>
       </c>
       <c r="G671" s="2" t="s">
-        <v>12</v>
+        <v>115</v>
       </c>
       <c r="H671" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="I671" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="J671" s="2" t="s">
         <v>14</v>
@@ -26759,22 +26770,22 @@
         <v>731</v>
       </c>
       <c r="B672" s="3">
-        <v>2700000</v>
+        <v>1250000</v>
       </c>
       <c r="C672" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D672" s="2">
         <v>1</v>
       </c>
       <c r="E672" s="2">
-        <v>250</v>
+        <v>184</v>
       </c>
       <c r="F672" s="4">
         <f>B672/E672</f>
       </c>
       <c r="G672" s="2" t="s">
-        <v>12</v>
+        <v>115</v>
       </c>
       <c r="H672" s="2" t="s">
         <v>13</v>
@@ -26794,20 +26805,22 @@
         <v>731</v>
       </c>
       <c r="B673" s="3">
-        <v>120000</v>
+        <v>845000</v>
       </c>
       <c r="C673" s="2">
-        <v>1</v>
-      </c>
-      <c r="D673" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="D673" s="2">
+        <v>1</v>
+      </c>
       <c r="E673" s="2">
-        <v>9.56</v>
+        <v>98.06</v>
       </c>
       <c r="F673" s="4">
         <f>B673/E673</f>
       </c>
       <c r="G673" s="2" t="s">
-        <v>12</v>
+        <v>115</v>
       </c>
       <c r="H673" s="2" t="s">
         <v>13</v>
@@ -26827,25 +26840,25 @@
         <v>731</v>
       </c>
       <c r="B674" s="3">
-        <v>455000</v>
+        <v>1150000</v>
       </c>
       <c r="C674" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D674" s="2">
         <v>1</v>
       </c>
       <c r="E674" s="2">
-        <v>41.51</v>
+        <v>170.15</v>
       </c>
       <c r="F674" s="4">
         <f>B674/E674</f>
       </c>
       <c r="G674" s="2" t="s">
-        <v>12</v>
+        <v>115</v>
       </c>
       <c r="H674" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="I674" s="2" t="s">
         <v>13</v>
@@ -26862,25 +26875,25 @@
         <v>731</v>
       </c>
       <c r="B675" s="3">
-        <v>569000</v>
+        <v>1750000</v>
       </c>
       <c r="C675" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D675" s="2">
         <v>1</v>
       </c>
       <c r="E675" s="2">
-        <v>53.14</v>
+        <v>233</v>
       </c>
       <c r="F675" s="4">
         <f>B675/E675</f>
       </c>
       <c r="G675" s="2" t="s">
-        <v>12</v>
+        <v>115</v>
       </c>
       <c r="H675" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="I675" s="2" t="s">
         <v>13</v>
@@ -26897,28 +26910,28 @@
         <v>731</v>
       </c>
       <c r="B676" s="3">
-        <v>2950000</v>
+        <v>950000</v>
       </c>
       <c r="C676" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D676" s="2">
         <v>1</v>
       </c>
       <c r="E676" s="2">
-        <v>191.04</v>
+        <v>114.21</v>
       </c>
       <c r="F676" s="4">
         <f>B676/E676</f>
       </c>
       <c r="G676" s="2" t="s">
-        <v>12</v>
+        <v>115</v>
       </c>
       <c r="H676" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="I676" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="J676" s="2" t="s">
         <v>14</v>
@@ -26932,25 +26945,25 @@
         <v>731</v>
       </c>
       <c r="B677" s="3">
-        <v>1790000</v>
+        <v>1295000</v>
       </c>
       <c r="C677" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D677" s="2">
         <v>1</v>
       </c>
       <c r="E677" s="2">
-        <v>91.08</v>
+        <v>204.51</v>
       </c>
       <c r="F677" s="4">
         <f>B677/E677</f>
       </c>
       <c r="G677" s="2" t="s">
-        <v>12</v>
+        <v>115</v>
       </c>
       <c r="H677" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="I677" s="2" t="s">
         <v>13</v>
@@ -26967,16 +26980,16 @@
         <v>731</v>
       </c>
       <c r="B678" s="3">
-        <v>950000</v>
+        <v>562500</v>
       </c>
       <c r="C678" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D678" s="2">
         <v>1</v>
       </c>
       <c r="E678" s="2">
-        <v>114.21</v>
+        <v>93.39</v>
       </c>
       <c r="F678" s="4">
         <f>B678/E678</f>
@@ -26985,7 +26998,7 @@
         <v>115</v>
       </c>
       <c r="H678" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="I678" s="2" t="s">
         <v>13</v>
@@ -27002,16 +27015,16 @@
         <v>731</v>
       </c>
       <c r="B679" s="3">
-        <v>550000</v>
+        <v>3500000</v>
       </c>
       <c r="C679" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D679" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E679" s="2">
-        <v>83.1</v>
+        <v>586.44</v>
       </c>
       <c r="F679" s="4">
         <f>B679/E679</f>
@@ -27037,16 +27050,16 @@
         <v>731</v>
       </c>
       <c r="B680" s="3">
-        <v>630000</v>
+        <v>645000</v>
       </c>
       <c r="C680" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D680" s="2">
         <v>1</v>
       </c>
       <c r="E680" s="2">
-        <v>89.66</v>
+        <v>117.73</v>
       </c>
       <c r="F680" s="4">
         <f>B680/E680</f>
@@ -27055,7 +27068,7 @@
         <v>115</v>
       </c>
       <c r="H680" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="I680" s="2" t="s">
         <v>214</v>
@@ -27072,16 +27085,16 @@
         <v>731</v>
       </c>
       <c r="B681" s="3">
-        <v>675000</v>
+        <v>3980000</v>
       </c>
       <c r="C681" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D681" s="2">
         <v>1</v>
       </c>
       <c r="E681" s="2">
-        <v>75</v>
+        <v>486</v>
       </c>
       <c r="F681" s="4">
         <f>B681/E681</f>
@@ -27107,16 +27120,16 @@
         <v>731</v>
       </c>
       <c r="B682" s="3">
-        <v>1250000</v>
+        <v>575000</v>
       </c>
       <c r="C682" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D682" s="2">
         <v>1</v>
       </c>
       <c r="E682" s="2">
-        <v>184</v>
+        <v>53.95</v>
       </c>
       <c r="F682" s="4">
         <f>B682/E682</f>
@@ -27142,7 +27155,7 @@
         <v>731</v>
       </c>
       <c r="B683" s="3">
-        <v>845000</v>
+        <v>1290000</v>
       </c>
       <c r="C683" s="2">
         <v>3</v>
@@ -27151,7 +27164,7 @@
         <v>1</v>
       </c>
       <c r="E683" s="2">
-        <v>98.06</v>
+        <v>157</v>
       </c>
       <c r="F683" s="4">
         <f>B683/E683</f>
@@ -27177,16 +27190,16 @@
         <v>731</v>
       </c>
       <c r="B684" s="3">
-        <v>1150000</v>
+        <v>1250000</v>
       </c>
       <c r="C684" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D684" s="2">
         <v>1</v>
       </c>
       <c r="E684" s="2">
-        <v>170.15</v>
+        <v>138</v>
       </c>
       <c r="F684" s="4">
         <f>B684/E684</f>
@@ -27212,28 +27225,28 @@
         <v>731</v>
       </c>
       <c r="B685" s="3">
-        <v>950000</v>
+        <v>390000</v>
       </c>
       <c r="C685" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D685" s="2">
         <v>1</v>
       </c>
       <c r="E685" s="2">
-        <v>114.21</v>
+        <v>48.26</v>
       </c>
       <c r="F685" s="4">
         <f>B685/E685</f>
       </c>
       <c r="G685" s="2" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="H685" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="I685" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="J685" s="2" t="s">
         <v>14</v>
@@ -27247,22 +27260,18 @@
         <v>731</v>
       </c>
       <c r="B686" s="3">
-        <v>1295000</v>
-      </c>
-      <c r="C686" s="2">
-        <v>5</v>
-      </c>
-      <c r="D686" s="2">
-        <v>1</v>
-      </c>
+        <v>1570000</v>
+      </c>
+      <c r="C686" s="2"/>
+      <c r="D686" s="2"/>
       <c r="E686" s="2">
-        <v>204.51</v>
+        <v>280.1</v>
       </c>
       <c r="F686" s="4">
         <f>B686/E686</f>
       </c>
       <c r="G686" s="2" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="H686" s="2" t="s">
         <v>13</v>
@@ -27282,25 +27291,25 @@
         <v>731</v>
       </c>
       <c r="B687" s="3">
-        <v>562500</v>
+        <v>1200000</v>
       </c>
       <c r="C687" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D687" s="2">
         <v>1</v>
       </c>
       <c r="E687" s="2">
-        <v>93.39</v>
+        <v>154.49</v>
       </c>
       <c r="F687" s="4">
         <f>B687/E687</f>
       </c>
       <c r="G687" s="2" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="H687" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="I687" s="2" t="s">
         <v>13</v>
@@ -27317,22 +27326,22 @@
         <v>731</v>
       </c>
       <c r="B688" s="3">
-        <v>3500000</v>
+        <v>2780000</v>
       </c>
       <c r="C688" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D688" s="2">
         <v>4</v>
       </c>
       <c r="E688" s="2">
-        <v>586.44</v>
+        <v>425.73</v>
       </c>
       <c r="F688" s="4">
         <f>B688/E688</f>
       </c>
       <c r="G688" s="2" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="H688" s="2" t="s">
         <v>13</v>
@@ -27352,22 +27361,22 @@
         <v>731</v>
       </c>
       <c r="B689" s="3">
-        <v>645000</v>
+        <v>2490000</v>
       </c>
       <c r="C689" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D689" s="2">
         <v>1</v>
       </c>
       <c r="E689" s="2">
-        <v>117.73</v>
+        <v>295</v>
       </c>
       <c r="F689" s="4">
         <f>B689/E689</f>
       </c>
       <c r="G689" s="2" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="H689" s="2" t="s">
         <v>13</v>
@@ -27387,7 +27396,7 @@
         <v>731</v>
       </c>
       <c r="B690" s="3">
-        <v>3980000</v>
+        <v>2690000</v>
       </c>
       <c r="C690" s="2">
         <v>5</v>
@@ -27396,13 +27405,13 @@
         <v>1</v>
       </c>
       <c r="E690" s="2">
-        <v>486</v>
+        <v>262.48</v>
       </c>
       <c r="F690" s="4">
         <f>B690/E690</f>
       </c>
       <c r="G690" s="2" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="H690" s="2" t="s">
         <v>13</v>
@@ -27422,22 +27431,22 @@
         <v>731</v>
       </c>
       <c r="B691" s="3">
-        <v>575000</v>
+        <v>3500000</v>
       </c>
       <c r="C691" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D691" s="2">
         <v>1</v>
       </c>
       <c r="E691" s="2">
-        <v>53.95</v>
+        <v>410</v>
       </c>
       <c r="F691" s="4">
         <f>B691/E691</f>
       </c>
       <c r="G691" s="2" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="H691" s="2" t="s">
         <v>13</v>
@@ -27457,22 +27466,22 @@
         <v>731</v>
       </c>
       <c r="B692" s="3">
-        <v>1290000</v>
+        <v>3900000</v>
       </c>
       <c r="C692" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D692" s="2">
         <v>1</v>
       </c>
       <c r="E692" s="2">
-        <v>157</v>
+        <v>473.78</v>
       </c>
       <c r="F692" s="4">
         <f>B692/E692</f>
       </c>
       <c r="G692" s="2" t="s">
-        <v>115</v>
+        <v>860</v>
       </c>
       <c r="H692" s="2" t="s">
         <v>13</v>
@@ -27484,7 +27493,7 @@
         <v>14</v>
       </c>
       <c r="K692" s="2" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
     </row>
     <row r="693" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27492,22 +27501,22 @@
         <v>731</v>
       </c>
       <c r="B693" s="3">
-        <v>1250000</v>
+        <v>1750000</v>
       </c>
       <c r="C693" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D693" s="2">
         <v>1</v>
       </c>
       <c r="E693" s="2">
-        <v>138</v>
+        <v>533</v>
       </c>
       <c r="F693" s="4">
         <f>B693/E693</f>
       </c>
       <c r="G693" s="2" t="s">
-        <v>115</v>
+        <v>860</v>
       </c>
       <c r="H693" s="2" t="s">
         <v>13</v>
@@ -27519,7 +27528,7 @@
         <v>14</v>
       </c>
       <c r="K693" s="2" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
     </row>
     <row r="694" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27527,7 +27536,7 @@
         <v>731</v>
       </c>
       <c r="B694" s="3">
-        <v>1200000</v>
+        <v>1295000</v>
       </c>
       <c r="C694" s="2">
         <v>5</v>
@@ -27536,13 +27545,13 @@
         <v>1</v>
       </c>
       <c r="E694" s="2">
-        <v>154.49</v>
+        <v>204.88</v>
       </c>
       <c r="F694" s="4">
         <f>B694/E694</f>
       </c>
       <c r="G694" s="2" t="s">
-        <v>136</v>
+        <v>860</v>
       </c>
       <c r="H694" s="2" t="s">
         <v>13</v>
@@ -27554,7 +27563,7 @@
         <v>14</v>
       </c>
       <c r="K694" s="2" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="695" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27562,25 +27571,25 @@
         <v>731</v>
       </c>
       <c r="B695" s="3">
-        <v>3500000</v>
+        <v>1080000</v>
       </c>
       <c r="C695" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D695" s="2">
         <v>1</v>
       </c>
       <c r="E695" s="2">
-        <v>410</v>
+        <v>77.59</v>
       </c>
       <c r="F695" s="4">
         <f>B695/E695</f>
       </c>
       <c r="G695" s="2" t="s">
-        <v>136</v>
+        <v>860</v>
       </c>
       <c r="H695" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="I695" s="2" t="s">
         <v>13</v>
@@ -27589,7 +27598,7 @@
         <v>14</v>
       </c>
       <c r="K695" s="2" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
     </row>
     <row r="696" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27597,25 +27606,25 @@
         <v>731</v>
       </c>
       <c r="B696" s="3">
-        <v>3900000</v>
+        <v>2120000</v>
       </c>
       <c r="C696" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D696" s="2">
         <v>1</v>
       </c>
       <c r="E696" s="2">
-        <v>473.78</v>
+        <v>86.23</v>
       </c>
       <c r="F696" s="4">
         <f>B696/E696</f>
       </c>
       <c r="G696" s="2" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="H696" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="I696" s="2" t="s">
         <v>13</v>
@@ -27632,22 +27641,22 @@
         <v>731</v>
       </c>
       <c r="B697" s="3">
-        <v>1750000</v>
+        <v>3500000</v>
       </c>
       <c r="C697" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D697" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E697" s="2">
-        <v>533</v>
+        <v>239.53</v>
       </c>
       <c r="F697" s="4">
         <f>B697/E697</f>
       </c>
       <c r="G697" s="2" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="H697" s="2" t="s">
         <v>13</v>
@@ -27667,25 +27676,25 @@
         <v>731</v>
       </c>
       <c r="B698" s="3">
-        <v>1295000</v>
+        <v>596500</v>
       </c>
       <c r="C698" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D698" s="2">
         <v>1</v>
       </c>
       <c r="E698" s="2">
-        <v>204.88</v>
+        <v>68.04</v>
       </c>
       <c r="F698" s="4">
         <f>B698/E698</f>
       </c>
       <c r="G698" s="2" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="H698" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="I698" s="2" t="s">
         <v>13</v>
@@ -27702,7 +27711,7 @@
         <v>731</v>
       </c>
       <c r="B699" s="3">
-        <v>1080000</v>
+        <v>1050000</v>
       </c>
       <c r="C699" s="2">
         <v>3</v>
@@ -27711,16 +27720,16 @@
         <v>1</v>
       </c>
       <c r="E699" s="2">
-        <v>77.59</v>
+        <v>99.17</v>
       </c>
       <c r="F699" s="4">
         <f>B699/E699</f>
       </c>
       <c r="G699" s="2" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="H699" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="I699" s="2" t="s">
         <v>13</v>
@@ -27737,25 +27746,23 @@
         <v>731</v>
       </c>
       <c r="B700" s="3">
-        <v>2120000</v>
+        <v>1295000</v>
       </c>
       <c r="C700" s="2">
-        <v>2</v>
-      </c>
-      <c r="D700" s="2">
-        <v>1</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="D700" s="2"/>
       <c r="E700" s="2">
-        <v>86.23</v>
+        <v>214.39</v>
       </c>
       <c r="F700" s="4">
         <f>B700/E700</f>
       </c>
       <c r="G700" s="2" t="s">
-        <v>864</v>
+        <v>97</v>
       </c>
       <c r="H700" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="I700" s="2" t="s">
         <v>13</v>
@@ -27772,25 +27779,25 @@
         <v>731</v>
       </c>
       <c r="B701" s="3">
-        <v>3500000</v>
+        <v>685000</v>
       </c>
       <c r="C701" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D701" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E701" s="2">
-        <v>239.53</v>
+        <v>62.02</v>
       </c>
       <c r="F701" s="4">
         <f>B701/E701</f>
       </c>
       <c r="G701" s="2" t="s">
-        <v>864</v>
+        <v>870</v>
       </c>
       <c r="H701" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="I701" s="2" t="s">
         <v>13</v>
@@ -27799,7 +27806,7 @@
         <v>14</v>
       </c>
       <c r="K701" s="2" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
     </row>
     <row r="702" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27807,22 +27814,22 @@
         <v>731</v>
       </c>
       <c r="B702" s="3">
-        <v>596500</v>
+        <v>428750</v>
       </c>
       <c r="C702" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D702" s="2">
         <v>1</v>
       </c>
       <c r="E702" s="2">
-        <v>68.04</v>
+        <v>30.93</v>
       </c>
       <c r="F702" s="4">
         <f>B702/E702</f>
       </c>
       <c r="G702" s="2" t="s">
-        <v>864</v>
+        <v>870</v>
       </c>
       <c r="H702" s="2" t="s">
         <v>214</v>
@@ -27834,7 +27841,7 @@
         <v>14</v>
       </c>
       <c r="K702" s="2" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
     </row>
     <row r="703" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27842,7 +27849,7 @@
         <v>731</v>
       </c>
       <c r="B703" s="3">
-        <v>1050000</v>
+        <v>1495000</v>
       </c>
       <c r="C703" s="2">
         <v>3</v>
@@ -27851,13 +27858,13 @@
         <v>1</v>
       </c>
       <c r="E703" s="2">
-        <v>99.17</v>
+        <v>96.13</v>
       </c>
       <c r="F703" s="4">
         <f>B703/E703</f>
       </c>
       <c r="G703" s="2" t="s">
-        <v>864</v>
+        <v>870</v>
       </c>
       <c r="H703" s="2" t="s">
         <v>13</v>
@@ -27869,7 +27876,7 @@
         <v>14</v>
       </c>
       <c r="K703" s="2" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
     </row>
     <row r="704" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27877,32 +27884,34 @@
         <v>731</v>
       </c>
       <c r="B704" s="3">
-        <v>1295000</v>
+        <v>1760000</v>
       </c>
       <c r="C704" s="2">
         <v>4</v>
       </c>
-      <c r="D704" s="2"/>
+      <c r="D704" s="2">
+        <v>1</v>
+      </c>
       <c r="E704" s="2">
-        <v>214.39</v>
+        <v>177.93</v>
       </c>
       <c r="F704" s="4">
         <f>B704/E704</f>
       </c>
       <c r="G704" s="2" t="s">
-        <v>97</v>
+        <v>870</v>
       </c>
       <c r="H704" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="I704" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="J704" s="2" t="s">
         <v>14</v>
       </c>
       <c r="K704" s="2" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
     </row>
     <row r="705" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27910,7 +27919,7 @@
         <v>731</v>
       </c>
       <c r="B705" s="3">
-        <v>685000</v>
+        <v>361900</v>
       </c>
       <c r="C705" s="2">
         <v>1</v>
@@ -27919,13 +27928,13 @@
         <v>1</v>
       </c>
       <c r="E705" s="2">
-        <v>62.02</v>
+        <v>30.31</v>
       </c>
       <c r="F705" s="4">
         <f>B705/E705</f>
       </c>
       <c r="G705" s="2" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="H705" s="2" t="s">
         <v>214</v>
@@ -27960,7 +27969,7 @@
         <f>B706/E706</f>
       </c>
       <c r="G706" s="2" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="H706" s="2" t="s">
         <v>214</v>
@@ -27980,25 +27989,25 @@
         <v>731</v>
       </c>
       <c r="B707" s="3">
-        <v>1495000</v>
+        <v>630000</v>
       </c>
       <c r="C707" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D707" s="2">
         <v>1</v>
       </c>
       <c r="E707" s="2">
-        <v>96.13</v>
+        <v>81.8</v>
       </c>
       <c r="F707" s="4">
         <f>B707/E707</f>
       </c>
       <c r="G707" s="2" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="H707" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="I707" s="2" t="s">
         <v>13</v>
@@ -28015,28 +28024,28 @@
         <v>731</v>
       </c>
       <c r="B708" s="3">
-        <v>1760000</v>
+        <v>410000</v>
       </c>
       <c r="C708" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D708" s="2">
         <v>1</v>
       </c>
       <c r="E708" s="2">
-        <v>177.93</v>
+        <v>34.88</v>
       </c>
       <c r="F708" s="4">
         <f>B708/E708</f>
       </c>
       <c r="G708" s="2" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="H708" s="2" t="s">
         <v>214</v>
       </c>
       <c r="I708" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="J708" s="2" t="s">
         <v>14</v>
@@ -28050,22 +28059,22 @@
         <v>731</v>
       </c>
       <c r="B709" s="3">
-        <v>361900</v>
+        <v>890000</v>
       </c>
       <c r="C709" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D709" s="2">
         <v>1</v>
       </c>
       <c r="E709" s="2">
-        <v>30.31</v>
+        <v>52.8</v>
       </c>
       <c r="F709" s="4">
         <f>B709/E709</f>
       </c>
       <c r="G709" s="2" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="H709" s="2" t="s">
         <v>214</v>
@@ -28085,22 +28094,22 @@
         <v>731</v>
       </c>
       <c r="B710" s="3">
-        <v>428750</v>
+        <v>1020000</v>
       </c>
       <c r="C710" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D710" s="2">
         <v>1</v>
       </c>
       <c r="E710" s="2">
-        <v>30.93</v>
+        <v>86.8</v>
       </c>
       <c r="F710" s="4">
         <f>B710/E710</f>
       </c>
       <c r="G710" s="2" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="H710" s="2" t="s">
         <v>214</v>
@@ -28120,22 +28129,22 @@
         <v>731</v>
       </c>
       <c r="B711" s="3">
-        <v>630000</v>
+        <v>845000</v>
       </c>
       <c r="C711" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D711" s="2">
         <v>1</v>
       </c>
       <c r="E711" s="2">
-        <v>81.8</v>
+        <v>50.9</v>
       </c>
       <c r="F711" s="4">
         <f>B711/E711</f>
       </c>
       <c r="G711" s="2" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="H711" s="2" t="s">
         <v>214</v>
@@ -28155,22 +28164,22 @@
         <v>731</v>
       </c>
       <c r="B712" s="3">
-        <v>410000</v>
+        <v>4680000</v>
       </c>
       <c r="C712" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D712" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E712" s="2">
-        <v>34.88</v>
+        <v>322.08</v>
       </c>
       <c r="F712" s="4">
         <f>B712/E712</f>
       </c>
       <c r="G712" s="2" t="s">
-        <v>874</v>
+        <v>195</v>
       </c>
       <c r="H712" s="2" t="s">
         <v>214</v>
@@ -28179,7 +28188,7 @@
         <v>13</v>
       </c>
       <c r="J712" s="2" t="s">
-        <v>14</v>
+        <v>214</v>
       </c>
       <c r="K712" s="2" t="s">
         <v>882</v>
@@ -28190,25 +28199,25 @@
         <v>731</v>
       </c>
       <c r="B713" s="3">
-        <v>890000</v>
+        <v>1320000</v>
       </c>
       <c r="C713" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D713" s="2">
         <v>1</v>
       </c>
       <c r="E713" s="2">
-        <v>52.8</v>
+        <v>169.3</v>
       </c>
       <c r="F713" s="4">
         <f>B713/E713</f>
       </c>
       <c r="G713" s="2" t="s">
-        <v>874</v>
+        <v>883</v>
       </c>
       <c r="H713" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="I713" s="2" t="s">
         <v>13</v>
@@ -28217,7 +28226,7 @@
         <v>14</v>
       </c>
       <c r="K713" s="2" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
     </row>
     <row r="714" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -28225,25 +28234,25 @@
         <v>731</v>
       </c>
       <c r="B714" s="3">
-        <v>1020000</v>
+        <v>1390000</v>
       </c>
       <c r="C714" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D714" s="2">
         <v>1</v>
       </c>
       <c r="E714" s="2">
-        <v>86.8</v>
+        <v>161.32</v>
       </c>
       <c r="F714" s="4">
         <f>B714/E714</f>
       </c>
       <c r="G714" s="2" t="s">
-        <v>874</v>
+        <v>883</v>
       </c>
       <c r="H714" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="I714" s="2" t="s">
         <v>13</v>
@@ -28252,7 +28261,7 @@
         <v>14</v>
       </c>
       <c r="K714" s="2" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
     </row>
     <row r="715" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -28260,25 +28269,25 @@
         <v>731</v>
       </c>
       <c r="B715" s="3">
-        <v>845000</v>
+        <v>2700000</v>
       </c>
       <c r="C715" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D715" s="2">
         <v>1</v>
       </c>
       <c r="E715" s="2">
-        <v>50.9</v>
+        <v>328.59</v>
       </c>
       <c r="F715" s="4">
         <f>B715/E715</f>
       </c>
       <c r="G715" s="2" t="s">
-        <v>874</v>
+        <v>883</v>
       </c>
       <c r="H715" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="I715" s="2" t="s">
         <v>13</v>
@@ -28287,7 +28296,7 @@
         <v>14</v>
       </c>
       <c r="K715" s="2" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
     </row>
     <row r="716" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -28295,22 +28304,22 @@
         <v>731</v>
       </c>
       <c r="B716" s="3">
-        <v>4680000</v>
+        <v>780000</v>
       </c>
       <c r="C716" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D716" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E716" s="2">
-        <v>322.08</v>
+        <v>120</v>
       </c>
       <c r="F716" s="4">
         <f>B716/E716</f>
       </c>
       <c r="G716" s="2" t="s">
-        <v>195</v>
+        <v>883</v>
       </c>
       <c r="H716" s="2" t="s">
         <v>214</v>
@@ -28319,10 +28328,10 @@
         <v>13</v>
       </c>
       <c r="J716" s="2" t="s">
-        <v>214</v>
+        <v>14</v>
       </c>
       <c r="K716" s="2" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
     </row>
     <row r="717" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -28330,22 +28339,22 @@
         <v>731</v>
       </c>
       <c r="B717" s="3">
-        <v>1320000</v>
+        <v>3290000</v>
       </c>
       <c r="C717" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D717" s="2">
         <v>1</v>
       </c>
       <c r="E717" s="2">
-        <v>169.3</v>
+        <v>430.3</v>
       </c>
       <c r="F717" s="4">
         <f>B717/E717</f>
       </c>
       <c r="G717" s="2" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="H717" s="2" t="s">
         <v>13</v>
@@ -28365,34 +28374,34 @@
         <v>731</v>
       </c>
       <c r="B718" s="3">
-        <v>1390000</v>
+        <v>650000</v>
       </c>
       <c r="C718" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D718" s="2">
         <v>1</v>
       </c>
       <c r="E718" s="2">
-        <v>161.32</v>
+        <v>120.96</v>
       </c>
       <c r="F718" s="4">
         <f>B718/E718</f>
       </c>
       <c r="G718" s="2" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="H718" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="I718" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="J718" s="2" t="s">
         <v>14</v>
       </c>
       <c r="K718" s="2" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
     </row>
     <row r="719" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -28400,25 +28409,23 @@
         <v>731</v>
       </c>
       <c r="B719" s="3">
-        <v>780000</v>
-      </c>
-      <c r="C719" s="2">
-        <v>2</v>
-      </c>
+        <v>1150000</v>
+      </c>
+      <c r="C719" s="2"/>
       <c r="D719" s="2">
         <v>1</v>
       </c>
       <c r="E719" s="2">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="F719" s="4">
         <f>B719/E719</f>
       </c>
       <c r="G719" s="2" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="H719" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="I719" s="2" t="s">
         <v>13</v>
@@ -28427,7 +28434,7 @@
         <v>14</v>
       </c>
       <c r="K719" s="2" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
     </row>
     <row r="720" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -28435,16 +28442,16 @@
         <v>731</v>
       </c>
       <c r="B720" s="3">
-        <v>650000</v>
+        <v>1240000</v>
       </c>
       <c r="C720" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D720" s="2">
         <v>1</v>
       </c>
       <c r="E720" s="2">
-        <v>120.96</v>
+        <v>156</v>
       </c>
       <c r="F720" s="4">
         <f>B720/E720</f>
@@ -28453,16 +28460,16 @@
         <v>891</v>
       </c>
       <c r="H720" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="I720" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="J720" s="2" t="s">
         <v>14</v>
       </c>
       <c r="K720" s="2" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
     </row>
     <row r="721" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -28470,20 +28477,22 @@
         <v>731</v>
       </c>
       <c r="B721" s="3">
-        <v>1150000</v>
-      </c>
-      <c r="C721" s="2"/>
+        <v>1770000</v>
+      </c>
+      <c r="C721" s="2">
+        <v>7</v>
+      </c>
       <c r="D721" s="2">
         <v>1</v>
       </c>
       <c r="E721" s="2">
-        <v>136</v>
+        <v>260</v>
       </c>
       <c r="F721" s="4">
         <f>B721/E721</f>
       </c>
       <c r="G721" s="2" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="H721" s="2" t="s">
         <v>13</v>
@@ -28503,22 +28512,22 @@
         <v>731</v>
       </c>
       <c r="B722" s="3">
-        <v>1240000</v>
+        <v>975000</v>
       </c>
       <c r="C722" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D722" s="2">
         <v>1</v>
       </c>
       <c r="E722" s="2">
-        <v>156</v>
+        <v>130</v>
       </c>
       <c r="F722" s="4">
         <f>B722/E722</f>
       </c>
       <c r="G722" s="2" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="H722" s="2" t="s">
         <v>13</v>
@@ -28538,22 +28547,20 @@
         <v>731</v>
       </c>
       <c r="B723" s="3">
-        <v>1770000</v>
+        <v>599000</v>
       </c>
       <c r="C723" s="2">
-        <v>7</v>
-      </c>
-      <c r="D723" s="2">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D723" s="2"/>
       <c r="E723" s="2">
-        <v>260</v>
+        <v>87</v>
       </c>
       <c r="F723" s="4">
         <f>B723/E723</f>
       </c>
       <c r="G723" s="2" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="H723" s="2" t="s">
         <v>13</v>
@@ -28573,22 +28580,22 @@
         <v>731</v>
       </c>
       <c r="B724" s="3">
-        <v>975000</v>
+        <v>1400000</v>
       </c>
       <c r="C724" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D724" s="2">
         <v>1</v>
       </c>
       <c r="E724" s="2">
-        <v>130</v>
+        <v>155.77</v>
       </c>
       <c r="F724" s="4">
         <f>B724/E724</f>
       </c>
       <c r="G724" s="2" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="H724" s="2" t="s">
         <v>13</v>
@@ -28608,20 +28615,22 @@
         <v>731</v>
       </c>
       <c r="B725" s="3">
-        <v>599000</v>
+        <v>1440000</v>
       </c>
       <c r="C725" s="2">
-        <v>2</v>
-      </c>
-      <c r="D725" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="D725" s="2">
+        <v>1</v>
+      </c>
       <c r="E725" s="2">
-        <v>87</v>
+        <v>212.62</v>
       </c>
       <c r="F725" s="4">
         <f>B725/E725</f>
       </c>
       <c r="G725" s="2" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="H725" s="2" t="s">
         <v>13</v>
@@ -28641,7 +28650,7 @@
         <v>731</v>
       </c>
       <c r="B726" s="3">
-        <v>1400000</v>
+        <v>7000000</v>
       </c>
       <c r="C726" s="2">
         <v>5</v>
@@ -28650,13 +28659,13 @@
         <v>1</v>
       </c>
       <c r="E726" s="2">
-        <v>155.77</v>
+        <v>552.83</v>
       </c>
       <c r="F726" s="4">
         <f>B726/E726</f>
       </c>
       <c r="G726" s="2" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="H726" s="2" t="s">
         <v>13</v>
@@ -28676,22 +28685,22 @@
         <v>731</v>
       </c>
       <c r="B727" s="3">
-        <v>1440000</v>
+        <v>2980000</v>
       </c>
       <c r="C727" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D727" s="2">
         <v>1</v>
       </c>
       <c r="E727" s="2">
-        <v>212.62</v>
+        <v>264</v>
       </c>
       <c r="F727" s="4">
         <f>B727/E727</f>
       </c>
       <c r="G727" s="2" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="H727" s="2" t="s">
         <v>13</v>
@@ -28711,22 +28720,22 @@
         <v>731</v>
       </c>
       <c r="B728" s="3">
-        <v>7000000</v>
+        <v>3450000</v>
       </c>
       <c r="C728" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D728" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E728" s="2">
-        <v>552.83</v>
+        <v>386.26</v>
       </c>
       <c r="F728" s="4">
         <f>B728/E728</f>
       </c>
       <c r="G728" s="2" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="H728" s="2" t="s">
         <v>13</v>
@@ -28746,22 +28755,22 @@
         <v>731</v>
       </c>
       <c r="B729" s="3">
-        <v>2980000</v>
+        <v>5000000</v>
       </c>
       <c r="C729" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D729" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E729" s="2">
-        <v>264</v>
+        <v>500</v>
       </c>
       <c r="F729" s="4">
         <f>B729/E729</f>
       </c>
       <c r="G729" s="2" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="H729" s="2" t="s">
         <v>13</v>
@@ -28781,22 +28790,22 @@
         <v>731</v>
       </c>
       <c r="B730" s="3">
-        <v>3450000</v>
+        <v>1150000</v>
       </c>
       <c r="C730" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D730" s="2">
         <v>3</v>
       </c>
       <c r="E730" s="2">
-        <v>386.26</v>
+        <v>154</v>
       </c>
       <c r="F730" s="4">
         <f>B730/E730</f>
       </c>
       <c r="G730" s="2" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="H730" s="2" t="s">
         <v>13</v>
@@ -28816,25 +28825,25 @@
         <v>731</v>
       </c>
       <c r="B731" s="3">
-        <v>5000000</v>
+        <v>1700000</v>
       </c>
       <c r="C731" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D731" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E731" s="2">
-        <v>500</v>
+        <v>133</v>
       </c>
       <c r="F731" s="4">
         <f>B731/E731</f>
       </c>
       <c r="G731" s="2" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="H731" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="I731" s="2" t="s">
         <v>13</v>
@@ -28851,22 +28860,22 @@
         <v>731</v>
       </c>
       <c r="B732" s="3">
-        <v>1150000</v>
+        <v>1155000</v>
       </c>
       <c r="C732" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D732" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E732" s="2">
-        <v>154</v>
+        <v>143.41</v>
       </c>
       <c r="F732" s="4">
         <f>B732/E732</f>
       </c>
       <c r="G732" s="2" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="H732" s="2" t="s">
         <v>13</v>
@@ -28886,25 +28895,25 @@
         <v>731</v>
       </c>
       <c r="B733" s="3">
-        <v>1700000</v>
+        <v>1975000</v>
       </c>
       <c r="C733" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D733" s="2">
         <v>1</v>
       </c>
       <c r="E733" s="2">
-        <v>133</v>
+        <v>168</v>
       </c>
       <c r="F733" s="4">
         <f>B733/E733</f>
       </c>
       <c r="G733" s="2" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="H733" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="I733" s="2" t="s">
         <v>13</v>
@@ -28921,22 +28930,22 @@
         <v>731</v>
       </c>
       <c r="B734" s="3">
-        <v>1155000</v>
+        <v>1400000</v>
       </c>
       <c r="C734" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D734" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E734" s="2">
-        <v>143.41</v>
+        <v>134</v>
       </c>
       <c r="F734" s="4">
         <f>B734/E734</f>
       </c>
       <c r="G734" s="2" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="H734" s="2" t="s">
         <v>13</v>
@@ -28956,7 +28965,7 @@
         <v>731</v>
       </c>
       <c r="B735" s="3">
-        <v>1975000</v>
+        <v>1850000</v>
       </c>
       <c r="C735" s="2">
         <v>5</v>
@@ -28965,13 +28974,13 @@
         <v>1</v>
       </c>
       <c r="E735" s="2">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="F735" s="4">
         <f>B735/E735</f>
       </c>
       <c r="G735" s="2" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="H735" s="2" t="s">
         <v>13</v>
@@ -28991,22 +29000,22 @@
         <v>731</v>
       </c>
       <c r="B736" s="3">
-        <v>1400000</v>
+        <v>1695000</v>
       </c>
       <c r="C736" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D736" s="2">
         <v>1</v>
       </c>
       <c r="E736" s="2">
-        <v>134</v>
+        <v>207</v>
       </c>
       <c r="F736" s="4">
         <f>B736/E736</f>
       </c>
       <c r="G736" s="2" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="H736" s="2" t="s">
         <v>13</v>
@@ -29026,34 +29035,34 @@
         <v>731</v>
       </c>
       <c r="B737" s="3">
-        <v>1440000</v>
+        <v>835000</v>
       </c>
       <c r="C737" s="2">
         <v>4</v>
       </c>
       <c r="D737" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E737" s="2">
-        <v>151.43</v>
+        <v>145.61</v>
       </c>
       <c r="F737" s="4">
         <f>B737/E737</f>
       </c>
       <c r="G737" s="2" t="s">
+        <v>891</v>
+      </c>
+      <c r="H737" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I737" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J737" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K737" s="2" t="s">
         <v>910</v>
-      </c>
-      <c r="H737" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I737" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J737" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K737" s="2" t="s">
-        <v>911</v>
       </c>
     </row>
     <row r="738" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -29061,22 +29070,22 @@
         <v>731</v>
       </c>
       <c r="B738" s="3">
-        <v>4200000</v>
+        <v>1440000</v>
       </c>
       <c r="C738" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D738" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E738" s="2">
-        <v>502</v>
+        <v>151.43</v>
       </c>
       <c r="F738" s="4">
         <f>B738/E738</f>
       </c>
       <c r="G738" s="2" t="s">
-        <v>910</v>
+        <v>891</v>
       </c>
       <c r="H738" s="2" t="s">
         <v>13</v>
@@ -29088,7 +29097,7 @@
         <v>14</v>
       </c>
       <c r="K738" s="2" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="739" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -29096,22 +29105,22 @@
         <v>731</v>
       </c>
       <c r="B739" s="3">
-        <v>1450000</v>
+        <v>1995000</v>
       </c>
       <c r="C739" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D739" s="2">
         <v>1</v>
       </c>
       <c r="E739" s="2">
-        <v>313.78</v>
+        <v>147.26</v>
       </c>
       <c r="F739" s="4">
         <f>B739/E739</f>
       </c>
       <c r="G739" s="2" t="s">
-        <v>913</v>
+        <v>891</v>
       </c>
       <c r="H739" s="2" t="s">
         <v>13</v>
@@ -29123,7 +29132,7 @@
         <v>14</v>
       </c>
       <c r="K739" s="2" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
     </row>
     <row r="740" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -29131,34 +29140,34 @@
         <v>731</v>
       </c>
       <c r="B740" s="3">
-        <v>890000</v>
+        <v>795000</v>
       </c>
       <c r="C740" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D740" s="2">
         <v>1</v>
       </c>
       <c r="E740" s="2">
-        <v>160.08</v>
+        <v>115.86</v>
       </c>
       <c r="F740" s="4">
         <f>B740/E740</f>
       </c>
       <c r="G740" s="2" t="s">
+        <v>891</v>
+      </c>
+      <c r="H740" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="I740" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J740" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K740" s="2" t="s">
         <v>913</v>
-      </c>
-      <c r="H740" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I740" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J740" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K740" s="2" t="s">
-        <v>915</v>
       </c>
     </row>
     <row r="741" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -29166,22 +29175,22 @@
         <v>731</v>
       </c>
       <c r="B741" s="3">
-        <v>1600000</v>
+        <v>945000</v>
       </c>
       <c r="C741" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D741" s="2">
         <v>1</v>
       </c>
       <c r="E741" s="2">
-        <v>208</v>
+        <v>94.68</v>
       </c>
       <c r="F741" s="4">
         <f>B741/E741</f>
       </c>
       <c r="G741" s="2" t="s">
-        <v>913</v>
+        <v>891</v>
       </c>
       <c r="H741" s="2" t="s">
         <v>13</v>
@@ -29193,7 +29202,7 @@
         <v>14</v>
       </c>
       <c r="K741" s="2" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
     </row>
     <row r="742" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -29201,25 +29210,25 @@
         <v>731</v>
       </c>
       <c r="B742" s="3">
-        <v>1790000</v>
+        <v>695000</v>
       </c>
       <c r="C742" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D742" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E742" s="2">
-        <v>250</v>
+        <v>105.56</v>
       </c>
       <c r="F742" s="4">
         <f>B742/E742</f>
       </c>
       <c r="G742" s="2" t="s">
-        <v>913</v>
+        <v>891</v>
       </c>
       <c r="H742" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="I742" s="2" t="s">
         <v>13</v>
@@ -29228,7 +29237,7 @@
         <v>14</v>
       </c>
       <c r="K742" s="2" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
     </row>
     <row r="743" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -29236,22 +29245,22 @@
         <v>731</v>
       </c>
       <c r="B743" s="3">
-        <v>1995000</v>
+        <v>4200000</v>
       </c>
       <c r="C743" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D743" s="2">
         <v>1</v>
       </c>
       <c r="E743" s="2">
-        <v>190.1</v>
+        <v>502</v>
       </c>
       <c r="F743" s="4">
         <f>B743/E743</f>
       </c>
       <c r="G743" s="2" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="H743" s="2" t="s">
         <v>13</v>
@@ -29263,7 +29272,7 @@
         <v>14</v>
       </c>
       <c r="K743" s="2" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="744" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -29271,22 +29280,22 @@
         <v>731</v>
       </c>
       <c r="B744" s="3">
-        <v>1995000</v>
+        <v>1450000</v>
       </c>
       <c r="C744" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D744" s="2">
         <v>1</v>
       </c>
       <c r="E744" s="2">
-        <v>328</v>
+        <v>313.78</v>
       </c>
       <c r="F744" s="4">
         <f>B744/E744</f>
       </c>
       <c r="G744" s="2" t="s">
-        <v>913</v>
+        <v>918</v>
       </c>
       <c r="H744" s="2" t="s">
         <v>13</v>
@@ -29306,22 +29315,22 @@
         <v>731</v>
       </c>
       <c r="B745" s="3">
-        <v>1795000</v>
+        <v>890000</v>
       </c>
       <c r="C745" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D745" s="2">
         <v>1</v>
       </c>
       <c r="E745" s="2">
-        <v>240</v>
+        <v>160.08</v>
       </c>
       <c r="F745" s="4">
         <f>B745/E745</f>
       </c>
       <c r="G745" s="2" t="s">
-        <v>913</v>
+        <v>918</v>
       </c>
       <c r="H745" s="2" t="s">
         <v>13</v>
@@ -29341,22 +29350,22 @@
         <v>731</v>
       </c>
       <c r="B746" s="3">
-        <v>1990000</v>
+        <v>1600000</v>
       </c>
       <c r="C746" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D746" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E746" s="2">
-        <v>310</v>
+        <v>208</v>
       </c>
       <c r="F746" s="4">
         <f>B746/E746</f>
       </c>
       <c r="G746" s="2" t="s">
-        <v>913</v>
+        <v>918</v>
       </c>
       <c r="H746" s="2" t="s">
         <v>13</v>
@@ -29376,25 +29385,25 @@
         <v>731</v>
       </c>
       <c r="B747" s="3">
-        <v>740000</v>
+        <v>1790000</v>
       </c>
       <c r="C747" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D747" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E747" s="2">
-        <v>209.04</v>
+        <v>250</v>
       </c>
       <c r="F747" s="4">
         <f>B747/E747</f>
       </c>
       <c r="G747" s="2" t="s">
-        <v>913</v>
+        <v>918</v>
       </c>
       <c r="H747" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="I747" s="2" t="s">
         <v>13</v>
@@ -29411,34 +29420,34 @@
         <v>731</v>
       </c>
       <c r="B748" s="3">
-        <v>565000</v>
+        <v>1995000</v>
       </c>
       <c r="C748" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D748" s="2">
         <v>1</v>
       </c>
       <c r="E748" s="2">
-        <v>72</v>
+        <v>190.1</v>
       </c>
       <c r="F748" s="4">
         <f>B748/E748</f>
       </c>
       <c r="G748" s="2" t="s">
+        <v>918</v>
+      </c>
+      <c r="H748" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I748" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J748" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K748" s="2" t="s">
         <v>923</v>
-      </c>
-      <c r="H748" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="I748" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="J748" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K748" s="2" t="s">
-        <v>924</v>
       </c>
     </row>
     <row r="749" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -29446,18 +29455,22 @@
         <v>731</v>
       </c>
       <c r="B749" s="3">
-        <v>1990000</v>
-      </c>
-      <c r="C749" s="2"/>
-      <c r="D749" s="2"/>
+        <v>1995000</v>
+      </c>
+      <c r="C749" s="2">
+        <v>6</v>
+      </c>
+      <c r="D749" s="2">
+        <v>1</v>
+      </c>
       <c r="E749" s="2">
-        <v>333.83</v>
+        <v>328</v>
       </c>
       <c r="F749" s="4">
         <f>B749/E749</f>
       </c>
       <c r="G749" s="2" t="s">
-        <v>923</v>
+        <v>918</v>
       </c>
       <c r="H749" s="2" t="s">
         <v>13</v>
@@ -29469,7 +29482,7 @@
         <v>14</v>
       </c>
       <c r="K749" s="2" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
     <row r="750" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -29477,18 +29490,22 @@
         <v>731</v>
       </c>
       <c r="B750" s="3">
-        <v>2050000</v>
-      </c>
-      <c r="C750" s="2"/>
-      <c r="D750" s="2"/>
+        <v>1795000</v>
+      </c>
+      <c r="C750" s="2">
+        <v>5</v>
+      </c>
+      <c r="D750" s="2">
+        <v>1</v>
+      </c>
       <c r="E750" s="2">
-        <v>333.83</v>
+        <v>240</v>
       </c>
       <c r="F750" s="4">
         <f>B750/E750</f>
       </c>
       <c r="G750" s="2" t="s">
-        <v>923</v>
+        <v>918</v>
       </c>
       <c r="H750" s="2" t="s">
         <v>13</v>
@@ -29500,7 +29517,7 @@
         <v>14</v>
       </c>
       <c r="K750" s="2" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="751" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -29508,22 +29525,22 @@
         <v>731</v>
       </c>
       <c r="B751" s="3">
-        <v>900000</v>
+        <v>1990000</v>
       </c>
       <c r="C751" s="2">
         <v>4</v>
       </c>
       <c r="D751" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E751" s="2">
-        <v>175</v>
+        <v>310</v>
       </c>
       <c r="F751" s="4">
         <f>B751/E751</f>
       </c>
       <c r="G751" s="2" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="H751" s="2" t="s">
         <v>13</v>
@@ -29543,34 +29560,34 @@
         <v>731</v>
       </c>
       <c r="B752" s="3">
-        <v>249000</v>
+        <v>370000</v>
       </c>
       <c r="C752" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D752" s="2">
         <v>1</v>
       </c>
       <c r="E752" s="2">
-        <v>31.19</v>
+        <v>75</v>
       </c>
       <c r="F752" s="4">
         <f>B752/E752</f>
       </c>
       <c r="G752" s="2" t="s">
-        <v>923</v>
+        <v>928</v>
       </c>
       <c r="H752" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="I752" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="J752" s="2" t="s">
         <v>14</v>
       </c>
       <c r="K752" s="2" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
     </row>
     <row r="753" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -29578,7 +29595,7 @@
         <v>731</v>
       </c>
       <c r="B753" s="3">
-        <v>1100000</v>
+        <v>1450000</v>
       </c>
       <c r="C753" s="2">
         <v>4</v>
@@ -29587,13 +29604,13 @@
         <v>1</v>
       </c>
       <c r="E753" s="2">
-        <v>184.25</v>
+        <v>207</v>
       </c>
       <c r="F753" s="4">
         <f>B753/E753</f>
       </c>
       <c r="G753" s="2" t="s">
-        <v>923</v>
+        <v>930</v>
       </c>
       <c r="H753" s="2" t="s">
         <v>13</v>
@@ -29605,7 +29622,7 @@
         <v>14</v>
       </c>
       <c r="K753" s="2" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
     </row>
     <row r="754" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -29613,34 +29630,34 @@
         <v>731</v>
       </c>
       <c r="B754" s="3">
-        <v>560000</v>
+        <v>1350000</v>
       </c>
       <c r="C754" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D754" s="2">
         <v>1</v>
       </c>
       <c r="E754" s="2">
-        <v>112.82</v>
+        <v>166</v>
       </c>
       <c r="F754" s="4">
         <f>B754/E754</f>
       </c>
       <c r="G754" s="2" t="s">
-        <v>923</v>
+        <v>930</v>
       </c>
       <c r="H754" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="I754" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="J754" s="2" t="s">
         <v>14</v>
       </c>
       <c r="K754" s="2" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
     </row>
     <row r="755" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -29648,34 +29665,34 @@
         <v>731</v>
       </c>
       <c r="B755" s="3">
-        <v>370000</v>
+        <v>5000000</v>
       </c>
       <c r="C755" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D755" s="2">
         <v>1</v>
       </c>
       <c r="E755" s="2">
-        <v>75</v>
+        <v>470</v>
       </c>
       <c r="F755" s="4">
         <f>B755/E755</f>
       </c>
       <c r="G755" s="2" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="H755" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="I755" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="J755" s="2" t="s">
         <v>14</v>
       </c>
       <c r="K755" s="2" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
     </row>
     <row r="756" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -29683,22 +29700,22 @@
         <v>731</v>
       </c>
       <c r="B756" s="3">
-        <v>1450000</v>
+        <v>3000000</v>
       </c>
       <c r="C756" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D756" s="2">
         <v>1</v>
       </c>
       <c r="E756" s="2">
-        <v>207</v>
+        <v>361.03</v>
       </c>
       <c r="F756" s="4">
         <f>B756/E756</f>
       </c>
       <c r="G756" s="2" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="H756" s="2" t="s">
         <v>13</v>
@@ -29718,34 +29735,34 @@
         <v>731</v>
       </c>
       <c r="B757" s="3">
-        <v>795000</v>
+        <v>1680000</v>
       </c>
       <c r="C757" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D757" s="2">
         <v>1</v>
       </c>
       <c r="E757" s="2">
-        <v>115.86</v>
+        <v>228.95</v>
       </c>
       <c r="F757" s="4">
         <f>B757/E757</f>
       </c>
       <c r="G757" s="2" t="s">
+        <v>930</v>
+      </c>
+      <c r="H757" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I757" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J757" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K757" s="2" t="s">
         <v>935</v>
-      </c>
-      <c r="H757" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="I757" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J757" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K757" s="2" t="s">
-        <v>936</v>
       </c>
     </row>
     <row r="758" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -29753,34 +29770,34 @@
         <v>731</v>
       </c>
       <c r="B758" s="3">
-        <v>945000</v>
+        <v>560000</v>
       </c>
       <c r="C758" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D758" s="2">
         <v>1</v>
       </c>
       <c r="E758" s="2">
-        <v>94.68</v>
+        <v>112.82</v>
       </c>
       <c r="F758" s="4">
         <f>B758/E758</f>
       </c>
       <c r="G758" s="2" t="s">
-        <v>935</v>
+        <v>930</v>
       </c>
       <c r="H758" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="I758" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="J758" s="2" t="s">
         <v>14</v>
       </c>
       <c r="K758" s="2" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
     <row r="759" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -29803,7 +29820,7 @@
         <f>B759/E759</f>
       </c>
       <c r="G759" s="2" t="s">
-        <v>935</v>
+        <v>930</v>
       </c>
       <c r="H759" s="2" t="s">
         <v>13</v>
@@ -29815,7 +29832,7 @@
         <v>14</v>
       </c>
       <c r="K759" s="2" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="760" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -29823,22 +29840,22 @@
         <v>731</v>
       </c>
       <c r="B760" s="3">
-        <v>1680000</v>
+        <v>1290000</v>
       </c>
       <c r="C760" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D760" s="2">
         <v>1</v>
       </c>
       <c r="E760" s="2">
-        <v>228.95</v>
+        <v>166</v>
       </c>
       <c r="F760" s="4">
         <f>B760/E760</f>
       </c>
       <c r="G760" s="2" t="s">
-        <v>935</v>
+        <v>930</v>
       </c>
       <c r="H760" s="2" t="s">
         <v>13</v>
@@ -29850,7 +29867,7 @@
         <v>14</v>
       </c>
       <c r="K760" s="2" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="761" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -29858,25 +29875,25 @@
         <v>731</v>
       </c>
       <c r="B761" s="3">
-        <v>1695000</v>
+        <v>740000</v>
       </c>
       <c r="C761" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D761" s="2">
         <v>1</v>
       </c>
       <c r="E761" s="2">
-        <v>207</v>
+        <v>209.04</v>
       </c>
       <c r="F761" s="4">
         <f>B761/E761</f>
       </c>
       <c r="G761" s="2" t="s">
-        <v>935</v>
+        <v>939</v>
       </c>
       <c r="H761" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="I761" s="2" t="s">
         <v>13</v>
@@ -29893,34 +29910,34 @@
         <v>731</v>
       </c>
       <c r="B762" s="3">
-        <v>1995000</v>
+        <v>745000</v>
       </c>
       <c r="C762" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D762" s="2">
         <v>1</v>
       </c>
       <c r="E762" s="2">
-        <v>147.26</v>
+        <v>124</v>
       </c>
       <c r="F762" s="4">
         <f>B762/E762</f>
       </c>
       <c r="G762" s="2" t="s">
-        <v>935</v>
+        <v>941</v>
       </c>
       <c r="H762" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I762" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="J762" s="2" t="s">
         <v>14</v>
       </c>
       <c r="K762" s="2" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
     </row>
     <row r="763" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -29928,22 +29945,22 @@
         <v>731</v>
       </c>
       <c r="B763" s="3">
-        <v>1290000</v>
+        <v>2750000</v>
       </c>
       <c r="C763" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D763" s="2">
         <v>1</v>
       </c>
       <c r="E763" s="2">
-        <v>166</v>
+        <v>380</v>
       </c>
       <c r="F763" s="4">
         <f>B763/E763</f>
       </c>
       <c r="G763" s="2" t="s">
-        <v>935</v>
+        <v>941</v>
       </c>
       <c r="H763" s="2" t="s">
         <v>13</v>
@@ -29955,7 +29972,7 @@
         <v>14</v>
       </c>
       <c r="K763" s="2" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
     </row>
     <row r="764" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -29963,22 +29980,22 @@
         <v>731</v>
       </c>
       <c r="B764" s="3">
-        <v>835000</v>
+        <v>595000</v>
       </c>
       <c r="C764" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D764" s="2">
         <v>1</v>
       </c>
       <c r="E764" s="2">
-        <v>145.61</v>
+        <v>69.09</v>
       </c>
       <c r="F764" s="4">
         <f>B764/E764</f>
       </c>
       <c r="G764" s="2" t="s">
-        <v>935</v>
+        <v>941</v>
       </c>
       <c r="H764" s="2" t="s">
         <v>13</v>
@@ -29990,7 +30007,7 @@
         <v>14</v>
       </c>
       <c r="K764" s="2" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
     </row>
     <row r="765" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -29998,22 +30015,22 @@
         <v>731</v>
       </c>
       <c r="B765" s="3">
-        <v>5000000</v>
+        <v>1275000</v>
       </c>
       <c r="C765" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D765" s="2">
         <v>1</v>
       </c>
       <c r="E765" s="2">
-        <v>470</v>
+        <v>173</v>
       </c>
       <c r="F765" s="4">
         <f>B765/E765</f>
       </c>
       <c r="G765" s="2" t="s">
-        <v>935</v>
+        <v>941</v>
       </c>
       <c r="H765" s="2" t="s">
         <v>13</v>
@@ -30025,7 +30042,7 @@
         <v>14</v>
       </c>
       <c r="K765" s="2" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
     </row>
     <row r="766" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30033,22 +30050,22 @@
         <v>731</v>
       </c>
       <c r="B766" s="3">
-        <v>1350000</v>
+        <v>1990000</v>
       </c>
       <c r="C766" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D766" s="2">
         <v>1</v>
       </c>
       <c r="E766" s="2">
-        <v>166</v>
+        <v>230</v>
       </c>
       <c r="F766" s="4">
         <f>B766/E766</f>
       </c>
       <c r="G766" s="2" t="s">
-        <v>935</v>
+        <v>941</v>
       </c>
       <c r="H766" s="2" t="s">
         <v>13</v>
@@ -30060,7 +30077,7 @@
         <v>14</v>
       </c>
       <c r="K766" s="2" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
     </row>
     <row r="767" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30068,22 +30085,18 @@
         <v>731</v>
       </c>
       <c r="B767" s="3">
-        <v>3000000</v>
-      </c>
-      <c r="C767" s="2">
-        <v>6</v>
-      </c>
-      <c r="D767" s="2">
-        <v>1</v>
-      </c>
+        <v>4680000</v>
+      </c>
+      <c r="C767" s="2"/>
+      <c r="D767" s="2"/>
       <c r="E767" s="2">
-        <v>361.03</v>
+        <v>600</v>
       </c>
       <c r="F767" s="4">
         <f>B767/E767</f>
       </c>
       <c r="G767" s="2" t="s">
-        <v>935</v>
+        <v>941</v>
       </c>
       <c r="H767" s="2" t="s">
         <v>13</v>
@@ -30095,7 +30108,7 @@
         <v>14</v>
       </c>
       <c r="K767" s="2" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
     </row>
     <row r="768" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30103,22 +30116,22 @@
         <v>731</v>
       </c>
       <c r="B768" s="3">
-        <v>1850000</v>
+        <v>2200000</v>
       </c>
       <c r="C768" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D768" s="2">
         <v>1</v>
       </c>
       <c r="E768" s="2">
-        <v>186</v>
+        <v>225</v>
       </c>
       <c r="F768" s="4">
         <f>B768/E768</f>
       </c>
       <c r="G768" s="2" t="s">
-        <v>935</v>
+        <v>941</v>
       </c>
       <c r="H768" s="2" t="s">
         <v>13</v>
@@ -30130,7 +30143,7 @@
         <v>14</v>
       </c>
       <c r="K768" s="2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
     </row>
     <row r="769" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30138,28 +30151,28 @@
         <v>731</v>
       </c>
       <c r="B769" s="3">
-        <v>745000</v>
+        <v>880000</v>
       </c>
       <c r="C769" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D769" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E769" s="2">
-        <v>124</v>
+        <v>93.99</v>
       </c>
       <c r="F769" s="4">
         <f>B769/E769</f>
       </c>
       <c r="G769" s="2" t="s">
-        <v>948</v>
+        <v>941</v>
       </c>
       <c r="H769" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I769" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="J769" s="2" t="s">
         <v>14</v>
@@ -30173,22 +30186,22 @@
         <v>731</v>
       </c>
       <c r="B770" s="3">
-        <v>2750000</v>
+        <v>1100000</v>
       </c>
       <c r="C770" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D770" s="2">
         <v>1</v>
       </c>
       <c r="E770" s="2">
-        <v>380</v>
+        <v>184.25</v>
       </c>
       <c r="F770" s="4">
         <f>B770/E770</f>
       </c>
       <c r="G770" s="2" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="H770" s="2" t="s">
         <v>13</v>
@@ -30200,7 +30213,7 @@
         <v>14</v>
       </c>
       <c r="K770" s="2" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
     </row>
     <row r="771" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30208,22 +30221,22 @@
         <v>731</v>
       </c>
       <c r="B771" s="3">
-        <v>595000</v>
+        <v>900000</v>
       </c>
       <c r="C771" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D771" s="2">
         <v>1</v>
       </c>
       <c r="E771" s="2">
-        <v>69.09</v>
+        <v>175</v>
       </c>
       <c r="F771" s="4">
         <f>B771/E771</f>
       </c>
       <c r="G771" s="2" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="H771" s="2" t="s">
         <v>13</v>
@@ -30235,7 +30248,7 @@
         <v>14</v>
       </c>
       <c r="K771" s="2" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
     </row>
     <row r="772" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30243,22 +30256,22 @@
         <v>731</v>
       </c>
       <c r="B772" s="3">
-        <v>1275000</v>
+        <v>3700000</v>
       </c>
       <c r="C772" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D772" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E772" s="2">
-        <v>173</v>
+        <v>446</v>
       </c>
       <c r="F772" s="4">
         <f>B772/E772</f>
       </c>
       <c r="G772" s="2" t="s">
-        <v>948</v>
+        <v>953</v>
       </c>
       <c r="H772" s="2" t="s">
         <v>13</v>
@@ -30270,7 +30283,7 @@
         <v>14</v>
       </c>
       <c r="K772" s="2" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
     </row>
     <row r="773" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30278,22 +30291,22 @@
         <v>731</v>
       </c>
       <c r="B773" s="3">
-        <v>1990000</v>
+        <v>2100000</v>
       </c>
       <c r="C773" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D773" s="2">
         <v>1</v>
       </c>
       <c r="E773" s="2">
-        <v>230</v>
+        <v>447.66</v>
       </c>
       <c r="F773" s="4">
         <f>B773/E773</f>
       </c>
       <c r="G773" s="2" t="s">
-        <v>948</v>
+        <v>953</v>
       </c>
       <c r="H773" s="2" t="s">
         <v>13</v>
@@ -30302,10 +30315,10 @@
         <v>13</v>
       </c>
       <c r="J773" s="2" t="s">
-        <v>14</v>
+        <v>214</v>
       </c>
       <c r="K773" s="2" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
     </row>
     <row r="774" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30313,18 +30326,18 @@
         <v>731</v>
       </c>
       <c r="B774" s="3">
-        <v>4680000</v>
+        <v>1990000</v>
       </c>
       <c r="C774" s="2"/>
       <c r="D774" s="2"/>
       <c r="E774" s="2">
-        <v>600</v>
+        <v>333.83</v>
       </c>
       <c r="F774" s="4">
         <f>B774/E774</f>
       </c>
       <c r="G774" s="2" t="s">
-        <v>948</v>
+        <v>953</v>
       </c>
       <c r="H774" s="2" t="s">
         <v>13</v>
@@ -30336,7 +30349,7 @@
         <v>14</v>
       </c>
       <c r="K774" s="2" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
     </row>
     <row r="775" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30344,22 +30357,18 @@
         <v>731</v>
       </c>
       <c r="B775" s="3">
-        <v>2200000</v>
-      </c>
-      <c r="C775" s="2">
-        <v>6</v>
-      </c>
-      <c r="D775" s="2">
-        <v>1</v>
-      </c>
+        <v>2050000</v>
+      </c>
+      <c r="C775" s="2"/>
+      <c r="D775" s="2"/>
       <c r="E775" s="2">
-        <v>225</v>
+        <v>333.83</v>
       </c>
       <c r="F775" s="4">
         <f>B775/E775</f>
       </c>
       <c r="G775" s="2" t="s">
-        <v>948</v>
+        <v>953</v>
       </c>
       <c r="H775" s="2" t="s">
         <v>13</v>
@@ -30371,7 +30380,7 @@
         <v>14</v>
       </c>
       <c r="K775" s="2" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
     </row>
     <row r="776" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30379,22 +30388,22 @@
         <v>731</v>
       </c>
       <c r="B776" s="3">
-        <v>880000</v>
+        <v>595000</v>
       </c>
       <c r="C776" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D776" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E776" s="2">
-        <v>93.99</v>
+        <v>214.6</v>
       </c>
       <c r="F776" s="4">
         <f>B776/E776</f>
       </c>
       <c r="G776" s="2" t="s">
-        <v>948</v>
+        <v>953</v>
       </c>
       <c r="H776" s="2" t="s">
         <v>13</v>
@@ -30406,7 +30415,7 @@
         <v>14</v>
       </c>
       <c r="K776" s="2" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
     </row>
     <row r="777" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30414,22 +30423,22 @@
         <v>731</v>
       </c>
       <c r="B777" s="3">
-        <v>3700000</v>
+        <v>2850000</v>
       </c>
       <c r="C777" s="2">
         <v>6</v>
       </c>
       <c r="D777" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E777" s="2">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="F777" s="4">
         <f>B777/E777</f>
       </c>
       <c r="G777" s="2" t="s">
-        <v>957</v>
+        <v>953</v>
       </c>
       <c r="H777" s="2" t="s">
         <v>13</v>
@@ -30441,7 +30450,7 @@
         <v>14</v>
       </c>
       <c r="K777" s="2" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
     </row>
     <row r="778" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30449,34 +30458,34 @@
         <v>731</v>
       </c>
       <c r="B778" s="3">
-        <v>2100000</v>
+        <v>565000</v>
       </c>
       <c r="C778" s="2">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D778" s="2">
         <v>1</v>
       </c>
       <c r="E778" s="2">
-        <v>447.66</v>
+        <v>72</v>
       </c>
       <c r="F778" s="4">
         <f>B778/E778</f>
       </c>
       <c r="G778" s="2" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="H778" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="I778" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="J778" s="2" t="s">
-        <v>214</v>
+        <v>14</v>
       </c>
       <c r="K778" s="2" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
     </row>
     <row r="779" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30484,22 +30493,22 @@
         <v>731</v>
       </c>
       <c r="B779" s="3">
-        <v>595000</v>
+        <v>249000</v>
       </c>
       <c r="C779" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D779" s="2">
         <v>1</v>
       </c>
       <c r="E779" s="2">
-        <v>214.6</v>
+        <v>31.19</v>
       </c>
       <c r="F779" s="4">
         <f>B779/E779</f>
       </c>
       <c r="G779" s="2" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="H779" s="2" t="s">
         <v>13</v>
@@ -30511,7 +30520,7 @@
         <v>14</v>
       </c>
       <c r="K779" s="2" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
     </row>
     <row r="780" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30519,22 +30528,22 @@
         <v>731</v>
       </c>
       <c r="B780" s="3">
-        <v>2850000</v>
+        <v>4095000</v>
       </c>
       <c r="C780" s="2">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="D780" s="2">
         <v>1</v>
       </c>
       <c r="E780" s="2">
-        <v>455</v>
+        <v>1737</v>
       </c>
       <c r="F780" s="4">
         <f>B780/E780</f>
       </c>
       <c r="G780" s="2" t="s">
-        <v>957</v>
+        <v>963</v>
       </c>
       <c r="H780" s="2" t="s">
         <v>13</v>
@@ -30546,7 +30555,7 @@
         <v>14</v>
       </c>
       <c r="K780" s="2" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
     </row>
   </sheetData>
@@ -30566,527 +30575,527 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>962</v>
+        <v>965</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>966</v>
+        <v>969</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>968</v>
+        <v>971</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>968</v>
+        <v>971</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>968</v>
+        <v>971</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>968</v>
+        <v>971</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>972</v>
+        <v>975</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>973</v>
+        <v>976</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" s="6" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" s="6" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" s="6" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" s="6" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" s="6" t="s">
-        <v>997</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" s="6" t="s">
-        <v>997</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" s="6" t="s">
-        <v>997</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
-        <v>997</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" s="6" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" s="6" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" s="6" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" s="6" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="6" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" s="6" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" s="6" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" s="6" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" s="6" t="s">
-        <v>1000</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" s="6" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" s="6" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" s="6" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" s="6" t="s">
-        <v>1002</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" s="6" t="s">
-        <v>1002</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" s="6" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" s="6" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" s="6" t="s">
-        <v>1004</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" s="6" t="s">
-        <v>1004</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" s="6" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" s="6" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" s="6" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" s="6" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" s="6" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" s="6" t="s">
-        <v>1008</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" s="6" t="s">
-        <v>1008</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" s="6" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" s="6" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" s="6" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105" s="6" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
     </row>
   </sheetData>

--- a/listings-sale.xlsx
+++ b/listings-sale.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4790" uniqueCount="1016">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4712" uniqueCount="999">
   <si>
     <t>Source</t>
   </si>
@@ -167,12 +167,12 @@
     <t>https://www.barnes-international.com/en/for-sale/france/boulogne-billancourt/ref-APM-85141225.html</t>
   </si>
   <si>
+    <t>https://www.barnes-international.com/en/for-sale/france/boulogne-billancourt/ref-APM-87180111.html</t>
+  </si>
+  <si>
     <t>https://www.barnes-international.com/en/for-sale/france/boulogne-billancourt/ref-APM-87142043.html</t>
   </si>
   <si>
-    <t>https://www.barnes-international.com/en/for-sale/france/boulogne-billancourt/ref-APM-87180111.html</t>
-  </si>
-  <si>
     <t>https://www.barnes-international.com/en/for-sale/france/boulogne-billancourt/ref-APM-87044516.html</t>
   </si>
   <si>
@@ -242,12 +242,12 @@
     <t>https://www.barnes-international.com/en/for-sale/france/boulogne-billancourt/ref-APM-87014108.html</t>
   </si>
   <si>
+    <t>https://www.barnes-international.com/en/for-sale/france/boulogne-billancourt/ref-APM-86869751.html</t>
+  </si>
+  <si>
     <t>https://www.barnes-international.com/en/for-sale/france/boulogne-billancourt/ref-APM-86687783.html</t>
   </si>
   <si>
-    <t>https://www.barnes-international.com/en/for-sale/france/boulogne-billancourt/ref-APM-86869751.html</t>
-  </si>
-  <si>
     <t>https://www.barnes-international.com/en/for-sale/france/boulogne-billancourt/ref-APM-86940243.html</t>
   </si>
   <si>
@@ -323,12 +323,12 @@
     <t>https://www.barnes-international.com/en/for-sale/france/suresnes/ref-APM-85956488.html</t>
   </si>
   <si>
+    <t>https://www.barnes-international.com/en/for-sale/france/suresnes/ref-APM-86778833.html</t>
+  </si>
+  <si>
     <t>https://www.barnes-international.com/en/for-sale/france/suresnes/ref-APM-86504020.html</t>
   </si>
   <si>
-    <t>https://www.barnes-international.com/en/for-sale/france/suresnes/ref-APM-86778833.html</t>
-  </si>
-  <si>
     <t>https://www.barnes-international.com/en/for-sale/france/suresnes/ref-APM-86872602.html</t>
   </si>
   <si>
@@ -539,12 +539,12 @@
     <t>https://www.barnes-international.com/en/for-sale/france/saint-germain-en-laye/ref-APM-87155229.html</t>
   </si>
   <si>
+    <t>https://www.barnes-international.com/en/for-sale/france/saint-germain-en-laye/ref-APM-86844576.html</t>
+  </si>
+  <si>
     <t>https://www.barnes-international.com/en/for-sale/france/saint-germain-en-laye/ref-APM-86056417.html</t>
   </si>
   <si>
-    <t>https://www.barnes-international.com/en/for-sale/france/saint-germain-en-laye/ref-APM-86844576.html</t>
-  </si>
-  <si>
     <t>https://www.barnes-international.com/en/for-sale/france/saint-germain-en-laye/ref-APM-84486371.html</t>
   </si>
   <si>
@@ -2348,6 +2348,24 @@
     <t>https://www.junot.fr/fr/biens/86869353-issy-les-moulineaux-ile-saint-germain</t>
   </si>
   <si>
+    <t>https://www.junot.fr/fr/biens/86689945-paris-16e-garigliano</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86924138-paris-16e-boileau</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86369553-vanves-michelet</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86827371-paris-16e-porte-de-saint-cloud</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86723506-paris-16e-michel-ange</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86941073-paris-16e-auteuil</t>
+  </si>
+  <si>
     <t>La-Garenne-Colombes</t>
   </si>
   <si>
@@ -2432,6 +2450,21 @@
     <t>https://www.junot.fr/fr/biens/86726109-meudon-bellevue</t>
   </si>
   <si>
+    <t>https://www.junot.fr/fr/biens/86927403-ville-d-avray-centre</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/87157964-ville-d-avray-cote-dargent</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/85905505-ville-d-avray-cote-dargent</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/87069117-saint-cloud-parc-de-montretout</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86973126-ville-d-avray-centre</t>
+  </si>
+  <si>
     <t>Nanterre</t>
   </si>
   <si>
@@ -2471,94 +2504,259 @@
     <t>https://www.junot.fr/fr/biens/86754230-rueil-malmaison-rueil-sur-seine</t>
   </si>
   <si>
+    <t>https://www.junot.fr/fr/biens/87176871-neuilly-sur-seine-saint-james</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/87169484-neuilly-sur-seine</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/87095615-neuilly-sur-seine-victor-hugo</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86884592-neuilly-sur-seine-sablons</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86108932-neuilly-sur-seine-pont-de-neuilly</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86911620-neuilly-sur-seine-madrid-saint-james</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86806678-neuilly-sur-seine-pont-de-neuilly</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/85460591-rueil-malmaison-saint-cucufa</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/82573732-rueil-malmaison-centre-ville</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86872335-rueil-malmaison-bords-de-seine</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/87151941-rueil-malmaison-mont-valerien</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/87089492-rueil-malmaison-saint-cucufa</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86883296-rueil-malmaison-richelieu</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86790803-rueil-malmaison-centre-ville-chateau-de-la-malmaison</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/87090496-rueil-malmaison-buzenval</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/87043503-rueil-malmaison-saint-cucufa</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86992006-saint-cloud-montretout</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/87119982-saint-cloud-pasteur</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86364093-saint-cloud-montretout</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86377932-saint-cloud-montretout</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/87072517-saint-cloud-montretout</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/84682885-saint-cloud-les-coteaux</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86700513-saint-cloud-coteaux</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86826251-saint-cloud-les-coteaux</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/85476183-saint-cloud-les-coteaux</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86418379-saint-cloud-montretout</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86235728-saint-cloud-milons</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86333180-saint-cloud-montretout</t>
+  </si>
+  <si>
+    <t>Sceaux</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86935086-sceaux-parc-de-sceaux</t>
+  </si>
+  <si>
     <t>https://www.junot.fr/fr/biens/87013564-suresnes-carnot-gambetta</t>
   </si>
   <si>
-    <t>https://www.junot.fr/fr/biens/85342115-rueil-malmaison-plateau</t>
-  </si>
-  <si>
     <t>https://www.junot.fr/fr/biens/86855201-suresnes-carnot-gambetta</t>
   </si>
   <si>
-    <t>https://www.junot.fr/fr/biens/86818496-rueil-malmaison-mont-valerien</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86665428-rueil-malmaison-mont-valerien</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86406200-rueil-malmaison-triangle-dor-les-martinets</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86872057-rueil-malmaison-buzenval</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86803064-rueil-malmaison-mont-valerien</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/87151941-rueil-malmaison-mont-valerien</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/82823472-rueil-malmaison-centre-ville</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/87176871-neuilly-sur-seine-saint-james</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/87169484-neuilly-sur-seine</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/87095615-neuilly-sur-seine-victor-hugo</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86884592-neuilly-sur-seine-sablons</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86108932-neuilly-sur-seine-pont-de-neuilly</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86911620-neuilly-sur-seine-madrid-saint-james</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86806678-neuilly-sur-seine-pont-de-neuilly</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/85460591-rueil-malmaison-saint-cucufa</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/82573732-rueil-malmaison-centre-ville</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86872335-rueil-malmaison-bords-de-seine</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/87089492-rueil-malmaison-saint-cucufa</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86883296-rueil-malmaison-richelieu</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86790803-rueil-malmaison-centre-ville-chateau-de-la-malmaison</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/87090496-rueil-malmaison-buzenval</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/87043503-rueil-malmaison-saint-cucufa</t>
+    <t>https://www.junot.fr/fr/biens/86741268-suresnes-parc-du-chateau-republique</t>
+  </si>
+  <si>
+    <t>Vanves</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86095295-paris-15e-vaugirard</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86342372-paris-15e-convention</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86044992-paris-15e-convention</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/87220895-paris-15e-saint-lambert</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86800284-paris-15e-villa-violet</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86694620-paris-15e-quartier-commerce</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86962420-paris-15e-entrepreneurs-commerce</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86492856-vaucresson-division-thery</t>
+  </si>
+  <si>
+    <t>Ville-D-Avray</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/85599270-ville-d-avray-les-etangs-de-corot</t>
+  </si>
+  <si>
+    <t>Bougival</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/87106607-bougival</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86744535-croissy-sur-seine-quartier-de-lecluse</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/85998514-louveciennes-louveciennes</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86820988-la-celle-saint-cloud-les-gressets</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86442985-la-celle-saint-cloud-le-bourg</t>
   </si>
   <si>
     <t>https://www.junot.fr/fr/biens/85269373-rueil-malmaison-hameau-de-la-jonchere</t>
   </si>
   <si>
-    <t>https://www.junot.fr/fr/biens/84234005-rueil-malmaison-centre-ville</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/87003936-rueil-malmaison-chataigneraie-empereur</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/85308431-rueil-malmaison-parc-de-la-malmaison</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/85972482-rueil-malmaison-buzenval</t>
+    <t>https://www.junot.fr/fr/biens/86348793-la-celle-saint-cloud-les-gressets</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/87049238-croissy-sur-seine-coeur-de-ville</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86872545-la-celle-saint-cloud-la-feuillaume</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/87149384-croissy-sur-seine-centre</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86614783-la-celle-saint-cloud-feuillaume</t>
+  </si>
+  <si>
+    <t>Chatou</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/85490363-chatou-centre-ville-mairie</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86493519-chatou-brimont</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/85450021-chatou-cote-croissy</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86787184-chatou-cote-croissy</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86690890-chatou-gambetta</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86279734-chatou-parc-piece-deau</t>
+  </si>
+  <si>
+    <t>Croissy-sur-Seine</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/87093552-le-vesinet-centre-ville</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86913195-le-vesinet-centre</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86872237-le-vesinet-centre</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86197868-le-vesinet-centre</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/87170292-le-vesinet-centre-ville</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86346204-le-vesinet-lac-inferieur</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86390403-le-vesinet-lac-superieur</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86837357-le-vesinet-centre-ville</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/87149480-le-vesinet-centre-ville</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/87116726-le-vesinet-centre</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/85441374-le-vesinet-lac-superieur-centre-ville</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/85675677-le-vesinet</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/87101200-le-vesinet-lac-superieur</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/85281254-rueil-malmaison-bords-de-seine</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86495403-le-vesinet-lac-inferieur</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86355108-le-vesinet-charmettes</t>
+  </si>
+  <si>
+    <t>La-Celle-Saint-Cloud</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86837059-la-celle-saint-cloud-la-chataigneraie</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86333080-la-celle-saint-cloud-chataigneraie</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86796631-le-chesnay-rocquencourt-aubert</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/85842451-rueil-malmaison-saint-cucufa</t>
   </si>
   <si>
     <t>https://www.junot.fr/fr/biens/85639422-rueil-malmaison-parc-de-la-malmaison</t>
@@ -2567,241 +2765,40 @@
     <t>https://www.junot.fr/fr/biens/86778792-rueil-malmaison-saint-cucufa</t>
   </si>
   <si>
-    <t>https://www.junot.fr/fr/biens/85842451-rueil-malmaison-saint-cucufa</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/85624615-rueil-malmaison-coeur-de-ville</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86992006-saint-cloud-montretout</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/87119982-saint-cloud-pasteur</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/87069117-saint-cloud-parc-de-montretout</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86364093-saint-cloud-montretout</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86377932-saint-cloud-montretout</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/87072517-saint-cloud-montretout</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/84682885-saint-cloud-les-coteaux</t>
-  </si>
-  <si>
-    <t>Sceaux</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86935086-sceaux-parc-de-sceaux</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86358591-verrieres-le-buisson-entre-le-centre-et-la-foret</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86369553-vanves-michelet</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86044992-paris-15e-convention</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86342372-paris-15e-convention</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86095295-paris-15e-vaugirard</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/87149452-paris-14e-rue-roli</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/87220895-paris-15e-saint-lambert</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86741268-suresnes-parc-du-chateau-republique</t>
-  </si>
-  <si>
-    <t>Vanves</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86800284-paris-15e-villa-violet</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86694620-paris-15e-quartier-commerce</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86962420-paris-15e-entrepreneurs-commerce</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86689945-paris-16e-garigliano</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86694718-paris-15e-quartier-commerce</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86694703-paris-15e-quartier-commerce</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/85962720-paris-15e-volontaires</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/87252349-paris-15e-commerce-fondary</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/87067584-paris-15e-suffren-breteuil</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/87067560-paris-15e</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/87067590-paris-15e-suffren-breteuil</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86492856-vaucresson-division-thery</t>
-  </si>
-  <si>
-    <t>Ville-D-Avray</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86927403-ville-d-avray-centre</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/87157964-ville-d-avray-cote-dargent</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86973126-ville-d-avray-centre</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/85599270-ville-d-avray-les-etangs-de-corot</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/85905505-ville-d-avray-cote-dargent</t>
-  </si>
-  <si>
-    <t>Bougival</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/87106607-bougival</t>
-  </si>
-  <si>
-    <t>Chatou</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/85490363-chatou-centre-ville-mairie</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86493519-chatou-brimont</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/85450021-chatou-cote-croissy</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86787184-chatou-cote-croissy</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86690890-chatou-gambetta</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86279734-chatou-parc-piece-deau</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/87101200-le-vesinet-lac-superieur</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86390403-le-vesinet-lac-superieur</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/85441374-le-vesinet-lac-superieur-centre-ville</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86913195-le-vesinet-centre</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/85281254-rueil-malmaison-bords-de-seine</t>
+    <t>Le-Mesnil-le-Roi</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86383927-le-mesnil-le-roi-saint-germain-en-laye</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86373985-maisons-laffitte-foch</t>
   </si>
   <si>
     <t>https://www.junot.fr/fr/biens/87030985-montesson-centre-ouest</t>
   </si>
   <si>
-    <t>https://www.junot.fr/fr/biens/87149480-le-vesinet-centre-ville</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/87149384-croissy-sur-seine-centre</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/87093552-le-vesinet-centre-ville</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/87170292-le-vesinet-centre-ville</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86197868-le-vesinet-centre</t>
-  </si>
-  <si>
     <t>https://www.junot.fr/fr/biens/86491268-le-vesinet-charmettes</t>
   </si>
   <si>
-    <t>https://www.junot.fr/fr/biens/85675677-le-vesinet</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/87049238-croissy-sur-seine-coeur-de-ville</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86872237-le-vesinet-centre</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86355108-le-vesinet-charmettes</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/87116726-le-vesinet-centre</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86353933-rueil-malmaison-bords-de-seine</t>
-  </si>
-  <si>
-    <t>Croissy-sur-Seine</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86744535-croissy-sur-seine-quartier-de-lecluse</t>
-  </si>
-  <si>
-    <t>La-Celle-Saint-Cloud</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86820988-la-celle-saint-cloud-les-gressets</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86837059-la-celle-saint-cloud-la-chataigneraie</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86872545-la-celle-saint-cloud-la-feuillaume</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86614783-la-celle-saint-cloud-feuillaume</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86442985-la-celle-saint-cloud-le-bourg</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86348793-la-celle-saint-cloud-les-gressets</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86333080-la-celle-saint-cloud-chataigneraie</t>
-  </si>
-  <si>
-    <t>Le-Chesnay-Rocquencourt</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86796631-le-chesnay-rocquencourt-aubert</t>
-  </si>
-  <si>
-    <t>Le-Mesnil-le-Roi</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86383927-le-mesnil-le-roi-saint-germain-en-laye</t>
+    <t>https://www.junot.fr/fr/biens/85932180-le-vesinet-ibis</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/85936999-maisons-laffitte-entre-centre-et-parc</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/85969840-le-vesinet-lac-inferieur</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86341196-le-vesinet-pelouses</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86344394-maisons-laffitte-petit-parc</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86800783-maisons-laffitte-petit-parc</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86344051-maisons-laffitte-petit-parc</t>
   </si>
   <si>
     <t>Le-Pecq</t>
@@ -2810,31 +2807,16 @@
     <t>https://www.junot.fr/fr/biens/86820063-le-pecq-limite-le-vesinet</t>
   </si>
   <si>
-    <t>https://www.junot.fr/fr/biens/86341196-le-vesinet-pelouses</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/85932180-le-vesinet-ibis</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/85969840-le-vesinet-lac-inferieur</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86495403-le-vesinet-lac-inferieur</t>
-  </si>
-  <si>
     <t>https://www.junot.fr/fr/biens/87097485-marly-le-roi-montval</t>
   </si>
   <si>
-    <t>https://www.junot.fr/fr/biens/86346204-le-vesinet-lac-inferieur</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86837357-le-vesinet-centre-ville</t>
-  </si>
-  <si>
     <t>Louveciennes</t>
   </si>
   <si>
-    <t>https://www.junot.fr/fr/biens/85998514-louveciennes-louveciennes</t>
+    <t>https://www.junot.fr/fr/biens/86802694-marly-le-roi-village</t>
+  </si>
+  <si>
+    <t>https://www.junot.fr/fr/biens/86082156-marly-le-roi-village</t>
   </si>
   <si>
     <t>Maisons-Laffitte</t>
@@ -2843,36 +2825,12 @@
     <t>https://www.junot.fr/fr/biens/87093747-maisons-laffitte-parc-de-maisons-laffitte</t>
   </si>
   <si>
-    <t>https://www.junot.fr/fr/biens/85936999-maisons-laffitte-entre-centre-et-parc</t>
-  </si>
-  <si>
     <t>https://www.junot.fr/fr/biens/87042274-maisons-laffitte-parc</t>
   </si>
   <si>
-    <t>https://www.junot.fr/fr/biens/86373985-maisons-laffitte-foch</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86800783-maisons-laffitte-petit-parc</t>
-  </si>
-  <si>
     <t>https://www.junot.fr/fr/biens/86933530-maisons-laffitte-charlemagne</t>
   </si>
   <si>
-    <t>https://www.junot.fr/fr/biens/86344051-maisons-laffitte-petit-parc</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86344394-maisons-laffitte-petit-parc</t>
-  </si>
-  <si>
-    <t>Marly-le-Roi</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86082156-marly-le-roi-village</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86802694-marly-le-roi-village</t>
-  </si>
-  <si>
     <t>Neauphle-le-Chateau</t>
   </si>
   <si>
@@ -2894,25 +2852,16 @@
     <t>https://www.junot.fr/fr/biens/86096224-rambouillet-yvelines</t>
   </si>
   <si>
-    <t>Rambouillet</t>
-  </si>
-  <si>
     <t>https://www.junot.fr/fr/biens/86760248-versailles-notre-dame</t>
   </si>
   <si>
     <t>https://www.junot.fr/fr/biens/86822950-versailles-centre-ville</t>
   </si>
   <si>
-    <t>Thoiry</t>
-  </si>
-  <si>
-    <t>https://www.junot.fr/fr/biens/86910338-bray-et-lu-vexin</t>
-  </si>
-  <si>
     <t>Prospector — Paris Listings</t>
   </si>
   <si>
-    <t>Generated: 16/08/2026, 08:03:02</t>
+    <t>Generated: 17/08/2026, 08:21:07</t>
   </si>
   <si>
     <t>Barnes: FAILED — Timed out after 300000ms: Barnes scrape</t>
@@ -3059,7 +3008,7 @@
     <t>Eiffel Housing: 36 listings</t>
   </si>
   <si>
-    <t>Junot: 205 listings</t>
+    <t>Junot: 192 listings</t>
   </si>
 </sst>
 </file>
@@ -3472,7 +3421,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K780"/>
+  <dimension ref="A1:K767"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -4738,13 +4687,13 @@
         <v>1790000</v>
       </c>
       <c r="C37" s="2">
+        <v>5</v>
+      </c>
+      <c r="D37" s="2">
         <v>3</v>
       </c>
-      <c r="D37" s="2">
-        <v>2</v>
-      </c>
       <c r="E37" s="2">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="F37" s="4">
         <f>B37/E37</f>
@@ -4773,13 +4722,13 @@
         <v>1790000</v>
       </c>
       <c r="C38" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D38" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E38" s="2">
-        <v>162</v>
+        <v>137</v>
       </c>
       <c r="F38" s="4">
         <f>B38/E38</f>
@@ -5611,13 +5560,13 @@
         <v>750000</v>
       </c>
       <c r="C62" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D62" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E62" s="2">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F62" s="4">
         <f>B62/E62</f>
@@ -5646,13 +5595,13 @@
         <v>750000</v>
       </c>
       <c r="C63" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D63" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E63" s="2">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F63" s="4">
         <f>B63/E63</f>
@@ -6509,13 +6458,13 @@
         <v>1450000</v>
       </c>
       <c r="C88" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D88" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E88" s="2">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="F88" s="4">
         <f>B88/E88</f>
@@ -6544,13 +6493,13 @@
         <v>1450000</v>
       </c>
       <c r="C89" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D89" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E89" s="2">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="F89" s="4">
         <f>B89/E89</f>
@@ -8839,10 +8788,10 @@
         <v>3</v>
       </c>
       <c r="D155" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E155" s="2">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F155" s="4">
         <f>B155/E155</f>
@@ -8874,10 +8823,10 @@
         <v>3</v>
       </c>
       <c r="D156" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E156" s="2">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F156" s="4">
         <f>B156/E156</f>
@@ -24741,34 +24690,34 @@
         <v>731</v>
       </c>
       <c r="B613" s="3">
-        <v>1295000</v>
+        <v>1760000</v>
       </c>
       <c r="C613" s="2">
         <v>4</v>
       </c>
       <c r="D613" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E613" s="2">
-        <v>174.35</v>
+        <v>177.93</v>
       </c>
       <c r="F613" s="4">
         <f>B613/E613</f>
       </c>
       <c r="G613" s="2" t="s">
+        <v>776</v>
+      </c>
+      <c r="H613" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="I613" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="J613" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K613" s="2" t="s">
         <v>778</v>
-      </c>
-      <c r="H613" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I613" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J613" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K613" s="2" t="s">
-        <v>779</v>
       </c>
     </row>
     <row r="614" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24776,7 +24725,7 @@
         <v>731</v>
       </c>
       <c r="B614" s="3">
-        <v>735000</v>
+        <v>1250000</v>
       </c>
       <c r="C614" s="2">
         <v>2</v>
@@ -24785,16 +24734,16 @@
         <v>1</v>
       </c>
       <c r="E614" s="2">
-        <v>66</v>
+        <v>84.27</v>
       </c>
       <c r="F614" s="4">
         <f>B614/E614</f>
       </c>
       <c r="G614" s="2" t="s">
-        <v>109</v>
+        <v>776</v>
       </c>
       <c r="H614" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="I614" s="2" t="s">
         <v>13</v>
@@ -24803,7 +24752,7 @@
         <v>14</v>
       </c>
       <c r="K614" s="2" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="615" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24811,25 +24760,25 @@
         <v>731</v>
       </c>
       <c r="B615" s="3">
-        <v>735000</v>
+        <v>1295000</v>
       </c>
       <c r="C615" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D615" s="2">
         <v>1</v>
       </c>
       <c r="E615" s="2">
-        <v>66</v>
+        <v>204.88</v>
       </c>
       <c r="F615" s="4">
         <f>B615/E615</f>
       </c>
       <c r="G615" s="2" t="s">
-        <v>109</v>
+        <v>776</v>
       </c>
       <c r="H615" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="I615" s="2" t="s">
         <v>13</v>
@@ -24838,7 +24787,7 @@
         <v>14</v>
       </c>
       <c r="K615" s="2" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="616" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24846,34 +24795,34 @@
         <v>731</v>
       </c>
       <c r="B616" s="3">
-        <v>1290000</v>
+        <v>410000</v>
       </c>
       <c r="C616" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D616" s="2">
         <v>1</v>
       </c>
       <c r="E616" s="2">
-        <v>105.32</v>
+        <v>40.82</v>
       </c>
       <c r="F616" s="4">
         <f>B616/E616</f>
       </c>
       <c r="G616" s="2" t="s">
-        <v>109</v>
+        <v>776</v>
       </c>
       <c r="H616" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="I616" s="2" t="s">
         <v>13</v>
       </c>
       <c r="J616" s="2" t="s">
-        <v>14</v>
+        <v>214</v>
       </c>
       <c r="K616" s="2" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="617" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24881,22 +24830,22 @@
         <v>731</v>
       </c>
       <c r="B617" s="3">
-        <v>2150000</v>
+        <v>1070000</v>
       </c>
       <c r="C617" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D617" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E617" s="2">
-        <v>160.24</v>
+        <v>95.22</v>
       </c>
       <c r="F617" s="4">
         <f>B617/E617</f>
       </c>
       <c r="G617" s="2" t="s">
-        <v>109</v>
+        <v>776</v>
       </c>
       <c r="H617" s="2" t="s">
         <v>214</v>
@@ -24908,7 +24857,7 @@
         <v>14</v>
       </c>
       <c r="K617" s="2" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="618" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24916,32 +24865,34 @@
         <v>731</v>
       </c>
       <c r="B618" s="3">
-        <v>350000</v>
-      </c>
-      <c r="C618" s="2"/>
+        <v>8925000</v>
+      </c>
+      <c r="C618" s="2">
+        <v>8</v>
+      </c>
       <c r="D618" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E618" s="2">
-        <v>32.99</v>
+        <v>522.37</v>
       </c>
       <c r="F618" s="4">
         <f>B618/E618</f>
       </c>
       <c r="G618" s="2" t="s">
-        <v>109</v>
+        <v>776</v>
       </c>
       <c r="H618" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="I618" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="J618" s="2" t="s">
         <v>14</v>
       </c>
       <c r="K618" s="2" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="619" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -24949,25 +24900,25 @@
         <v>731</v>
       </c>
       <c r="B619" s="3">
-        <v>2290000</v>
+        <v>1295000</v>
       </c>
       <c r="C619" s="2">
+        <v>4</v>
+      </c>
+      <c r="D619" s="2">
         <v>3</v>
       </c>
-      <c r="D619" s="2">
-        <v>1</v>
-      </c>
       <c r="E619" s="2">
-        <v>134</v>
+        <v>174.35</v>
       </c>
       <c r="F619" s="4">
         <f>B619/E619</f>
       </c>
       <c r="G619" s="2" t="s">
-        <v>109</v>
+        <v>784</v>
       </c>
       <c r="H619" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="I619" s="2" t="s">
         <v>13</v>
@@ -24984,16 +24935,16 @@
         <v>731</v>
       </c>
       <c r="B620" s="3">
-        <v>2295000</v>
+        <v>735000</v>
       </c>
       <c r="C620" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D620" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E620" s="2">
-        <v>172.78</v>
+        <v>66</v>
       </c>
       <c r="F620" s="4">
         <f>B620/E620</f>
@@ -25019,14 +24970,16 @@
         <v>731</v>
       </c>
       <c r="B621" s="3">
-        <v>2575000</v>
-      </c>
-      <c r="C621" s="2"/>
+        <v>735000</v>
+      </c>
+      <c r="C621" s="2">
+        <v>2</v>
+      </c>
       <c r="D621" s="2">
         <v>1</v>
       </c>
       <c r="E621" s="2">
-        <v>170.9</v>
+        <v>66</v>
       </c>
       <c r="F621" s="4">
         <f>B621/E621</f>
@@ -25052,12 +25005,16 @@
         <v>731</v>
       </c>
       <c r="B622" s="3">
-        <v>306275</v>
-      </c>
-      <c r="C622" s="2"/>
-      <c r="D622" s="2"/>
+        <v>1290000</v>
+      </c>
+      <c r="C622" s="2">
+        <v>2</v>
+      </c>
+      <c r="D622" s="2">
+        <v>1</v>
+      </c>
       <c r="E622" s="2">
-        <v>20.4</v>
+        <v>105.32</v>
       </c>
       <c r="F622" s="4">
         <f>B622/E622</f>
@@ -25083,14 +25040,16 @@
         <v>731</v>
       </c>
       <c r="B623" s="3">
-        <v>1883000</v>
-      </c>
-      <c r="C623" s="2"/>
+        <v>2150000</v>
+      </c>
+      <c r="C623" s="2">
+        <v>4</v>
+      </c>
       <c r="D623" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E623" s="2">
-        <v>126</v>
+        <v>160.24</v>
       </c>
       <c r="F623" s="4">
         <f>B623/E623</f>
@@ -25116,12 +25075,14 @@
         <v>731</v>
       </c>
       <c r="B624" s="3">
-        <v>1919950</v>
+        <v>350000</v>
       </c>
       <c r="C624" s="2"/>
-      <c r="D624" s="2"/>
+      <c r="D624" s="2">
+        <v>1</v>
+      </c>
       <c r="E624" s="2">
-        <v>135.1</v>
+        <v>32.99</v>
       </c>
       <c r="F624" s="4">
         <f>B624/E624</f>
@@ -25133,7 +25094,7 @@
         <v>214</v>
       </c>
       <c r="I624" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="J624" s="2" t="s">
         <v>14</v>
@@ -25147,12 +25108,16 @@
         <v>731</v>
       </c>
       <c r="B625" s="3">
-        <v>2269400</v>
-      </c>
-      <c r="C625" s="2"/>
-      <c r="D625" s="2"/>
+        <v>2290000</v>
+      </c>
+      <c r="C625" s="2">
+        <v>3</v>
+      </c>
+      <c r="D625" s="2">
+        <v>1</v>
+      </c>
       <c r="E625" s="2">
-        <v>160.6</v>
+        <v>134</v>
       </c>
       <c r="F625" s="4">
         <f>B625/E625</f>
@@ -25178,12 +25143,16 @@
         <v>731</v>
       </c>
       <c r="B626" s="3">
-        <v>2328550</v>
-      </c>
-      <c r="C626" s="2"/>
-      <c r="D626" s="2"/>
+        <v>2295000</v>
+      </c>
+      <c r="C626" s="2">
+        <v>3</v>
+      </c>
+      <c r="D626" s="2">
+        <v>2</v>
+      </c>
       <c r="E626" s="2">
-        <v>158</v>
+        <v>172.78</v>
       </c>
       <c r="F626" s="4">
         <f>B626/E626</f>
@@ -25209,16 +25178,14 @@
         <v>731</v>
       </c>
       <c r="B627" s="3">
-        <v>1275000</v>
-      </c>
-      <c r="C627" s="2">
-        <v>3</v>
-      </c>
+        <v>2575000</v>
+      </c>
+      <c r="C627" s="2"/>
       <c r="D627" s="2">
         <v>1</v>
       </c>
       <c r="E627" s="2">
-        <v>109.85</v>
+        <v>170.9</v>
       </c>
       <c r="F627" s="4">
         <f>B627/E627</f>
@@ -25230,7 +25197,7 @@
         <v>214</v>
       </c>
       <c r="I627" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="J627" s="2" t="s">
         <v>14</v>
@@ -25244,16 +25211,12 @@
         <v>731</v>
       </c>
       <c r="B628" s="3">
-        <v>1750000</v>
-      </c>
-      <c r="C628" s="2">
-        <v>5</v>
-      </c>
-      <c r="D628" s="2">
-        <v>1</v>
-      </c>
+        <v>306275</v>
+      </c>
+      <c r="C628" s="2"/>
+      <c r="D628" s="2"/>
       <c r="E628" s="2">
-        <v>159.85</v>
+        <v>20.4</v>
       </c>
       <c r="F628" s="4">
         <f>B628/E628</f>
@@ -25265,7 +25228,7 @@
         <v>214</v>
       </c>
       <c r="I628" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="J628" s="2" t="s">
         <v>14</v>
@@ -25279,16 +25242,14 @@
         <v>731</v>
       </c>
       <c r="B629" s="3">
-        <v>798000</v>
-      </c>
-      <c r="C629" s="2">
-        <v>2</v>
-      </c>
+        <v>1883000</v>
+      </c>
+      <c r="C629" s="2"/>
       <c r="D629" s="2">
         <v>1</v>
       </c>
       <c r="E629" s="2">
-        <v>73.88</v>
+        <v>126</v>
       </c>
       <c r="F629" s="4">
         <f>B629/E629</f>
@@ -25314,16 +25275,12 @@
         <v>731</v>
       </c>
       <c r="B630" s="3">
-        <v>639000</v>
-      </c>
-      <c r="C630" s="2">
-        <v>2</v>
-      </c>
-      <c r="D630" s="2">
-        <v>1</v>
-      </c>
+        <v>1919950</v>
+      </c>
+      <c r="C630" s="2"/>
+      <c r="D630" s="2"/>
       <c r="E630" s="2">
-        <v>70.51</v>
+        <v>135.1</v>
       </c>
       <c r="F630" s="4">
         <f>B630/E630</f>
@@ -25335,7 +25292,7 @@
         <v>214</v>
       </c>
       <c r="I630" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="J630" s="2" t="s">
         <v>14</v>
@@ -25349,16 +25306,12 @@
         <v>731</v>
       </c>
       <c r="B631" s="3">
-        <v>289000</v>
-      </c>
-      <c r="C631" s="2">
-        <v>1</v>
-      </c>
-      <c r="D631" s="2">
-        <v>1</v>
-      </c>
+        <v>2269400</v>
+      </c>
+      <c r="C631" s="2"/>
+      <c r="D631" s="2"/>
       <c r="E631" s="2">
-        <v>31.86</v>
+        <v>160.6</v>
       </c>
       <c r="F631" s="4">
         <f>B631/E631</f>
@@ -25367,7 +25320,7 @@
         <v>109</v>
       </c>
       <c r="H631" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="I631" s="2" t="s">
         <v>13</v>
@@ -25384,12 +25337,12 @@
         <v>731</v>
       </c>
       <c r="B632" s="3">
-        <v>2533950</v>
+        <v>2328550</v>
       </c>
       <c r="C632" s="2"/>
       <c r="D632" s="2"/>
       <c r="E632" s="2">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="F632" s="4">
         <f>B632/E632</f>
@@ -25401,7 +25354,7 @@
         <v>214</v>
       </c>
       <c r="I632" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="J632" s="2" t="s">
         <v>14</v>
@@ -25415,14 +25368,16 @@
         <v>731</v>
       </c>
       <c r="B633" s="3">
-        <v>2404300</v>
-      </c>
-      <c r="C633" s="2"/>
+        <v>1275000</v>
+      </c>
+      <c r="C633" s="2">
+        <v>3</v>
+      </c>
       <c r="D633" s="2">
         <v>1</v>
       </c>
       <c r="E633" s="2">
-        <v>170.7</v>
+        <v>109.85</v>
       </c>
       <c r="F633" s="4">
         <f>B633/E633</f>
@@ -25434,7 +25389,7 @@
         <v>214</v>
       </c>
       <c r="I633" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="J633" s="2" t="s">
         <v>14</v>
@@ -25448,14 +25403,16 @@
         <v>731</v>
       </c>
       <c r="B634" s="3">
-        <v>172000</v>
-      </c>
-      <c r="C634" s="2"/>
+        <v>1750000</v>
+      </c>
+      <c r="C634" s="2">
+        <v>5</v>
+      </c>
       <c r="D634" s="2">
         <v>1</v>
       </c>
       <c r="E634" s="2">
-        <v>15.56</v>
+        <v>159.85</v>
       </c>
       <c r="F634" s="4">
         <f>B634/E634</f>
@@ -25467,7 +25424,7 @@
         <v>214</v>
       </c>
       <c r="I634" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="J634" s="2" t="s">
         <v>14</v>
@@ -25481,16 +25438,16 @@
         <v>731</v>
       </c>
       <c r="B635" s="3">
-        <v>2790000</v>
+        <v>798000</v>
       </c>
       <c r="C635" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D635" s="2">
         <v>1</v>
       </c>
       <c r="E635" s="2">
-        <v>160.32</v>
+        <v>73.88</v>
       </c>
       <c r="F635" s="4">
         <f>B635/E635</f>
@@ -25516,16 +25473,16 @@
         <v>731</v>
       </c>
       <c r="B636" s="3">
-        <v>470000</v>
+        <v>639000</v>
       </c>
       <c r="C636" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D636" s="2">
         <v>1</v>
       </c>
       <c r="E636" s="2">
-        <v>40.48</v>
+        <v>70.51</v>
       </c>
       <c r="F636" s="4">
         <f>B636/E636</f>
@@ -25534,10 +25491,10 @@
         <v>109</v>
       </c>
       <c r="H636" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="I636" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="J636" s="2" t="s">
         <v>14</v>
@@ -25551,12 +25508,16 @@
         <v>731</v>
       </c>
       <c r="B637" s="3">
-        <v>2526150</v>
-      </c>
-      <c r="C637" s="2"/>
-      <c r="D637" s="2"/>
+        <v>289000</v>
+      </c>
+      <c r="C637" s="2">
+        <v>1</v>
+      </c>
+      <c r="D637" s="2">
+        <v>1</v>
+      </c>
       <c r="E637" s="2">
-        <v>169</v>
+        <v>31.86</v>
       </c>
       <c r="F637" s="4">
         <f>B637/E637</f>
@@ -25565,10 +25526,10 @@
         <v>109</v>
       </c>
       <c r="H637" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="I637" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="J637" s="2" t="s">
         <v>14</v>
@@ -25582,34 +25543,30 @@
         <v>731</v>
       </c>
       <c r="B638" s="3">
-        <v>2400000</v>
-      </c>
-      <c r="C638" s="2">
-        <v>7</v>
-      </c>
-      <c r="D638" s="2">
-        <v>1</v>
-      </c>
+        <v>2533950</v>
+      </c>
+      <c r="C638" s="2"/>
+      <c r="D638" s="2"/>
       <c r="E638" s="2">
-        <v>243.61</v>
+        <v>171</v>
       </c>
       <c r="F638" s="4">
         <f>B638/E638</f>
       </c>
       <c r="G638" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="H638" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="I638" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="J638" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K638" s="2" t="s">
         <v>804</v>
-      </c>
-      <c r="H638" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I638" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J638" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K638" s="2" t="s">
-        <v>805</v>
       </c>
     </row>
     <row r="639" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25617,25 +25574,23 @@
         <v>731</v>
       </c>
       <c r="B639" s="3">
-        <v>1350000</v>
-      </c>
-      <c r="C639" s="2">
-        <v>4</v>
-      </c>
+        <v>2404300</v>
+      </c>
+      <c r="C639" s="2"/>
       <c r="D639" s="2">
         <v>1</v>
       </c>
       <c r="E639" s="2">
-        <v>170</v>
+        <v>170.7</v>
       </c>
       <c r="F639" s="4">
         <f>B639/E639</f>
       </c>
       <c r="G639" s="2" t="s">
-        <v>806</v>
+        <v>109</v>
       </c>
       <c r="H639" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="I639" s="2" t="s">
         <v>13</v>
@@ -25644,7 +25599,7 @@
         <v>14</v>
       </c>
       <c r="K639" s="2" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
     </row>
     <row r="640" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25652,34 +25607,32 @@
         <v>731</v>
       </c>
       <c r="B640" s="3">
-        <v>1300000</v>
-      </c>
-      <c r="C640" s="2">
-        <v>5</v>
-      </c>
+        <v>172000</v>
+      </c>
+      <c r="C640" s="2"/>
       <c r="D640" s="2">
         <v>1</v>
       </c>
       <c r="E640" s="2">
-        <v>181.93</v>
+        <v>15.56</v>
       </c>
       <c r="F640" s="4">
         <f>B640/E640</f>
       </c>
       <c r="G640" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="H640" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="I640" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J640" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K640" s="2" t="s">
         <v>806</v>
-      </c>
-      <c r="H640" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I640" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J640" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K640" s="2" t="s">
-        <v>808</v>
       </c>
     </row>
     <row r="641" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25687,25 +25640,25 @@
         <v>731</v>
       </c>
       <c r="B641" s="3">
-        <v>780000</v>
+        <v>2790000</v>
       </c>
       <c r="C641" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D641" s="2">
         <v>1</v>
       </c>
       <c r="E641" s="2">
-        <v>130.94</v>
+        <v>160.32</v>
       </c>
       <c r="F641" s="4">
         <f>B641/E641</f>
       </c>
       <c r="G641" s="2" t="s">
-        <v>806</v>
+        <v>109</v>
       </c>
       <c r="H641" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="I641" s="2" t="s">
         <v>13</v>
@@ -25714,7 +25667,7 @@
         <v>14</v>
       </c>
       <c r="K641" s="2" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
     </row>
     <row r="642" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25722,22 +25675,22 @@
         <v>731</v>
       </c>
       <c r="B642" s="3">
-        <v>990000</v>
+        <v>470000</v>
       </c>
       <c r="C642" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D642" s="2">
         <v>1</v>
       </c>
       <c r="E642" s="2">
-        <v>130.24</v>
+        <v>40.48</v>
       </c>
       <c r="F642" s="4">
         <f>B642/E642</f>
       </c>
       <c r="G642" s="2" t="s">
-        <v>806</v>
+        <v>109</v>
       </c>
       <c r="H642" s="2" t="s">
         <v>13</v>
@@ -25749,7 +25702,7 @@
         <v>14</v>
       </c>
       <c r="K642" s="2" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
     </row>
     <row r="643" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25757,34 +25710,30 @@
         <v>731</v>
       </c>
       <c r="B643" s="3">
-        <v>985000</v>
-      </c>
-      <c r="C643" s="2">
-        <v>3</v>
-      </c>
-      <c r="D643" s="2">
-        <v>1</v>
-      </c>
+        <v>2526150</v>
+      </c>
+      <c r="C643" s="2"/>
+      <c r="D643" s="2"/>
       <c r="E643" s="2">
-        <v>141.58</v>
+        <v>169</v>
       </c>
       <c r="F643" s="4">
         <f>B643/E643</f>
       </c>
       <c r="G643" s="2" t="s">
-        <v>806</v>
+        <v>109</v>
       </c>
       <c r="H643" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="I643" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="J643" s="2" t="s">
         <v>14</v>
       </c>
       <c r="K643" s="2" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
     </row>
     <row r="644" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25792,22 +25741,22 @@
         <v>731</v>
       </c>
       <c r="B644" s="3">
-        <v>875000</v>
+        <v>2400000</v>
       </c>
       <c r="C644" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D644" s="2">
         <v>1</v>
       </c>
       <c r="E644" s="2">
-        <v>109.85</v>
+        <v>243.61</v>
       </c>
       <c r="F644" s="4">
         <f>B644/E644</f>
       </c>
       <c r="G644" s="2" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="H644" s="2" t="s">
         <v>13</v>
@@ -25819,7 +25768,7 @@
         <v>14</v>
       </c>
       <c r="K644" s="2" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="645" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25827,22 +25776,22 @@
         <v>731</v>
       </c>
       <c r="B645" s="3">
-        <v>650000</v>
+        <v>1320000</v>
       </c>
       <c r="C645" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D645" s="2">
         <v>1</v>
       </c>
       <c r="E645" s="2">
-        <v>153.4</v>
+        <v>169.3</v>
       </c>
       <c r="F645" s="4">
         <f>B645/E645</f>
       </c>
       <c r="G645" s="2" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="H645" s="2" t="s">
         <v>13</v>
@@ -25854,7 +25803,7 @@
         <v>14</v>
       </c>
       <c r="K645" s="2" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="646" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25862,22 +25811,22 @@
         <v>731</v>
       </c>
       <c r="B646" s="3">
-        <v>740000</v>
+        <v>1390000</v>
       </c>
       <c r="C646" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D646" s="2">
         <v>1</v>
       </c>
       <c r="E646" s="2">
-        <v>118.44</v>
+        <v>161.32</v>
       </c>
       <c r="F646" s="4">
         <f>B646/E646</f>
       </c>
       <c r="G646" s="2" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="H646" s="2" t="s">
         <v>13</v>
@@ -25889,7 +25838,7 @@
         <v>14</v>
       </c>
       <c r="K646" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="647" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25897,22 +25846,22 @@
         <v>731</v>
       </c>
       <c r="B647" s="3">
-        <v>1350000</v>
+        <v>3290000</v>
       </c>
       <c r="C647" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D647" s="2">
         <v>1</v>
       </c>
       <c r="E647" s="2">
-        <v>258.62</v>
+        <v>430.3</v>
       </c>
       <c r="F647" s="4">
         <f>B647/E647</f>
       </c>
       <c r="G647" s="2" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="H647" s="2" t="s">
         <v>13</v>
@@ -25924,7 +25873,7 @@
         <v>14</v>
       </c>
       <c r="K647" s="2" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="648" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25932,22 +25881,22 @@
         <v>731</v>
       </c>
       <c r="B648" s="3">
-        <v>1195000</v>
+        <v>1200000</v>
       </c>
       <c r="C648" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D648" s="2">
         <v>1</v>
       </c>
       <c r="E648" s="2">
-        <v>193.27</v>
+        <v>154.49</v>
       </c>
       <c r="F648" s="4">
         <f>B648/E648</f>
       </c>
       <c r="G648" s="2" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="H648" s="2" t="s">
         <v>13</v>
@@ -25959,7 +25908,7 @@
         <v>14</v>
       </c>
       <c r="K648" s="2" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="649" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25967,22 +25916,22 @@
         <v>731</v>
       </c>
       <c r="B649" s="3">
-        <v>1150000</v>
+        <v>2700000</v>
       </c>
       <c r="C649" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D649" s="2">
         <v>1</v>
       </c>
       <c r="E649" s="2">
-        <v>117.15</v>
+        <v>328.59</v>
       </c>
       <c r="F649" s="4">
         <f>B649/E649</f>
       </c>
       <c r="G649" s="2" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="H649" s="2" t="s">
         <v>13</v>
@@ -25994,7 +25943,7 @@
         <v>14</v>
       </c>
       <c r="K649" s="2" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="650" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26002,25 +25951,25 @@
         <v>731</v>
       </c>
       <c r="B650" s="3">
-        <v>995000</v>
+        <v>1350000</v>
       </c>
       <c r="C650" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D650" s="2">
         <v>1</v>
       </c>
       <c r="E650" s="2">
-        <v>109.07</v>
+        <v>170</v>
       </c>
       <c r="F650" s="4">
         <f>B650/E650</f>
       </c>
       <c r="G650" s="2" t="s">
-        <v>806</v>
+        <v>817</v>
       </c>
       <c r="H650" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="I650" s="2" t="s">
         <v>13</v>
@@ -26037,25 +25986,25 @@
         <v>731</v>
       </c>
       <c r="B651" s="3">
-        <v>1090000</v>
+        <v>1300000</v>
       </c>
       <c r="C651" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D651" s="2">
         <v>1</v>
       </c>
       <c r="E651" s="2">
-        <v>138.13</v>
+        <v>181.93</v>
       </c>
       <c r="F651" s="4">
         <f>B651/E651</f>
       </c>
       <c r="G651" s="2" t="s">
-        <v>806</v>
+        <v>817</v>
       </c>
       <c r="H651" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="I651" s="2" t="s">
         <v>13</v>
@@ -26072,22 +26021,22 @@
         <v>731</v>
       </c>
       <c r="B652" s="3">
-        <v>1100000</v>
+        <v>780000</v>
       </c>
       <c r="C652" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D652" s="2">
         <v>1</v>
       </c>
       <c r="E652" s="2">
-        <v>183</v>
+        <v>130.94</v>
       </c>
       <c r="F652" s="4">
         <f>B652/E652</f>
       </c>
       <c r="G652" s="2" t="s">
-        <v>806</v>
+        <v>817</v>
       </c>
       <c r="H652" s="2" t="s">
         <v>13</v>
@@ -26107,28 +26056,28 @@
         <v>731</v>
       </c>
       <c r="B653" s="3">
-        <v>650000</v>
+        <v>990000</v>
       </c>
       <c r="C653" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D653" s="2">
         <v>1</v>
       </c>
       <c r="E653" s="2">
-        <v>86.77</v>
+        <v>130.24</v>
       </c>
       <c r="F653" s="4">
         <f>B653/E653</f>
       </c>
       <c r="G653" s="2" t="s">
-        <v>806</v>
+        <v>817</v>
       </c>
       <c r="H653" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="I653" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="J653" s="2" t="s">
         <v>14</v>
@@ -26142,25 +26091,25 @@
         <v>731</v>
       </c>
       <c r="B654" s="3">
-        <v>375000</v>
+        <v>985000</v>
       </c>
       <c r="C654" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D654" s="2">
         <v>1</v>
       </c>
       <c r="E654" s="2">
-        <v>53.33</v>
+        <v>141.58</v>
       </c>
       <c r="F654" s="4">
         <f>B654/E654</f>
       </c>
       <c r="G654" s="2" t="s">
-        <v>806</v>
+        <v>817</v>
       </c>
       <c r="H654" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="I654" s="2" t="s">
         <v>13</v>
@@ -26177,22 +26126,22 @@
         <v>731</v>
       </c>
       <c r="B655" s="3">
-        <v>1190000</v>
+        <v>875000</v>
       </c>
       <c r="C655" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D655" s="2">
         <v>1</v>
       </c>
       <c r="E655" s="2">
-        <v>247</v>
+        <v>109.85</v>
       </c>
       <c r="F655" s="4">
         <f>B655/E655</f>
       </c>
       <c r="G655" s="2" t="s">
-        <v>806</v>
+        <v>817</v>
       </c>
       <c r="H655" s="2" t="s">
         <v>13</v>
@@ -26212,28 +26161,28 @@
         <v>731</v>
       </c>
       <c r="B656" s="3">
-        <v>385000</v>
+        <v>650000</v>
       </c>
       <c r="C656" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D656" s="2">
         <v>1</v>
       </c>
       <c r="E656" s="2">
-        <v>76.56</v>
+        <v>153.4</v>
       </c>
       <c r="F656" s="4">
         <f>B656/E656</f>
       </c>
       <c r="G656" s="2" t="s">
-        <v>806</v>
+        <v>817</v>
       </c>
       <c r="H656" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I656" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="J656" s="2" t="s">
         <v>14</v>
@@ -26247,7 +26196,7 @@
         <v>731</v>
       </c>
       <c r="B657" s="3">
-        <v>1260000</v>
+        <v>740000</v>
       </c>
       <c r="C657" s="2">
         <v>4</v>
@@ -26256,13 +26205,13 @@
         <v>1</v>
       </c>
       <c r="E657" s="2">
-        <v>168</v>
+        <v>118.44</v>
       </c>
       <c r="F657" s="4">
         <f>B657/E657</f>
       </c>
       <c r="G657" s="2" t="s">
-        <v>806</v>
+        <v>817</v>
       </c>
       <c r="H657" s="2" t="s">
         <v>13</v>
@@ -26282,22 +26231,22 @@
         <v>731</v>
       </c>
       <c r="B658" s="3">
-        <v>1180000</v>
+        <v>1350000</v>
       </c>
       <c r="C658" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D658" s="2">
         <v>1</v>
       </c>
       <c r="E658" s="2">
-        <v>228</v>
+        <v>258.62</v>
       </c>
       <c r="F658" s="4">
         <f>B658/E658</f>
       </c>
       <c r="G658" s="2" t="s">
-        <v>806</v>
+        <v>817</v>
       </c>
       <c r="H658" s="2" t="s">
         <v>13</v>
@@ -26317,28 +26266,28 @@
         <v>731</v>
       </c>
       <c r="B659" s="3">
-        <v>330000</v>
+        <v>1195000</v>
       </c>
       <c r="C659" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D659" s="2">
         <v>1</v>
       </c>
       <c r="E659" s="2">
-        <v>57.74</v>
+        <v>193.27</v>
       </c>
       <c r="F659" s="4">
         <f>B659/E659</f>
       </c>
       <c r="G659" s="2" t="s">
-        <v>806</v>
+        <v>817</v>
       </c>
       <c r="H659" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="I659" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="J659" s="2" t="s">
         <v>14</v>
@@ -26352,22 +26301,22 @@
         <v>731</v>
       </c>
       <c r="B660" s="3">
-        <v>600000</v>
+        <v>1150000</v>
       </c>
       <c r="C660" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D660" s="2">
         <v>1</v>
       </c>
       <c r="E660" s="2">
-        <v>90.46</v>
+        <v>117.15</v>
       </c>
       <c r="F660" s="4">
         <f>B660/E660</f>
       </c>
       <c r="G660" s="2" t="s">
-        <v>806</v>
+        <v>817</v>
       </c>
       <c r="H660" s="2" t="s">
         <v>13</v>
@@ -26387,28 +26336,28 @@
         <v>731</v>
       </c>
       <c r="B661" s="3">
-        <v>395000</v>
+        <v>995000</v>
       </c>
       <c r="C661" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D661" s="2">
         <v>1</v>
       </c>
       <c r="E661" s="2">
-        <v>42.95</v>
+        <v>109.07</v>
       </c>
       <c r="F661" s="4">
         <f>B661/E661</f>
       </c>
       <c r="G661" s="2" t="s">
-        <v>12</v>
+        <v>817</v>
       </c>
       <c r="H661" s="2" t="s">
         <v>214</v>
       </c>
       <c r="I661" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="J661" s="2" t="s">
         <v>14</v>
@@ -26422,16 +26371,16 @@
         <v>731</v>
       </c>
       <c r="B662" s="3">
-        <v>2700000</v>
+        <v>395000</v>
       </c>
       <c r="C662" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D662" s="2">
         <v>1</v>
       </c>
       <c r="E662" s="2">
-        <v>250</v>
+        <v>42.95</v>
       </c>
       <c r="F662" s="4">
         <f>B662/E662</f>
@@ -26440,10 +26389,10 @@
         <v>12</v>
       </c>
       <c r="H662" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="I662" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="J662" s="2" t="s">
         <v>14</v>
@@ -26457,14 +26406,16 @@
         <v>731</v>
       </c>
       <c r="B663" s="3">
-        <v>120000</v>
+        <v>2700000</v>
       </c>
       <c r="C663" s="2">
-        <v>1</v>
-      </c>
-      <c r="D663" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="D663" s="2">
+        <v>1</v>
+      </c>
       <c r="E663" s="2">
-        <v>9.56</v>
+        <v>250</v>
       </c>
       <c r="F663" s="4">
         <f>B663/E663</f>
@@ -26490,16 +26441,14 @@
         <v>731</v>
       </c>
       <c r="B664" s="3">
-        <v>455000</v>
+        <v>120000</v>
       </c>
       <c r="C664" s="2">
         <v>1</v>
       </c>
-      <c r="D664" s="2">
-        <v>1</v>
-      </c>
+      <c r="D664" s="2"/>
       <c r="E664" s="2">
-        <v>41.51</v>
+        <v>9.56</v>
       </c>
       <c r="F664" s="4">
         <f>B664/E664</f>
@@ -26508,7 +26457,7 @@
         <v>12</v>
       </c>
       <c r="H664" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="I664" s="2" t="s">
         <v>13</v>
@@ -26525,7 +26474,7 @@
         <v>731</v>
       </c>
       <c r="B665" s="3">
-        <v>569000</v>
+        <v>455000</v>
       </c>
       <c r="C665" s="2">
         <v>1</v>
@@ -26534,7 +26483,7 @@
         <v>1</v>
       </c>
       <c r="E665" s="2">
-        <v>53.14</v>
+        <v>41.51</v>
       </c>
       <c r="F665" s="4">
         <f>B665/E665</f>
@@ -26560,16 +26509,16 @@
         <v>731</v>
       </c>
       <c r="B666" s="3">
-        <v>2950000</v>
+        <v>569000</v>
       </c>
       <c r="C666" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D666" s="2">
         <v>1</v>
       </c>
       <c r="E666" s="2">
-        <v>191.04</v>
+        <v>53.14</v>
       </c>
       <c r="F666" s="4">
         <f>B666/E666</f>
@@ -26578,7 +26527,7 @@
         <v>12</v>
       </c>
       <c r="H666" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="I666" s="2" t="s">
         <v>13</v>
@@ -26595,16 +26544,16 @@
         <v>731</v>
       </c>
       <c r="B667" s="3">
-        <v>1790000</v>
+        <v>2950000</v>
       </c>
       <c r="C667" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D667" s="2">
         <v>1</v>
       </c>
       <c r="E667" s="2">
-        <v>91.08</v>
+        <v>191.04</v>
       </c>
       <c r="F667" s="4">
         <f>B667/E667</f>
@@ -26613,7 +26562,7 @@
         <v>12</v>
       </c>
       <c r="H667" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="I667" s="2" t="s">
         <v>13</v>
@@ -26630,25 +26579,25 @@
         <v>731</v>
       </c>
       <c r="B668" s="3">
-        <v>950000</v>
+        <v>1790000</v>
       </c>
       <c r="C668" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D668" s="2">
         <v>1</v>
       </c>
       <c r="E668" s="2">
-        <v>114.21</v>
+        <v>91.08</v>
       </c>
       <c r="F668" s="4">
         <f>B668/E668</f>
       </c>
       <c r="G668" s="2" t="s">
-        <v>115</v>
+        <v>12</v>
       </c>
       <c r="H668" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="I668" s="2" t="s">
         <v>13</v>
@@ -26665,16 +26614,16 @@
         <v>731</v>
       </c>
       <c r="B669" s="3">
-        <v>550000</v>
+        <v>950000</v>
       </c>
       <c r="C669" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D669" s="2">
         <v>1</v>
       </c>
       <c r="E669" s="2">
-        <v>83.1</v>
+        <v>114.21</v>
       </c>
       <c r="F669" s="4">
         <f>B669/E669</f>
@@ -26700,7 +26649,7 @@
         <v>731</v>
       </c>
       <c r="B670" s="3">
-        <v>630000</v>
+        <v>550000</v>
       </c>
       <c r="C670" s="2">
         <v>3</v>
@@ -26709,7 +26658,7 @@
         <v>1</v>
       </c>
       <c r="E670" s="2">
-        <v>89.66</v>
+        <v>83.1</v>
       </c>
       <c r="F670" s="4">
         <f>B670/E670</f>
@@ -26718,10 +26667,10 @@
         <v>115</v>
       </c>
       <c r="H670" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="I670" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="J670" s="2" t="s">
         <v>14</v>
@@ -26735,7 +26684,7 @@
         <v>731</v>
       </c>
       <c r="B671" s="3">
-        <v>675000</v>
+        <v>630000</v>
       </c>
       <c r="C671" s="2">
         <v>3</v>
@@ -26744,7 +26693,7 @@
         <v>1</v>
       </c>
       <c r="E671" s="2">
-        <v>75</v>
+        <v>89.66</v>
       </c>
       <c r="F671" s="4">
         <f>B671/E671</f>
@@ -26753,10 +26702,10 @@
         <v>115</v>
       </c>
       <c r="H671" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="I671" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="J671" s="2" t="s">
         <v>14</v>
@@ -26770,16 +26719,16 @@
         <v>731</v>
       </c>
       <c r="B672" s="3">
-        <v>1250000</v>
+        <v>330000</v>
       </c>
       <c r="C672" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D672" s="2">
         <v>1</v>
       </c>
       <c r="E672" s="2">
-        <v>184</v>
+        <v>57.74</v>
       </c>
       <c r="F672" s="4">
         <f>B672/E672</f>
@@ -26788,10 +26737,10 @@
         <v>115</v>
       </c>
       <c r="H672" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="I672" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="J672" s="2" t="s">
         <v>14</v>
@@ -26805,7 +26754,7 @@
         <v>731</v>
       </c>
       <c r="B673" s="3">
-        <v>845000</v>
+        <v>675000</v>
       </c>
       <c r="C673" s="2">
         <v>3</v>
@@ -26814,7 +26763,7 @@
         <v>1</v>
       </c>
       <c r="E673" s="2">
-        <v>98.06</v>
+        <v>75</v>
       </c>
       <c r="F673" s="4">
         <f>B673/E673</f>
@@ -26840,7 +26789,7 @@
         <v>731</v>
       </c>
       <c r="B674" s="3">
-        <v>1150000</v>
+        <v>1250000</v>
       </c>
       <c r="C674" s="2">
         <v>5</v>
@@ -26849,7 +26798,7 @@
         <v>1</v>
       </c>
       <c r="E674" s="2">
-        <v>170.15</v>
+        <v>184</v>
       </c>
       <c r="F674" s="4">
         <f>B674/E674</f>
@@ -26875,16 +26824,16 @@
         <v>731</v>
       </c>
       <c r="B675" s="3">
-        <v>1750000</v>
+        <v>845000</v>
       </c>
       <c r="C675" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D675" s="2">
         <v>1</v>
       </c>
       <c r="E675" s="2">
-        <v>233</v>
+        <v>98.06</v>
       </c>
       <c r="F675" s="4">
         <f>B675/E675</f>
@@ -26910,16 +26859,16 @@
         <v>731</v>
       </c>
       <c r="B676" s="3">
-        <v>950000</v>
+        <v>1150000</v>
       </c>
       <c r="C676" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D676" s="2">
         <v>1</v>
       </c>
       <c r="E676" s="2">
-        <v>114.21</v>
+        <v>170.15</v>
       </c>
       <c r="F676" s="4">
         <f>B676/E676</f>
@@ -26928,10 +26877,10 @@
         <v>115</v>
       </c>
       <c r="H676" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="I676" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="J676" s="2" t="s">
         <v>14</v>
@@ -26945,7 +26894,7 @@
         <v>731</v>
       </c>
       <c r="B677" s="3">
-        <v>1295000</v>
+        <v>1750000</v>
       </c>
       <c r="C677" s="2">
         <v>5</v>
@@ -26954,7 +26903,7 @@
         <v>1</v>
       </c>
       <c r="E677" s="2">
-        <v>204.51</v>
+        <v>233</v>
       </c>
       <c r="F677" s="4">
         <f>B677/E677</f>
@@ -26980,25 +26929,25 @@
         <v>731</v>
       </c>
       <c r="B678" s="3">
-        <v>562500</v>
+        <v>390000</v>
       </c>
       <c r="C678" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D678" s="2">
         <v>1</v>
       </c>
       <c r="E678" s="2">
-        <v>93.39</v>
+        <v>48.26</v>
       </c>
       <c r="F678" s="4">
         <f>B678/E678</f>
       </c>
       <c r="G678" s="2" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="H678" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="I678" s="2" t="s">
         <v>13</v>
@@ -27015,22 +26964,18 @@
         <v>731</v>
       </c>
       <c r="B679" s="3">
-        <v>3500000</v>
-      </c>
-      <c r="C679" s="2">
-        <v>8</v>
-      </c>
-      <c r="D679" s="2">
-        <v>4</v>
-      </c>
+        <v>1570000</v>
+      </c>
+      <c r="C679" s="2"/>
+      <c r="D679" s="2"/>
       <c r="E679" s="2">
-        <v>586.44</v>
+        <v>280.1</v>
       </c>
       <c r="F679" s="4">
         <f>B679/E679</f>
       </c>
       <c r="G679" s="2" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="H679" s="2" t="s">
         <v>13</v>
@@ -27050,28 +26995,28 @@
         <v>731</v>
       </c>
       <c r="B680" s="3">
-        <v>645000</v>
+        <v>2780000</v>
       </c>
       <c r="C680" s="2">
+        <v>11</v>
+      </c>
+      <c r="D680" s="2">
         <v>4</v>
       </c>
-      <c r="D680" s="2">
-        <v>1</v>
-      </c>
       <c r="E680" s="2">
-        <v>117.73</v>
+        <v>425.73</v>
       </c>
       <c r="F680" s="4">
         <f>B680/E680</f>
       </c>
       <c r="G680" s="2" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="H680" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I680" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="J680" s="2" t="s">
         <v>14</v>
@@ -27085,28 +27030,28 @@
         <v>731</v>
       </c>
       <c r="B681" s="3">
-        <v>3980000</v>
+        <v>2490000</v>
       </c>
       <c r="C681" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D681" s="2">
         <v>1</v>
       </c>
       <c r="E681" s="2">
-        <v>486</v>
+        <v>295</v>
       </c>
       <c r="F681" s="4">
         <f>B681/E681</f>
       </c>
       <c r="G681" s="2" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="H681" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I681" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="J681" s="2" t="s">
         <v>14</v>
@@ -27120,22 +27065,22 @@
         <v>731</v>
       </c>
       <c r="B682" s="3">
-        <v>575000</v>
+        <v>2690000</v>
       </c>
       <c r="C682" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D682" s="2">
         <v>1</v>
       </c>
       <c r="E682" s="2">
-        <v>53.95</v>
+        <v>262.48</v>
       </c>
       <c r="F682" s="4">
         <f>B682/E682</f>
       </c>
       <c r="G682" s="2" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="H682" s="2" t="s">
         <v>13</v>
@@ -27155,22 +27100,22 @@
         <v>731</v>
       </c>
       <c r="B683" s="3">
-        <v>1290000</v>
+        <v>3500000</v>
       </c>
       <c r="C683" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D683" s="2">
         <v>1</v>
       </c>
       <c r="E683" s="2">
-        <v>157</v>
+        <v>410</v>
       </c>
       <c r="F683" s="4">
         <f>B683/E683</f>
       </c>
       <c r="G683" s="2" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="H683" s="2" t="s">
         <v>13</v>
@@ -27190,7 +27135,7 @@
         <v>731</v>
       </c>
       <c r="B684" s="3">
-        <v>1250000</v>
+        <v>1190000</v>
       </c>
       <c r="C684" s="2">
         <v>3</v>
@@ -27199,19 +27144,19 @@
         <v>1</v>
       </c>
       <c r="E684" s="2">
-        <v>138</v>
+        <v>123.94</v>
       </c>
       <c r="F684" s="4">
         <f>B684/E684</f>
       </c>
       <c r="G684" s="2" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="H684" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I684" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="J684" s="2" t="s">
         <v>14</v>
@@ -27225,7 +27170,7 @@
         <v>731</v>
       </c>
       <c r="B685" s="3">
-        <v>390000</v>
+        <v>350000</v>
       </c>
       <c r="C685" s="2">
         <v>1</v>
@@ -27234,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="E685" s="2">
-        <v>48.26</v>
+        <v>54.62</v>
       </c>
       <c r="F685" s="4">
         <f>B685/E685</f>
@@ -27260,12 +27205,16 @@
         <v>731</v>
       </c>
       <c r="B686" s="3">
-        <v>1570000</v>
-      </c>
-      <c r="C686" s="2"/>
-      <c r="D686" s="2"/>
+        <v>765000</v>
+      </c>
+      <c r="C686" s="2">
+        <v>3</v>
+      </c>
+      <c r="D686" s="2">
+        <v>1</v>
+      </c>
       <c r="E686" s="2">
-        <v>280.1</v>
+        <v>135.67</v>
       </c>
       <c r="F686" s="4">
         <f>B686/E686</f>
@@ -27274,7 +27223,7 @@
         <v>136</v>
       </c>
       <c r="H686" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="I686" s="2" t="s">
         <v>13</v>
@@ -27291,16 +27240,16 @@
         <v>731</v>
       </c>
       <c r="B687" s="3">
-        <v>1200000</v>
+        <v>3550000</v>
       </c>
       <c r="C687" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D687" s="2">
         <v>1</v>
       </c>
       <c r="E687" s="2">
-        <v>154.49</v>
+        <v>370</v>
       </c>
       <c r="F687" s="4">
         <f>B687/E687</f>
@@ -27326,16 +27275,16 @@
         <v>731</v>
       </c>
       <c r="B688" s="3">
-        <v>2780000</v>
+        <v>450000</v>
       </c>
       <c r="C688" s="2">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D688" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E688" s="2">
-        <v>425.73</v>
+        <v>71</v>
       </c>
       <c r="F688" s="4">
         <f>B688/E688</f>
@@ -27361,16 +27310,16 @@
         <v>731</v>
       </c>
       <c r="B689" s="3">
-        <v>2490000</v>
+        <v>850000</v>
       </c>
       <c r="C689" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D689" s="2">
         <v>1</v>
       </c>
       <c r="E689" s="2">
-        <v>295</v>
+        <v>117</v>
       </c>
       <c r="F689" s="4">
         <f>B689/E689</f>
@@ -27396,22 +27345,22 @@
         <v>731</v>
       </c>
       <c r="B690" s="3">
-        <v>2690000</v>
+        <v>3900000</v>
       </c>
       <c r="C690" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D690" s="2">
         <v>1</v>
       </c>
       <c r="E690" s="2">
-        <v>262.48</v>
+        <v>473.78</v>
       </c>
       <c r="F690" s="4">
         <f>B690/E690</f>
       </c>
       <c r="G690" s="2" t="s">
-        <v>136</v>
+        <v>858</v>
       </c>
       <c r="H690" s="2" t="s">
         <v>13</v>
@@ -27423,7 +27372,7 @@
         <v>14</v>
       </c>
       <c r="K690" s="2" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
     </row>
     <row r="691" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27431,25 +27380,25 @@
         <v>731</v>
       </c>
       <c r="B691" s="3">
-        <v>3500000</v>
+        <v>1090000</v>
       </c>
       <c r="C691" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D691" s="2">
         <v>1</v>
       </c>
       <c r="E691" s="2">
-        <v>410</v>
+        <v>138.13</v>
       </c>
       <c r="F691" s="4">
         <f>B691/E691</f>
       </c>
       <c r="G691" s="2" t="s">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="H691" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="I691" s="2" t="s">
         <v>13</v>
@@ -27458,7 +27407,7 @@
         <v>14</v>
       </c>
       <c r="K691" s="2" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
     </row>
     <row r="692" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27466,28 +27415,28 @@
         <v>731</v>
       </c>
       <c r="B692" s="3">
-        <v>3900000</v>
+        <v>650000</v>
       </c>
       <c r="C692" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D692" s="2">
         <v>1</v>
       </c>
       <c r="E692" s="2">
-        <v>473.78</v>
+        <v>86.77</v>
       </c>
       <c r="F692" s="4">
         <f>B692/E692</f>
       </c>
       <c r="G692" s="2" t="s">
-        <v>860</v>
+        <v>97</v>
       </c>
       <c r="H692" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="I692" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="J692" s="2" t="s">
         <v>14</v>
@@ -27501,22 +27450,20 @@
         <v>731</v>
       </c>
       <c r="B693" s="3">
-        <v>1750000</v>
+        <v>1295000</v>
       </c>
       <c r="C693" s="2">
-        <v>6</v>
-      </c>
-      <c r="D693" s="2">
-        <v>1</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="D693" s="2"/>
       <c r="E693" s="2">
-        <v>533</v>
+        <v>214.39</v>
       </c>
       <c r="F693" s="4">
         <f>B693/E693</f>
       </c>
       <c r="G693" s="2" t="s">
-        <v>860</v>
+        <v>97</v>
       </c>
       <c r="H693" s="2" t="s">
         <v>13</v>
@@ -27536,22 +27483,22 @@
         <v>731</v>
       </c>
       <c r="B694" s="3">
-        <v>1295000</v>
+        <v>3500000</v>
       </c>
       <c r="C694" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D694" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E694" s="2">
-        <v>204.88</v>
+        <v>239.53</v>
       </c>
       <c r="F694" s="4">
         <f>B694/E694</f>
       </c>
       <c r="G694" s="2" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="H694" s="2" t="s">
         <v>13</v>
@@ -27563,7 +27510,7 @@
         <v>14</v>
       </c>
       <c r="K694" s="2" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
     </row>
     <row r="695" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27571,22 +27518,22 @@
         <v>731</v>
       </c>
       <c r="B695" s="3">
-        <v>1080000</v>
+        <v>2120000</v>
       </c>
       <c r="C695" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D695" s="2">
         <v>1</v>
       </c>
       <c r="E695" s="2">
-        <v>77.59</v>
+        <v>86.23</v>
       </c>
       <c r="F695" s="4">
         <f>B695/E695</f>
       </c>
       <c r="G695" s="2" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="H695" s="2" t="s">
         <v>214</v>
@@ -27598,7 +27545,7 @@
         <v>14</v>
       </c>
       <c r="K695" s="2" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
     </row>
     <row r="696" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27606,22 +27553,22 @@
         <v>731</v>
       </c>
       <c r="B696" s="3">
-        <v>2120000</v>
+        <v>1080000</v>
       </c>
       <c r="C696" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D696" s="2">
         <v>1</v>
       </c>
       <c r="E696" s="2">
-        <v>86.23</v>
+        <v>77.59</v>
       </c>
       <c r="F696" s="4">
         <f>B696/E696</f>
       </c>
       <c r="G696" s="2" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="H696" s="2" t="s">
         <v>214</v>
@@ -27633,7 +27580,7 @@
         <v>14</v>
       </c>
       <c r="K696" s="2" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
     </row>
     <row r="697" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27641,22 +27588,22 @@
         <v>731</v>
       </c>
       <c r="B697" s="3">
-        <v>3500000</v>
+        <v>1050000</v>
       </c>
       <c r="C697" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D697" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E697" s="2">
-        <v>239.53</v>
+        <v>99.17</v>
       </c>
       <c r="F697" s="4">
         <f>B697/E697</f>
       </c>
       <c r="G697" s="2" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="H697" s="2" t="s">
         <v>13</v>
@@ -27668,7 +27615,7 @@
         <v>14</v>
       </c>
       <c r="K697" s="2" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
     </row>
     <row r="698" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27676,22 +27623,22 @@
         <v>731</v>
       </c>
       <c r="B698" s="3">
-        <v>596500</v>
+        <v>685000</v>
       </c>
       <c r="C698" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D698" s="2">
         <v>1</v>
       </c>
       <c r="E698" s="2">
-        <v>68.04</v>
+        <v>62.02</v>
       </c>
       <c r="F698" s="4">
         <f>B698/E698</f>
       </c>
       <c r="G698" s="2" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="H698" s="2" t="s">
         <v>214</v>
@@ -27703,7 +27650,7 @@
         <v>14</v>
       </c>
       <c r="K698" s="2" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="699" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27711,25 +27658,25 @@
         <v>731</v>
       </c>
       <c r="B699" s="3">
-        <v>1050000</v>
+        <v>428750</v>
       </c>
       <c r="C699" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D699" s="2">
         <v>1</v>
       </c>
       <c r="E699" s="2">
-        <v>99.17</v>
+        <v>30.93</v>
       </c>
       <c r="F699" s="4">
         <f>B699/E699</f>
       </c>
       <c r="G699" s="2" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="H699" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="I699" s="2" t="s">
         <v>13</v>
@@ -27738,7 +27685,7 @@
         <v>14</v>
       </c>
       <c r="K699" s="2" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
     </row>
     <row r="700" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27746,20 +27693,22 @@
         <v>731</v>
       </c>
       <c r="B700" s="3">
-        <v>1295000</v>
+        <v>1495000</v>
       </c>
       <c r="C700" s="2">
-        <v>4</v>
-      </c>
-      <c r="D700" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="D700" s="2">
+        <v>1</v>
+      </c>
       <c r="E700" s="2">
-        <v>214.39</v>
+        <v>96.13</v>
       </c>
       <c r="F700" s="4">
         <f>B700/E700</f>
       </c>
       <c r="G700" s="2" t="s">
-        <v>97</v>
+        <v>863</v>
       </c>
       <c r="H700" s="2" t="s">
         <v>13</v>
@@ -27771,7 +27720,7 @@
         <v>14</v>
       </c>
       <c r="K700" s="2" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
     </row>
     <row r="701" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27779,22 +27728,22 @@
         <v>731</v>
       </c>
       <c r="B701" s="3">
-        <v>685000</v>
+        <v>4680000</v>
       </c>
       <c r="C701" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D701" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E701" s="2">
-        <v>62.02</v>
+        <v>322.08</v>
       </c>
       <c r="F701" s="4">
         <f>B701/E701</f>
       </c>
       <c r="G701" s="2" t="s">
-        <v>870</v>
+        <v>195</v>
       </c>
       <c r="H701" s="2" t="s">
         <v>214</v>
@@ -27803,7 +27752,7 @@
         <v>13</v>
       </c>
       <c r="J701" s="2" t="s">
-        <v>14</v>
+        <v>214</v>
       </c>
       <c r="K701" s="2" t="s">
         <v>871</v>
@@ -27814,22 +27763,22 @@
         <v>731</v>
       </c>
       <c r="B702" s="3">
-        <v>428750</v>
+        <v>780000</v>
       </c>
       <c r="C702" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D702" s="2">
         <v>1</v>
       </c>
       <c r="E702" s="2">
-        <v>30.93</v>
+        <v>120</v>
       </c>
       <c r="F702" s="4">
         <f>B702/E702</f>
       </c>
       <c r="G702" s="2" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="H702" s="2" t="s">
         <v>214</v>
@@ -27841,7 +27790,7 @@
         <v>14</v>
       </c>
       <c r="K702" s="2" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
     </row>
     <row r="703" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27849,34 +27798,34 @@
         <v>731</v>
       </c>
       <c r="B703" s="3">
-        <v>1495000</v>
+        <v>650000</v>
       </c>
       <c r="C703" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D703" s="2">
         <v>1</v>
       </c>
       <c r="E703" s="2">
-        <v>96.13</v>
+        <v>120.96</v>
       </c>
       <c r="F703" s="4">
         <f>B703/E703</f>
       </c>
       <c r="G703" s="2" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="H703" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="I703" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="J703" s="2" t="s">
         <v>14</v>
       </c>
       <c r="K703" s="2" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
     </row>
     <row r="704" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27884,34 +27833,34 @@
         <v>731</v>
       </c>
       <c r="B704" s="3">
-        <v>1760000</v>
+        <v>4200000</v>
       </c>
       <c r="C704" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D704" s="2">
         <v>1</v>
       </c>
       <c r="E704" s="2">
-        <v>177.93</v>
+        <v>502</v>
       </c>
       <c r="F704" s="4">
         <f>B704/E704</f>
       </c>
       <c r="G704" s="2" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="H704" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="I704" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="J704" s="2" t="s">
         <v>14</v>
       </c>
       <c r="K704" s="2" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
     </row>
     <row r="705" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27919,22 +27868,22 @@
         <v>731</v>
       </c>
       <c r="B705" s="3">
-        <v>361900</v>
+        <v>740000</v>
       </c>
       <c r="C705" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D705" s="2">
         <v>1</v>
       </c>
       <c r="E705" s="2">
-        <v>30.31</v>
+        <v>209.04</v>
       </c>
       <c r="F705" s="4">
         <f>B705/E705</f>
       </c>
       <c r="G705" s="2" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="H705" s="2" t="s">
         <v>214</v>
@@ -27946,7 +27895,7 @@
         <v>14</v>
       </c>
       <c r="K705" s="2" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
     </row>
     <row r="706" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27954,25 +27903,25 @@
         <v>731</v>
       </c>
       <c r="B706" s="3">
-        <v>428750</v>
+        <v>1450000</v>
       </c>
       <c r="C706" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D706" s="2">
         <v>1</v>
       </c>
       <c r="E706" s="2">
-        <v>30.93</v>
+        <v>313.78</v>
       </c>
       <c r="F706" s="4">
         <f>B706/E706</f>
       </c>
       <c r="G706" s="2" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="H706" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="I706" s="2" t="s">
         <v>13</v>
@@ -27981,7 +27930,7 @@
         <v>14</v>
       </c>
       <c r="K706" s="2" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
     </row>
     <row r="707" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27989,25 +27938,25 @@
         <v>731</v>
       </c>
       <c r="B707" s="3">
-        <v>630000</v>
+        <v>1995000</v>
       </c>
       <c r="C707" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D707" s="2">
         <v>1</v>
       </c>
       <c r="E707" s="2">
-        <v>81.8</v>
+        <v>190.1</v>
       </c>
       <c r="F707" s="4">
         <f>B707/E707</f>
       </c>
       <c r="G707" s="2" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="H707" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="I707" s="2" t="s">
         <v>13</v>
@@ -28016,7 +27965,7 @@
         <v>14</v>
       </c>
       <c r="K707" s="2" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
     </row>
     <row r="708" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -28024,34 +27973,34 @@
         <v>731</v>
       </c>
       <c r="B708" s="3">
-        <v>410000</v>
+        <v>650000</v>
       </c>
       <c r="C708" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D708" s="2">
         <v>1</v>
       </c>
       <c r="E708" s="2">
-        <v>34.88</v>
+        <v>120.96</v>
       </c>
       <c r="F708" s="4">
         <f>B708/E708</f>
       </c>
       <c r="G708" s="2" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="H708" s="2" t="s">
         <v>214</v>
       </c>
       <c r="I708" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="J708" s="2" t="s">
         <v>14</v>
       </c>
       <c r="K708" s="2" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
     </row>
     <row r="709" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -28059,25 +28008,25 @@
         <v>731</v>
       </c>
       <c r="B709" s="3">
-        <v>890000</v>
+        <v>1995000</v>
       </c>
       <c r="C709" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D709" s="2">
         <v>1</v>
       </c>
       <c r="E709" s="2">
-        <v>52.8</v>
+        <v>328</v>
       </c>
       <c r="F709" s="4">
         <f>B709/E709</f>
       </c>
       <c r="G709" s="2" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="H709" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="I709" s="2" t="s">
         <v>13</v>
@@ -28086,7 +28035,7 @@
         <v>14</v>
       </c>
       <c r="K709" s="2" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
     </row>
     <row r="710" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -28094,25 +28043,25 @@
         <v>731</v>
       </c>
       <c r="B710" s="3">
-        <v>1020000</v>
+        <v>1440000</v>
       </c>
       <c r="C710" s="2">
+        <v>4</v>
+      </c>
+      <c r="D710" s="2">
         <v>2</v>
       </c>
-      <c r="D710" s="2">
-        <v>1</v>
-      </c>
       <c r="E710" s="2">
-        <v>86.8</v>
+        <v>151.43</v>
       </c>
       <c r="F710" s="4">
         <f>B710/E710</f>
       </c>
       <c r="G710" s="2" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="H710" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="I710" s="2" t="s">
         <v>13</v>
@@ -28121,7 +28070,7 @@
         <v>14</v>
       </c>
       <c r="K710" s="2" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
     </row>
     <row r="711" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -28129,25 +28078,25 @@
         <v>731</v>
       </c>
       <c r="B711" s="3">
-        <v>845000</v>
+        <v>1600000</v>
       </c>
       <c r="C711" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D711" s="2">
         <v>1</v>
       </c>
       <c r="E711" s="2">
-        <v>50.9</v>
+        <v>208</v>
       </c>
       <c r="F711" s="4">
         <f>B711/E711</f>
       </c>
       <c r="G711" s="2" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="H711" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="I711" s="2" t="s">
         <v>13</v>
@@ -28156,7 +28105,7 @@
         <v>14</v>
       </c>
       <c r="K711" s="2" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
     </row>
     <row r="712" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -28164,34 +28113,34 @@
         <v>731</v>
       </c>
       <c r="B712" s="3">
-        <v>4680000</v>
+        <v>1155000</v>
       </c>
       <c r="C712" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D712" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E712" s="2">
-        <v>322.08</v>
+        <v>143.41</v>
       </c>
       <c r="F712" s="4">
         <f>B712/E712</f>
       </c>
       <c r="G712" s="2" t="s">
-        <v>195</v>
+        <v>874</v>
       </c>
       <c r="H712" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="I712" s="2" t="s">
         <v>13</v>
       </c>
       <c r="J712" s="2" t="s">
-        <v>214</v>
+        <v>14</v>
       </c>
       <c r="K712" s="2" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
     </row>
     <row r="713" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -28199,22 +28148,22 @@
         <v>731</v>
       </c>
       <c r="B713" s="3">
-        <v>1320000</v>
+        <v>1790000</v>
       </c>
       <c r="C713" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D713" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E713" s="2">
-        <v>169.3</v>
+        <v>250</v>
       </c>
       <c r="F713" s="4">
         <f>B713/E713</f>
       </c>
       <c r="G713" s="2" t="s">
-        <v>883</v>
+        <v>874</v>
       </c>
       <c r="H713" s="2" t="s">
         <v>13</v>
@@ -28226,7 +28175,7 @@
         <v>14</v>
       </c>
       <c r="K713" s="2" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
     </row>
     <row r="714" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -28234,22 +28183,20 @@
         <v>731</v>
       </c>
       <c r="B714" s="3">
-        <v>1390000</v>
-      </c>
-      <c r="C714" s="2">
-        <v>5</v>
-      </c>
+        <v>1150000</v>
+      </c>
+      <c r="C714" s="2"/>
       <c r="D714" s="2">
         <v>1</v>
       </c>
       <c r="E714" s="2">
-        <v>161.32</v>
+        <v>136</v>
       </c>
       <c r="F714" s="4">
         <f>B714/E714</f>
       </c>
       <c r="G714" s="2" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="H714" s="2" t="s">
         <v>13</v>
@@ -28261,7 +28208,7 @@
         <v>14</v>
       </c>
       <c r="K714" s="2" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
     </row>
     <row r="715" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -28269,7 +28216,7 @@
         <v>731</v>
       </c>
       <c r="B715" s="3">
-        <v>2700000</v>
+        <v>1240000</v>
       </c>
       <c r="C715" s="2">
         <v>5</v>
@@ -28278,13 +28225,13 @@
         <v>1</v>
       </c>
       <c r="E715" s="2">
-        <v>328.59</v>
+        <v>156</v>
       </c>
       <c r="F715" s="4">
         <f>B715/E715</f>
       </c>
       <c r="G715" s="2" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="H715" s="2" t="s">
         <v>13</v>
@@ -28296,7 +28243,7 @@
         <v>14</v>
       </c>
       <c r="K715" s="2" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
     </row>
     <row r="716" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -28304,25 +28251,25 @@
         <v>731</v>
       </c>
       <c r="B716" s="3">
-        <v>780000</v>
+        <v>1770000</v>
       </c>
       <c r="C716" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D716" s="2">
         <v>1</v>
       </c>
       <c r="E716" s="2">
-        <v>120</v>
+        <v>260</v>
       </c>
       <c r="F716" s="4">
         <f>B716/E716</f>
       </c>
       <c r="G716" s="2" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="H716" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="I716" s="2" t="s">
         <v>13</v>
@@ -28331,7 +28278,7 @@
         <v>14</v>
       </c>
       <c r="K716" s="2" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
     </row>
     <row r="717" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -28339,22 +28286,22 @@
         <v>731</v>
       </c>
       <c r="B717" s="3">
-        <v>3290000</v>
+        <v>975000</v>
       </c>
       <c r="C717" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D717" s="2">
         <v>1</v>
       </c>
       <c r="E717" s="2">
-        <v>430.3</v>
+        <v>130</v>
       </c>
       <c r="F717" s="4">
         <f>B717/E717</f>
       </c>
       <c r="G717" s="2" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="H717" s="2" t="s">
         <v>13</v>
@@ -28366,7 +28313,7 @@
         <v>14</v>
       </c>
       <c r="K717" s="2" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
     </row>
     <row r="718" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -28374,34 +28321,32 @@
         <v>731</v>
       </c>
       <c r="B718" s="3">
-        <v>650000</v>
+        <v>599000</v>
       </c>
       <c r="C718" s="2">
         <v>2</v>
       </c>
-      <c r="D718" s="2">
-        <v>1</v>
-      </c>
+      <c r="D718" s="2"/>
       <c r="E718" s="2">
-        <v>120.96</v>
+        <v>87</v>
       </c>
       <c r="F718" s="4">
         <f>B718/E718</f>
       </c>
       <c r="G718" s="2" t="s">
-        <v>889</v>
+        <v>886</v>
       </c>
       <c r="H718" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="I718" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="J718" s="2" t="s">
         <v>14</v>
       </c>
       <c r="K718" s="2" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
     </row>
     <row r="719" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -28409,20 +28354,22 @@
         <v>731</v>
       </c>
       <c r="B719" s="3">
-        <v>1150000</v>
-      </c>
-      <c r="C719" s="2"/>
+        <v>1400000</v>
+      </c>
+      <c r="C719" s="2">
+        <v>5</v>
+      </c>
       <c r="D719" s="2">
         <v>1</v>
       </c>
       <c r="E719" s="2">
-        <v>136</v>
+        <v>155.77</v>
       </c>
       <c r="F719" s="4">
         <f>B719/E719</f>
       </c>
       <c r="G719" s="2" t="s">
-        <v>891</v>
+        <v>886</v>
       </c>
       <c r="H719" s="2" t="s">
         <v>13</v>
@@ -28442,7 +28389,7 @@
         <v>731</v>
       </c>
       <c r="B720" s="3">
-        <v>1240000</v>
+        <v>1975000</v>
       </c>
       <c r="C720" s="2">
         <v>5</v>
@@ -28451,13 +28398,13 @@
         <v>1</v>
       </c>
       <c r="E720" s="2">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="F720" s="4">
         <f>B720/E720</f>
       </c>
       <c r="G720" s="2" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="H720" s="2" t="s">
         <v>13</v>
@@ -28469,7 +28416,7 @@
         <v>14</v>
       </c>
       <c r="K720" s="2" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
     </row>
     <row r="721" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -28477,22 +28424,22 @@
         <v>731</v>
       </c>
       <c r="B721" s="3">
-        <v>1770000</v>
+        <v>3450000</v>
       </c>
       <c r="C721" s="2">
         <v>7</v>
       </c>
       <c r="D721" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E721" s="2">
-        <v>260</v>
+        <v>386.26</v>
       </c>
       <c r="F721" s="4">
         <f>B721/E721</f>
       </c>
       <c r="G721" s="2" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="H721" s="2" t="s">
         <v>13</v>
@@ -28504,7 +28451,7 @@
         <v>14</v>
       </c>
       <c r="K721" s="2" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
     </row>
     <row r="722" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -28512,22 +28459,22 @@
         <v>731</v>
       </c>
       <c r="B722" s="3">
-        <v>975000</v>
+        <v>1995000</v>
       </c>
       <c r="C722" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D722" s="2">
         <v>1</v>
       </c>
       <c r="E722" s="2">
-        <v>130</v>
+        <v>147.26</v>
       </c>
       <c r="F722" s="4">
         <f>B722/E722</f>
       </c>
       <c r="G722" s="2" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="H722" s="2" t="s">
         <v>13</v>
@@ -28539,7 +28486,7 @@
         <v>14</v>
       </c>
       <c r="K722" s="2" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
     </row>
     <row r="723" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -28547,20 +28494,22 @@
         <v>731</v>
       </c>
       <c r="B723" s="3">
-        <v>599000</v>
+        <v>1850000</v>
       </c>
       <c r="C723" s="2">
-        <v>2</v>
-      </c>
-      <c r="D723" s="2"/>
+        <v>5</v>
+      </c>
+      <c r="D723" s="2">
+        <v>1</v>
+      </c>
       <c r="E723" s="2">
-        <v>87</v>
+        <v>186</v>
       </c>
       <c r="F723" s="4">
         <f>B723/E723</f>
       </c>
       <c r="G723" s="2" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="H723" s="2" t="s">
         <v>13</v>
@@ -28572,7 +28521,7 @@
         <v>14</v>
       </c>
       <c r="K723" s="2" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
     </row>
     <row r="724" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -28583,19 +28532,19 @@
         <v>1400000</v>
       </c>
       <c r="C724" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D724" s="2">
         <v>1</v>
       </c>
       <c r="E724" s="2">
-        <v>155.77</v>
+        <v>134</v>
       </c>
       <c r="F724" s="4">
         <f>B724/E724</f>
       </c>
       <c r="G724" s="2" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="H724" s="2" t="s">
         <v>13</v>
@@ -28607,7 +28556,7 @@
         <v>14</v>
       </c>
       <c r="K724" s="2" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
     </row>
     <row r="725" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -28615,22 +28564,22 @@
         <v>731</v>
       </c>
       <c r="B725" s="3">
-        <v>1440000</v>
+        <v>2800000</v>
       </c>
       <c r="C725" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D725" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E725" s="2">
-        <v>212.62</v>
+        <v>318</v>
       </c>
       <c r="F725" s="4">
         <f>B725/E725</f>
       </c>
       <c r="G725" s="2" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="H725" s="2" t="s">
         <v>13</v>
@@ -28642,7 +28591,7 @@
         <v>14</v>
       </c>
       <c r="K725" s="2" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
     </row>
     <row r="726" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -28665,7 +28614,7 @@
         <f>B726/E726</f>
       </c>
       <c r="G726" s="2" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="H726" s="2" t="s">
         <v>13</v>
@@ -28677,7 +28626,7 @@
         <v>14</v>
       </c>
       <c r="K726" s="2" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
     </row>
     <row r="727" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -28685,22 +28634,22 @@
         <v>731</v>
       </c>
       <c r="B727" s="3">
-        <v>2980000</v>
+        <v>1290000</v>
       </c>
       <c r="C727" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D727" s="2">
         <v>1</v>
       </c>
       <c r="E727" s="2">
-        <v>264</v>
+        <v>166</v>
       </c>
       <c r="F727" s="4">
         <f>B727/E727</f>
       </c>
       <c r="G727" s="2" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="H727" s="2" t="s">
         <v>13</v>
@@ -28712,7 +28661,7 @@
         <v>14</v>
       </c>
       <c r="K727" s="2" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
     </row>
     <row r="728" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -28720,25 +28669,25 @@
         <v>731</v>
       </c>
       <c r="B728" s="3">
-        <v>3450000</v>
+        <v>1700000</v>
       </c>
       <c r="C728" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D728" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E728" s="2">
-        <v>386.26</v>
+        <v>133</v>
       </c>
       <c r="F728" s="4">
         <f>B728/E728</f>
       </c>
       <c r="G728" s="2" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="H728" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="I728" s="2" t="s">
         <v>13</v>
@@ -28747,7 +28696,7 @@
         <v>14</v>
       </c>
       <c r="K728" s="2" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
     </row>
     <row r="729" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -28755,22 +28704,22 @@
         <v>731</v>
       </c>
       <c r="B729" s="3">
-        <v>5000000</v>
+        <v>945000</v>
       </c>
       <c r="C729" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D729" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E729" s="2">
-        <v>500</v>
+        <v>94.68</v>
       </c>
       <c r="F729" s="4">
         <f>B729/E729</f>
       </c>
       <c r="G729" s="2" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="H729" s="2" t="s">
         <v>13</v>
@@ -28782,7 +28731,7 @@
         <v>14</v>
       </c>
       <c r="K729" s="2" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
     </row>
     <row r="730" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -28790,22 +28739,22 @@
         <v>731</v>
       </c>
       <c r="B730" s="3">
-        <v>1150000</v>
+        <v>2980000</v>
       </c>
       <c r="C730" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D730" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E730" s="2">
-        <v>154</v>
+        <v>264</v>
       </c>
       <c r="F730" s="4">
         <f>B730/E730</f>
       </c>
       <c r="G730" s="2" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="H730" s="2" t="s">
         <v>13</v>
@@ -28817,7 +28766,7 @@
         <v>14</v>
       </c>
       <c r="K730" s="2" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
     </row>
     <row r="731" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -28825,25 +28774,25 @@
         <v>731</v>
       </c>
       <c r="B731" s="3">
-        <v>1700000</v>
+        <v>835000</v>
       </c>
       <c r="C731" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D731" s="2">
         <v>1</v>
       </c>
       <c r="E731" s="2">
-        <v>133</v>
+        <v>145.61</v>
       </c>
       <c r="F731" s="4">
         <f>B731/E731</f>
       </c>
       <c r="G731" s="2" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="H731" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="I731" s="2" t="s">
         <v>13</v>
@@ -28852,7 +28801,7 @@
         <v>14</v>
       </c>
       <c r="K731" s="2" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
     </row>
     <row r="732" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -28860,22 +28809,22 @@
         <v>731</v>
       </c>
       <c r="B732" s="3">
-        <v>1155000</v>
+        <v>1440000</v>
       </c>
       <c r="C732" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D732" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E732" s="2">
-        <v>143.41</v>
+        <v>212.62</v>
       </c>
       <c r="F732" s="4">
         <f>B732/E732</f>
       </c>
       <c r="G732" s="2" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="H732" s="2" t="s">
         <v>13</v>
@@ -28887,7 +28836,7 @@
         <v>14</v>
       </c>
       <c r="K732" s="2" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
     </row>
     <row r="733" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -28895,22 +28844,22 @@
         <v>731</v>
       </c>
       <c r="B733" s="3">
-        <v>1975000</v>
+        <v>5000000</v>
       </c>
       <c r="C733" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D733" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E733" s="2">
-        <v>168</v>
+        <v>500</v>
       </c>
       <c r="F733" s="4">
         <f>B733/E733</f>
       </c>
       <c r="G733" s="2" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="H733" s="2" t="s">
         <v>13</v>
@@ -28922,7 +28871,7 @@
         <v>14</v>
       </c>
       <c r="K733" s="2" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
     </row>
     <row r="734" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -28930,22 +28879,22 @@
         <v>731</v>
       </c>
       <c r="B734" s="3">
-        <v>1400000</v>
+        <v>1680000</v>
       </c>
       <c r="C734" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D734" s="2">
         <v>1</v>
       </c>
       <c r="E734" s="2">
-        <v>134</v>
+        <v>228.95</v>
       </c>
       <c r="F734" s="4">
         <f>B734/E734</f>
       </c>
       <c r="G734" s="2" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="H734" s="2" t="s">
         <v>13</v>
@@ -28957,7 +28906,7 @@
         <v>14</v>
       </c>
       <c r="K734" s="2" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
     </row>
     <row r="735" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -28965,25 +28914,25 @@
         <v>731</v>
       </c>
       <c r="B735" s="3">
-        <v>1850000</v>
+        <v>795000</v>
       </c>
       <c r="C735" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D735" s="2">
         <v>1</v>
       </c>
       <c r="E735" s="2">
-        <v>186</v>
+        <v>115.86</v>
       </c>
       <c r="F735" s="4">
         <f>B735/E735</f>
       </c>
       <c r="G735" s="2" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="H735" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="I735" s="2" t="s">
         <v>13</v>
@@ -28992,7 +28941,7 @@
         <v>14</v>
       </c>
       <c r="K735" s="2" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
     </row>
     <row r="736" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -29000,22 +28949,22 @@
         <v>731</v>
       </c>
       <c r="B736" s="3">
-        <v>1695000</v>
+        <v>890000</v>
       </c>
       <c r="C736" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D736" s="2">
         <v>1</v>
       </c>
       <c r="E736" s="2">
-        <v>207</v>
+        <v>160.08</v>
       </c>
       <c r="F736" s="4">
         <f>B736/E736</f>
       </c>
       <c r="G736" s="2" t="s">
-        <v>891</v>
+        <v>910</v>
       </c>
       <c r="H736" s="2" t="s">
         <v>13</v>
@@ -29027,7 +28976,7 @@
         <v>14</v>
       </c>
       <c r="K736" s="2" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
     </row>
     <row r="737" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -29035,22 +28984,22 @@
         <v>731</v>
       </c>
       <c r="B737" s="3">
-        <v>835000</v>
+        <v>1795000</v>
       </c>
       <c r="C737" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D737" s="2">
         <v>1</v>
       </c>
       <c r="E737" s="2">
-        <v>145.61</v>
+        <v>240</v>
       </c>
       <c r="F737" s="4">
         <f>B737/E737</f>
       </c>
       <c r="G737" s="2" t="s">
-        <v>891</v>
+        <v>910</v>
       </c>
       <c r="H737" s="2" t="s">
         <v>13</v>
@@ -29062,7 +29011,7 @@
         <v>14</v>
       </c>
       <c r="K737" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
     </row>
     <row r="738" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -29070,22 +29019,22 @@
         <v>731</v>
       </c>
       <c r="B738" s="3">
-        <v>1440000</v>
+        <v>1990000</v>
       </c>
       <c r="C738" s="2">
         <v>4</v>
       </c>
       <c r="D738" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E738" s="2">
-        <v>151.43</v>
+        <v>310</v>
       </c>
       <c r="F738" s="4">
         <f>B738/E738</f>
       </c>
       <c r="G738" s="2" t="s">
-        <v>891</v>
+        <v>910</v>
       </c>
       <c r="H738" s="2" t="s">
         <v>13</v>
@@ -29097,7 +29046,7 @@
         <v>14</v>
       </c>
       <c r="K738" s="2" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
     </row>
     <row r="739" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -29105,22 +29054,22 @@
         <v>731</v>
       </c>
       <c r="B739" s="3">
-        <v>1995000</v>
+        <v>1290000</v>
       </c>
       <c r="C739" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D739" s="2">
         <v>1</v>
       </c>
       <c r="E739" s="2">
-        <v>147.26</v>
+        <v>157</v>
       </c>
       <c r="F739" s="4">
         <f>B739/E739</f>
       </c>
       <c r="G739" s="2" t="s">
-        <v>891</v>
+        <v>910</v>
       </c>
       <c r="H739" s="2" t="s">
         <v>13</v>
@@ -29132,7 +29081,7 @@
         <v>14</v>
       </c>
       <c r="K739" s="2" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
     </row>
     <row r="740" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -29140,25 +29089,25 @@
         <v>731</v>
       </c>
       <c r="B740" s="3">
-        <v>795000</v>
+        <v>3980000</v>
       </c>
       <c r="C740" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D740" s="2">
         <v>1</v>
       </c>
       <c r="E740" s="2">
-        <v>115.86</v>
+        <v>486</v>
       </c>
       <c r="F740" s="4">
         <f>B740/E740</f>
       </c>
       <c r="G740" s="2" t="s">
-        <v>891</v>
+        <v>910</v>
       </c>
       <c r="H740" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="I740" s="2" t="s">
         <v>13</v>
@@ -29167,7 +29116,7 @@
         <v>14</v>
       </c>
       <c r="K740" s="2" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
     </row>
     <row r="741" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -29175,22 +29124,22 @@
         <v>731</v>
       </c>
       <c r="B741" s="3">
-        <v>945000</v>
+        <v>575000</v>
       </c>
       <c r="C741" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D741" s="2">
         <v>1</v>
       </c>
       <c r="E741" s="2">
-        <v>94.68</v>
+        <v>53.95</v>
       </c>
       <c r="F741" s="4">
         <f>B741/E741</f>
       </c>
       <c r="G741" s="2" t="s">
-        <v>891</v>
+        <v>910</v>
       </c>
       <c r="H741" s="2" t="s">
         <v>13</v>
@@ -29202,7 +29151,7 @@
         <v>14</v>
       </c>
       <c r="K741" s="2" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
     </row>
     <row r="742" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -29210,34 +29159,34 @@
         <v>731</v>
       </c>
       <c r="B742" s="3">
-        <v>695000</v>
+        <v>370000</v>
       </c>
       <c r="C742" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D742" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E742" s="2">
-        <v>105.56</v>
+        <v>75</v>
       </c>
       <c r="F742" s="4">
         <f>B742/E742</f>
       </c>
       <c r="G742" s="2" t="s">
-        <v>891</v>
+        <v>917</v>
       </c>
       <c r="H742" s="2" t="s">
         <v>214</v>
       </c>
       <c r="I742" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="J742" s="2" t="s">
         <v>14</v>
       </c>
       <c r="K742" s="2" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
     </row>
     <row r="743" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -29245,7 +29194,7 @@
         <v>731</v>
       </c>
       <c r="B743" s="3">
-        <v>4200000</v>
+        <v>1275000</v>
       </c>
       <c r="C743" s="2">
         <v>5</v>
@@ -29254,13 +29203,13 @@
         <v>1</v>
       </c>
       <c r="E743" s="2">
-        <v>502</v>
+        <v>173</v>
       </c>
       <c r="F743" s="4">
         <f>B743/E743</f>
       </c>
       <c r="G743" s="2" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="H743" s="2" t="s">
         <v>13</v>
@@ -29272,7 +29221,7 @@
         <v>14</v>
       </c>
       <c r="K743" s="2" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
     </row>
     <row r="744" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -29280,22 +29229,22 @@
         <v>731</v>
       </c>
       <c r="B744" s="3">
-        <v>1450000</v>
+        <v>1150000</v>
       </c>
       <c r="C744" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D744" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E744" s="2">
-        <v>313.78</v>
+        <v>154</v>
       </c>
       <c r="F744" s="4">
         <f>B744/E744</f>
       </c>
       <c r="G744" s="2" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="H744" s="2" t="s">
         <v>13</v>
@@ -29307,7 +29256,7 @@
         <v>14</v>
       </c>
       <c r="K744" s="2" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
     </row>
     <row r="745" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -29315,22 +29264,22 @@
         <v>731</v>
       </c>
       <c r="B745" s="3">
-        <v>890000</v>
+        <v>1695000</v>
       </c>
       <c r="C745" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D745" s="2">
         <v>1</v>
       </c>
       <c r="E745" s="2">
-        <v>160.08</v>
+        <v>207</v>
       </c>
       <c r="F745" s="4">
         <f>B745/E745</f>
       </c>
       <c r="G745" s="2" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="H745" s="2" t="s">
         <v>13</v>
@@ -29342,7 +29291,7 @@
         <v>14</v>
       </c>
       <c r="K745" s="2" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
     </row>
     <row r="746" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -29350,22 +29299,22 @@
         <v>731</v>
       </c>
       <c r="B746" s="3">
-        <v>1600000</v>
+        <v>5000000</v>
       </c>
       <c r="C746" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D746" s="2">
         <v>1</v>
       </c>
       <c r="E746" s="2">
-        <v>208</v>
+        <v>470</v>
       </c>
       <c r="F746" s="4">
         <f>B746/E746</f>
       </c>
       <c r="G746" s="2" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="H746" s="2" t="s">
         <v>13</v>
@@ -29377,7 +29326,7 @@
         <v>14</v>
       </c>
       <c r="K746" s="2" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
     </row>
     <row r="747" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -29385,22 +29334,22 @@
         <v>731</v>
       </c>
       <c r="B747" s="3">
-        <v>1790000</v>
+        <v>2750000</v>
       </c>
       <c r="C747" s="2">
         <v>6</v>
       </c>
       <c r="D747" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E747" s="2">
-        <v>250</v>
+        <v>380</v>
       </c>
       <c r="F747" s="4">
         <f>B747/E747</f>
       </c>
       <c r="G747" s="2" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="H747" s="2" t="s">
         <v>13</v>
@@ -29412,7 +29361,7 @@
         <v>14</v>
       </c>
       <c r="K747" s="2" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
     </row>
     <row r="748" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -29420,22 +29369,22 @@
         <v>731</v>
       </c>
       <c r="B748" s="3">
-        <v>1995000</v>
+        <v>3000000</v>
       </c>
       <c r="C748" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D748" s="2">
         <v>1</v>
       </c>
       <c r="E748" s="2">
-        <v>190.1</v>
+        <v>361.03</v>
       </c>
       <c r="F748" s="4">
         <f>B748/E748</f>
       </c>
       <c r="G748" s="2" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="H748" s="2" t="s">
         <v>13</v>
@@ -29447,7 +29396,7 @@
         <v>14</v>
       </c>
       <c r="K748" s="2" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
     </row>
     <row r="749" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -29455,22 +29404,22 @@
         <v>731</v>
       </c>
       <c r="B749" s="3">
-        <v>1995000</v>
+        <v>1350000</v>
       </c>
       <c r="C749" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D749" s="2">
         <v>1</v>
       </c>
       <c r="E749" s="2">
-        <v>328</v>
+        <v>166</v>
       </c>
       <c r="F749" s="4">
         <f>B749/E749</f>
       </c>
       <c r="G749" s="2" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="H749" s="2" t="s">
         <v>13</v>
@@ -29482,7 +29431,7 @@
         <v>14</v>
       </c>
       <c r="K749" s="2" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
     </row>
     <row r="750" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -29490,22 +29439,22 @@
         <v>731</v>
       </c>
       <c r="B750" s="3">
-        <v>1795000</v>
+        <v>880000</v>
       </c>
       <c r="C750" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D750" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E750" s="2">
-        <v>240</v>
+        <v>93.99</v>
       </c>
       <c r="F750" s="4">
         <f>B750/E750</f>
       </c>
       <c r="G750" s="2" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="H750" s="2" t="s">
         <v>13</v>
@@ -29517,7 +29466,7 @@
         <v>14</v>
       </c>
       <c r="K750" s="2" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
     </row>
     <row r="751" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -29528,19 +29477,19 @@
         <v>1990000</v>
       </c>
       <c r="C751" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D751" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E751" s="2">
-        <v>310</v>
+        <v>230</v>
       </c>
       <c r="F751" s="4">
         <f>B751/E751</f>
       </c>
       <c r="G751" s="2" t="s">
-        <v>926</v>
+        <v>917</v>
       </c>
       <c r="H751" s="2" t="s">
         <v>13</v>
@@ -29560,34 +29509,34 @@
         <v>731</v>
       </c>
       <c r="B752" s="3">
-        <v>370000</v>
+        <v>2200000</v>
       </c>
       <c r="C752" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D752" s="2">
         <v>1</v>
       </c>
       <c r="E752" s="2">
-        <v>75</v>
+        <v>225</v>
       </c>
       <c r="F752" s="4">
         <f>B752/E752</f>
       </c>
       <c r="G752" s="2" t="s">
+        <v>917</v>
+      </c>
+      <c r="H752" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I752" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J752" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K752" s="2" t="s">
         <v>928</v>
-      </c>
-      <c r="H752" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="I752" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="J752" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K752" s="2" t="s">
-        <v>929</v>
       </c>
     </row>
     <row r="753" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -29610,19 +29559,19 @@
         <f>B753/E753</f>
       </c>
       <c r="G753" s="2" t="s">
+        <v>929</v>
+      </c>
+      <c r="H753" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I753" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J753" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K753" s="2" t="s">
         <v>930</v>
-      </c>
-      <c r="H753" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I753" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J753" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K753" s="2" t="s">
-        <v>931</v>
       </c>
     </row>
     <row r="754" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -29630,34 +29579,34 @@
         <v>731</v>
       </c>
       <c r="B754" s="3">
-        <v>1350000</v>
+        <v>560000</v>
       </c>
       <c r="C754" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D754" s="2">
         <v>1</v>
       </c>
       <c r="E754" s="2">
-        <v>166</v>
+        <v>112.82</v>
       </c>
       <c r="F754" s="4">
         <f>B754/E754</f>
       </c>
       <c r="G754" s="2" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="H754" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="I754" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="J754" s="2" t="s">
         <v>14</v>
       </c>
       <c r="K754" s="2" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="755" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -29665,22 +29614,22 @@
         <v>731</v>
       </c>
       <c r="B755" s="3">
-        <v>5000000</v>
+        <v>900000</v>
       </c>
       <c r="C755" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D755" s="2">
         <v>1</v>
       </c>
       <c r="E755" s="2">
-        <v>470</v>
+        <v>175</v>
       </c>
       <c r="F755" s="4">
         <f>B755/E755</f>
       </c>
       <c r="G755" s="2" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="H755" s="2" t="s">
         <v>13</v>
@@ -29700,22 +29649,22 @@
         <v>731</v>
       </c>
       <c r="B756" s="3">
-        <v>3000000</v>
+        <v>1100000</v>
       </c>
       <c r="C756" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D756" s="2">
         <v>1</v>
       </c>
       <c r="E756" s="2">
-        <v>361.03</v>
+        <v>184.25</v>
       </c>
       <c r="F756" s="4">
         <f>B756/E756</f>
       </c>
       <c r="G756" s="2" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="H756" s="2" t="s">
         <v>13</v>
@@ -29735,34 +29684,34 @@
         <v>731</v>
       </c>
       <c r="B757" s="3">
-        <v>1680000</v>
+        <v>745000</v>
       </c>
       <c r="C757" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D757" s="2">
         <v>1</v>
       </c>
       <c r="E757" s="2">
-        <v>228.95</v>
+        <v>124</v>
       </c>
       <c r="F757" s="4">
         <f>B757/E757</f>
       </c>
       <c r="G757" s="2" t="s">
-        <v>930</v>
+        <v>935</v>
       </c>
       <c r="H757" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I757" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="J757" s="2" t="s">
         <v>14</v>
       </c>
       <c r="K757" s="2" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
     </row>
     <row r="758" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -29770,34 +29719,34 @@
         <v>731</v>
       </c>
       <c r="B758" s="3">
-        <v>560000</v>
+        <v>595000</v>
       </c>
       <c r="C758" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D758" s="2">
         <v>1</v>
       </c>
       <c r="E758" s="2">
-        <v>112.82</v>
+        <v>69.09</v>
       </c>
       <c r="F758" s="4">
         <f>B758/E758</f>
       </c>
       <c r="G758" s="2" t="s">
-        <v>930</v>
+        <v>935</v>
       </c>
       <c r="H758" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="I758" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="J758" s="2" t="s">
         <v>14</v>
       </c>
       <c r="K758" s="2" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
     </row>
     <row r="759" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -29805,22 +29754,18 @@
         <v>731</v>
       </c>
       <c r="B759" s="3">
-        <v>2800000</v>
-      </c>
-      <c r="C759" s="2">
-        <v>6</v>
-      </c>
-      <c r="D759" s="2">
-        <v>2</v>
-      </c>
+        <v>4680000</v>
+      </c>
+      <c r="C759" s="2"/>
+      <c r="D759" s="2"/>
       <c r="E759" s="2">
-        <v>318</v>
+        <v>600</v>
       </c>
       <c r="F759" s="4">
         <f>B759/E759</f>
       </c>
       <c r="G759" s="2" t="s">
-        <v>930</v>
+        <v>935</v>
       </c>
       <c r="H759" s="2" t="s">
         <v>13</v>
@@ -29832,7 +29777,7 @@
         <v>14</v>
       </c>
       <c r="K759" s="2" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
     </row>
     <row r="760" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -29840,22 +29785,22 @@
         <v>731</v>
       </c>
       <c r="B760" s="3">
-        <v>1290000</v>
+        <v>3700000</v>
       </c>
       <c r="C760" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D760" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E760" s="2">
-        <v>166</v>
+        <v>446</v>
       </c>
       <c r="F760" s="4">
         <f>B760/E760</f>
       </c>
       <c r="G760" s="2" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="H760" s="2" t="s">
         <v>13</v>
@@ -29867,7 +29812,7 @@
         <v>14</v>
       </c>
       <c r="K760" s="2" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
     </row>
     <row r="761" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -29875,16 +29820,16 @@
         <v>731</v>
       </c>
       <c r="B761" s="3">
-        <v>740000</v>
+        <v>2100000</v>
       </c>
       <c r="C761" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D761" s="2">
         <v>1</v>
       </c>
       <c r="E761" s="2">
-        <v>209.04</v>
+        <v>447.66</v>
       </c>
       <c r="F761" s="4">
         <f>B761/E761</f>
@@ -29893,16 +29838,16 @@
         <v>939</v>
       </c>
       <c r="H761" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="I761" s="2" t="s">
         <v>13</v>
       </c>
       <c r="J761" s="2" t="s">
-        <v>14</v>
+        <v>214</v>
       </c>
       <c r="K761" s="2" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
     </row>
     <row r="762" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -29910,28 +29855,24 @@
         <v>731</v>
       </c>
       <c r="B762" s="3">
-        <v>745000</v>
-      </c>
-      <c r="C762" s="2">
-        <v>3</v>
-      </c>
-      <c r="D762" s="2">
-        <v>1</v>
-      </c>
+        <v>1990000</v>
+      </c>
+      <c r="C762" s="2"/>
+      <c r="D762" s="2"/>
       <c r="E762" s="2">
-        <v>124</v>
+        <v>333.83</v>
       </c>
       <c r="F762" s="4">
         <f>B762/E762</f>
       </c>
       <c r="G762" s="2" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="H762" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I762" s="2" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="J762" s="2" t="s">
         <v>14</v>
@@ -29945,22 +29886,18 @@
         <v>731</v>
       </c>
       <c r="B763" s="3">
-        <v>2750000</v>
-      </c>
-      <c r="C763" s="2">
-        <v>6</v>
-      </c>
-      <c r="D763" s="2">
-        <v>1</v>
-      </c>
+        <v>2050000</v>
+      </c>
+      <c r="C763" s="2"/>
+      <c r="D763" s="2"/>
       <c r="E763" s="2">
-        <v>380</v>
+        <v>333.83</v>
       </c>
       <c r="F763" s="4">
         <f>B763/E763</f>
       </c>
       <c r="G763" s="2" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="H763" s="2" t="s">
         <v>13</v>
@@ -29983,19 +29920,19 @@
         <v>595000</v>
       </c>
       <c r="C764" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D764" s="2">
         <v>1</v>
       </c>
       <c r="E764" s="2">
-        <v>69.09</v>
+        <v>214.6</v>
       </c>
       <c r="F764" s="4">
         <f>B764/E764</f>
       </c>
       <c r="G764" s="2" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="H764" s="2" t="s">
         <v>13</v>
@@ -30015,22 +29952,22 @@
         <v>731</v>
       </c>
       <c r="B765" s="3">
-        <v>1275000</v>
+        <v>2850000</v>
       </c>
       <c r="C765" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D765" s="2">
         <v>1</v>
       </c>
       <c r="E765" s="2">
-        <v>173</v>
+        <v>455</v>
       </c>
       <c r="F765" s="4">
         <f>B765/E765</f>
       </c>
       <c r="G765" s="2" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="H765" s="2" t="s">
         <v>13</v>
@@ -30050,28 +29987,28 @@
         <v>731</v>
       </c>
       <c r="B766" s="3">
-        <v>1990000</v>
+        <v>565000</v>
       </c>
       <c r="C766" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D766" s="2">
         <v>1</v>
       </c>
       <c r="E766" s="2">
-        <v>230</v>
+        <v>72</v>
       </c>
       <c r="F766" s="4">
         <f>B766/E766</f>
       </c>
       <c r="G766" s="2" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="H766" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="I766" s="2" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="J766" s="2" t="s">
         <v>14</v>
@@ -30085,18 +30022,22 @@
         <v>731</v>
       </c>
       <c r="B767" s="3">
-        <v>4680000</v>
-      </c>
-      <c r="C767" s="2"/>
-      <c r="D767" s="2"/>
+        <v>249000</v>
+      </c>
+      <c r="C767" s="2">
+        <v>1</v>
+      </c>
+      <c r="D767" s="2">
+        <v>1</v>
+      </c>
       <c r="E767" s="2">
-        <v>600</v>
+        <v>31.19</v>
       </c>
       <c r="F767" s="4">
         <f>B767/E767</f>
       </c>
       <c r="G767" s="2" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="H767" s="2" t="s">
         <v>13</v>
@@ -30109,453 +30050,6 @@
       </c>
       <c r="K767" s="2" t="s">
         <v>947</v>
-      </c>
-    </row>
-    <row r="768" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A768" s="2" t="s">
-        <v>731</v>
-      </c>
-      <c r="B768" s="3">
-        <v>2200000</v>
-      </c>
-      <c r="C768" s="2">
-        <v>6</v>
-      </c>
-      <c r="D768" s="2">
-        <v>1</v>
-      </c>
-      <c r="E768" s="2">
-        <v>225</v>
-      </c>
-      <c r="F768" s="4">
-        <f>B768/E768</f>
-      </c>
-      <c r="G768" s="2" t="s">
-        <v>941</v>
-      </c>
-      <c r="H768" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I768" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J768" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K768" s="2" t="s">
-        <v>948</v>
-      </c>
-    </row>
-    <row r="769" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A769" s="2" t="s">
-        <v>731</v>
-      </c>
-      <c r="B769" s="3">
-        <v>880000</v>
-      </c>
-      <c r="C769" s="2">
-        <v>2</v>
-      </c>
-      <c r="D769" s="2">
-        <v>2</v>
-      </c>
-      <c r="E769" s="2">
-        <v>93.99</v>
-      </c>
-      <c r="F769" s="4">
-        <f>B769/E769</f>
-      </c>
-      <c r="G769" s="2" t="s">
-        <v>941</v>
-      </c>
-      <c r="H769" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I769" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J769" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K769" s="2" t="s">
-        <v>949</v>
-      </c>
-    </row>
-    <row r="770" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A770" s="2" t="s">
-        <v>731</v>
-      </c>
-      <c r="B770" s="3">
-        <v>1100000</v>
-      </c>
-      <c r="C770" s="2">
-        <v>4</v>
-      </c>
-      <c r="D770" s="2">
-        <v>1</v>
-      </c>
-      <c r="E770" s="2">
-        <v>184.25</v>
-      </c>
-      <c r="F770" s="4">
-        <f>B770/E770</f>
-      </c>
-      <c r="G770" s="2" t="s">
-        <v>950</v>
-      </c>
-      <c r="H770" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I770" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J770" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K770" s="2" t="s">
-        <v>951</v>
-      </c>
-    </row>
-    <row r="771" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A771" s="2" t="s">
-        <v>731</v>
-      </c>
-      <c r="B771" s="3">
-        <v>900000</v>
-      </c>
-      <c r="C771" s="2">
-        <v>4</v>
-      </c>
-      <c r="D771" s="2">
-        <v>1</v>
-      </c>
-      <c r="E771" s="2">
-        <v>175</v>
-      </c>
-      <c r="F771" s="4">
-        <f>B771/E771</f>
-      </c>
-      <c r="G771" s="2" t="s">
-        <v>950</v>
-      </c>
-      <c r="H771" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I771" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J771" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K771" s="2" t="s">
-        <v>952</v>
-      </c>
-    </row>
-    <row r="772" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A772" s="2" t="s">
-        <v>731</v>
-      </c>
-      <c r="B772" s="3">
-        <v>3700000</v>
-      </c>
-      <c r="C772" s="2">
-        <v>6</v>
-      </c>
-      <c r="D772" s="2">
-        <v>2</v>
-      </c>
-      <c r="E772" s="2">
-        <v>446</v>
-      </c>
-      <c r="F772" s="4">
-        <f>B772/E772</f>
-      </c>
-      <c r="G772" s="2" t="s">
-        <v>953</v>
-      </c>
-      <c r="H772" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I772" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J772" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K772" s="2" t="s">
-        <v>954</v>
-      </c>
-    </row>
-    <row r="773" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A773" s="2" t="s">
-        <v>731</v>
-      </c>
-      <c r="B773" s="3">
-        <v>2100000</v>
-      </c>
-      <c r="C773" s="2">
-        <v>12</v>
-      </c>
-      <c r="D773" s="2">
-        <v>1</v>
-      </c>
-      <c r="E773" s="2">
-        <v>447.66</v>
-      </c>
-      <c r="F773" s="4">
-        <f>B773/E773</f>
-      </c>
-      <c r="G773" s="2" t="s">
-        <v>953</v>
-      </c>
-      <c r="H773" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I773" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J773" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="K773" s="2" t="s">
-        <v>955</v>
-      </c>
-    </row>
-    <row r="774" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A774" s="2" t="s">
-        <v>731</v>
-      </c>
-      <c r="B774" s="3">
-        <v>1990000</v>
-      </c>
-      <c r="C774" s="2"/>
-      <c r="D774" s="2"/>
-      <c r="E774" s="2">
-        <v>333.83</v>
-      </c>
-      <c r="F774" s="4">
-        <f>B774/E774</f>
-      </c>
-      <c r="G774" s="2" t="s">
-        <v>953</v>
-      </c>
-      <c r="H774" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I774" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J774" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K774" s="2" t="s">
-        <v>956</v>
-      </c>
-    </row>
-    <row r="775" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A775" s="2" t="s">
-        <v>731</v>
-      </c>
-      <c r="B775" s="3">
-        <v>2050000</v>
-      </c>
-      <c r="C775" s="2"/>
-      <c r="D775" s="2"/>
-      <c r="E775" s="2">
-        <v>333.83</v>
-      </c>
-      <c r="F775" s="4">
-        <f>B775/E775</f>
-      </c>
-      <c r="G775" s="2" t="s">
-        <v>953</v>
-      </c>
-      <c r="H775" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I775" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J775" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K775" s="2" t="s">
-        <v>957</v>
-      </c>
-    </row>
-    <row r="776" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A776" s="2" t="s">
-        <v>731</v>
-      </c>
-      <c r="B776" s="3">
-        <v>595000</v>
-      </c>
-      <c r="C776" s="2">
-        <v>4</v>
-      </c>
-      <c r="D776" s="2">
-        <v>1</v>
-      </c>
-      <c r="E776" s="2">
-        <v>214.6</v>
-      </c>
-      <c r="F776" s="4">
-        <f>B776/E776</f>
-      </c>
-      <c r="G776" s="2" t="s">
-        <v>953</v>
-      </c>
-      <c r="H776" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I776" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J776" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K776" s="2" t="s">
-        <v>958</v>
-      </c>
-    </row>
-    <row r="777" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A777" s="2" t="s">
-        <v>731</v>
-      </c>
-      <c r="B777" s="3">
-        <v>2850000</v>
-      </c>
-      <c r="C777" s="2">
-        <v>6</v>
-      </c>
-      <c r="D777" s="2">
-        <v>1</v>
-      </c>
-      <c r="E777" s="2">
-        <v>455</v>
-      </c>
-      <c r="F777" s="4">
-        <f>B777/E777</f>
-      </c>
-      <c r="G777" s="2" t="s">
-        <v>953</v>
-      </c>
-      <c r="H777" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I777" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J777" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K777" s="2" t="s">
-        <v>959</v>
-      </c>
-    </row>
-    <row r="778" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A778" s="2" t="s">
-        <v>731</v>
-      </c>
-      <c r="B778" s="3">
-        <v>565000</v>
-      </c>
-      <c r="C778" s="2">
-        <v>1</v>
-      </c>
-      <c r="D778" s="2">
-        <v>1</v>
-      </c>
-      <c r="E778" s="2">
-        <v>72</v>
-      </c>
-      <c r="F778" s="4">
-        <f>B778/E778</f>
-      </c>
-      <c r="G778" s="2" t="s">
-        <v>960</v>
-      </c>
-      <c r="H778" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="I778" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="J778" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K778" s="2" t="s">
-        <v>961</v>
-      </c>
-    </row>
-    <row r="779" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A779" s="2" t="s">
-        <v>731</v>
-      </c>
-      <c r="B779" s="3">
-        <v>249000</v>
-      </c>
-      <c r="C779" s="2">
-        <v>1</v>
-      </c>
-      <c r="D779" s="2">
-        <v>1</v>
-      </c>
-      <c r="E779" s="2">
-        <v>31.19</v>
-      </c>
-      <c r="F779" s="4">
-        <f>B779/E779</f>
-      </c>
-      <c r="G779" s="2" t="s">
-        <v>960</v>
-      </c>
-      <c r="H779" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I779" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J779" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K779" s="2" t="s">
-        <v>962</v>
-      </c>
-    </row>
-    <row r="780" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A780" s="2" t="s">
-        <v>731</v>
-      </c>
-      <c r="B780" s="3">
-        <v>4095000</v>
-      </c>
-      <c r="C780" s="2">
-        <v>27</v>
-      </c>
-      <c r="D780" s="2">
-        <v>1</v>
-      </c>
-      <c r="E780" s="2">
-        <v>1737</v>
-      </c>
-      <c r="F780" s="4">
-        <f>B780/E780</f>
-      </c>
-      <c r="G780" s="2" t="s">
-        <v>963</v>
-      </c>
-      <c r="H780" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I780" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J780" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K780" s="2" t="s">
-        <v>964</v>
       </c>
     </row>
   </sheetData>
@@ -30575,527 +30069,527 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>965</v>
+        <v>948</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>966</v>
+        <v>949</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>967</v>
+        <v>950</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>968</v>
+        <v>951</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>969</v>
+        <v>952</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>970</v>
+        <v>953</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>971</v>
+        <v>954</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>971</v>
+        <v>954</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>971</v>
+        <v>954</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>971</v>
+        <v>954</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>972</v>
+        <v>955</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>972</v>
+        <v>955</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>973</v>
+        <v>956</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>973</v>
+        <v>956</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>973</v>
+        <v>956</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>974</v>
+        <v>957</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>974</v>
+        <v>957</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>974</v>
+        <v>957</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>975</v>
+        <v>958</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>976</v>
+        <v>959</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>977</v>
+        <v>960</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>977</v>
+        <v>960</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>977</v>
+        <v>960</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>977</v>
+        <v>960</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>978</v>
+        <v>961</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>979</v>
+        <v>962</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>980</v>
+        <v>963</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>980</v>
+        <v>963</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>980</v>
+        <v>963</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>981</v>
+        <v>964</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>982</v>
+        <v>965</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>982</v>
+        <v>965</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>983</v>
+        <v>966</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>983</v>
+        <v>966</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>983</v>
+        <v>966</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>984</v>
+        <v>967</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>984</v>
+        <v>967</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>984</v>
+        <v>967</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>985</v>
+        <v>968</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>985</v>
+        <v>968</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
-        <v>985</v>
+        <v>968</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
-        <v>986</v>
+        <v>969</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
-        <v>986</v>
+        <v>969</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
-        <v>987</v>
+        <v>970</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
-        <v>987</v>
+        <v>970</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
-        <v>988</v>
+        <v>971</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
-        <v>988</v>
+        <v>971</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
-        <v>989</v>
+        <v>972</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
-        <v>990</v>
+        <v>973</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
-        <v>990</v>
+        <v>973</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
-        <v>990</v>
+        <v>973</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>991</v>
+        <v>974</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
-        <v>992</v>
+        <v>975</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
-        <v>993</v>
+        <v>976</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
-        <v>993</v>
+        <v>976</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
-        <v>994</v>
+        <v>977</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
-        <v>994</v>
+        <v>977</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
-        <v>994</v>
+        <v>977</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
-        <v>995</v>
+        <v>978</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
-        <v>995</v>
+        <v>978</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
-        <v>996</v>
+        <v>979</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
-        <v>997</v>
+        <v>980</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" s="6" t="s">
-        <v>997</v>
+        <v>980</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
-        <v>997</v>
+        <v>980</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
-        <v>998</v>
+        <v>981</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
-        <v>998</v>
+        <v>981</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" s="6" t="s">
-        <v>998</v>
+        <v>981</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
-        <v>998</v>
+        <v>981</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
-        <v>998</v>
+        <v>981</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
-        <v>999</v>
+        <v>982</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" s="6" t="s">
-        <v>999</v>
+        <v>982</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" s="6" t="s">
-        <v>999</v>
+        <v>982</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" s="6" t="s">
-        <v>1000</v>
+        <v>983</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" s="6" t="s">
-        <v>1000</v>
+        <v>983</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" s="6" t="s">
-        <v>1000</v>
+        <v>983</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
-        <v>1000</v>
+        <v>983</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" s="6" t="s">
-        <v>1001</v>
+        <v>984</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" s="6" t="s">
-        <v>1001</v>
+        <v>984</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" s="6" t="s">
-        <v>1001</v>
+        <v>984</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" s="6" t="s">
-        <v>1001</v>
+        <v>984</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="6" t="s">
-        <v>1001</v>
+        <v>984</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" s="6" t="s">
-        <v>1002</v>
+        <v>985</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" s="6" t="s">
-        <v>1002</v>
+        <v>985</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" s="6" t="s">
-        <v>1002</v>
+        <v>985</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" s="6" t="s">
-        <v>1003</v>
+        <v>986</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" s="6" t="s">
-        <v>1004</v>
+        <v>987</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" s="6" t="s">
-        <v>1004</v>
+        <v>987</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" s="6" t="s">
-        <v>1004</v>
+        <v>987</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" s="6" t="s">
-        <v>1005</v>
+        <v>988</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" s="6" t="s">
-        <v>1005</v>
+        <v>988</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" s="6" t="s">
-        <v>1006</v>
+        <v>989</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" s="6" t="s">
-        <v>1006</v>
+        <v>989</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" s="6" t="s">
-        <v>1007</v>
+        <v>990</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" s="6" t="s">
-        <v>1007</v>
+        <v>990</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" s="6" t="s">
-        <v>1008</v>
+        <v>991</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" s="6" t="s">
-        <v>1008</v>
+        <v>991</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" s="6" t="s">
-        <v>1009</v>
+        <v>992</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" s="6" t="s">
-        <v>1010</v>
+        <v>993</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" s="6" t="s">
-        <v>1010</v>
+        <v>993</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" s="6" t="s">
-        <v>1011</v>
+        <v>994</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" s="6" t="s">
-        <v>1011</v>
+        <v>994</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" s="6" t="s">
-        <v>1012</v>
+        <v>995</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" s="6" t="s">
-        <v>1013</v>
+        <v>996</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" s="6" t="s">
-        <v>1014</v>
+        <v>997</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105" s="6" t="s">
-        <v>1015</v>
+        <v>998</v>
       </c>
     </row>
   </sheetData>
